--- a/工作日志.xlsx
+++ b/工作日志.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="96" activeTab="103"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="122" activeTab="129"/>
   </bookViews>
   <sheets>
     <sheet name="20240225" sheetId="89" r:id="rId1"/>
@@ -111,6 +111,32 @@
     <sheet name="20250522" sheetId="103" r:id="rId102"/>
     <sheet name="20250523" sheetId="104" r:id="rId103"/>
     <sheet name="20250524" sheetId="106" r:id="rId104"/>
+    <sheet name="20250525" sheetId="108" r:id="rId105"/>
+    <sheet name="20250526" sheetId="110" r:id="rId106"/>
+    <sheet name="20250527" sheetId="112" r:id="rId107"/>
+    <sheet name="20250528" sheetId="113" r:id="rId108"/>
+    <sheet name="20250529" sheetId="114" r:id="rId109"/>
+    <sheet name="20250530" sheetId="115" r:id="rId110"/>
+    <sheet name="20250531" sheetId="117" r:id="rId111"/>
+    <sheet name="20250601" sheetId="118" r:id="rId112"/>
+    <sheet name="20250602" sheetId="119" r:id="rId113"/>
+    <sheet name="20250603" sheetId="120" r:id="rId114"/>
+    <sheet name="20250604" sheetId="121" r:id="rId115"/>
+    <sheet name="20250605" sheetId="122" r:id="rId116"/>
+    <sheet name="20250607" sheetId="123" r:id="rId117"/>
+    <sheet name="20250608" sheetId="124" r:id="rId118"/>
+    <sheet name="20250609" sheetId="126" r:id="rId119"/>
+    <sheet name="20250610" sheetId="128" r:id="rId120"/>
+    <sheet name="20250611" sheetId="129" r:id="rId121"/>
+    <sheet name="20250612" sheetId="132" r:id="rId122"/>
+    <sheet name="20250613" sheetId="133" r:id="rId123"/>
+    <sheet name="20250614" sheetId="135" r:id="rId124"/>
+    <sheet name="20250615" sheetId="136" r:id="rId125"/>
+    <sheet name="20250616" sheetId="137" r:id="rId126"/>
+    <sheet name="20250617" sheetId="138" r:id="rId127"/>
+    <sheet name="20250618" sheetId="140" r:id="rId128"/>
+    <sheet name="20250619" sheetId="141" r:id="rId129"/>
+    <sheet name="20250620" sheetId="142" r:id="rId130"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -129,8 +155,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="2011">
   <si>
     <t>SRAM和DRAM的比较</t>
   </si>
@@ -2954,7 +3002,7 @@
     <t>绝对值之积等于###积的绝对值###</t>
   </si>
   <si>
-    <t>数列Xn具有有界性的含义：###|Xn|&lt;=M###</t>
+    <t>数列Xn具有有界性的含义：###min&lt;=Xn&lt;=max###</t>
   </si>
   <si>
     <t>分奇偶数类讨论：奇数类的情况+偶数类的情况=###全体整数类的情况###</t>
@@ -3950,10 +3998,10 @@
     <t>看到求矩阵的k次幂，就要想到这是利用相似对角化（无需作答）### ###</t>
   </si>
   <si>
-    <t>含抽象函数选择题的选项，一般来说要用###特殊情况###做###排除###</t>
-  </si>
-  <si>
-    <t>直接推导只能推###正确###的情况</t>
+    <t>含抽象函数选择题的选项，一般来说要用###特例或反例###做###排除###</t>
+  </si>
+  <si>
+    <t>直接推导只能推###正确###（正确/错误）的情况</t>
   </si>
   <si>
     <t>###不正确###的情况###不一定###和题设条件冲突，也可能只是###存在和题设条件兼容的反例###</t>
@@ -3998,7 +4046,7 @@
     <t>等价矩阵的###秩###相等（这个性质合同/相似矩阵也有）</t>
   </si>
   <si>
-    <t>合同矩阵的###正惯性指数###相等（合同矩阵特有）</t>
+    <t>合同矩阵的###正负惯性指数###相等（合同矩阵特有）</t>
   </si>
   <si>
     <t>相似矩阵的###特征值###和###特征向量###相等（相似矩阵特有）</t>
@@ -4109,7 +4157,7 @@
     <t>a²+b²###&gt;=###2ab, a+b###&gt;=###2*sqrt(ab)</t>
   </si>
   <si>
-    <t>x/(1+x)###&lt;=###ln(1+x), x###&gt;=###ln(1+x), x###&gt;=###-1（定义域）</t>
+    <t>对数不等式：x/(1+x)###&lt;=###ln(1+x), x###&gt;=###ln(1+x), x###&gt;###-1（定义域）</t>
   </si>
   <si>
     <t>以下不等式在x=###0###时取等号</t>
@@ -4824,6 +4872,1572 @@
   </si>
   <si>
     <t>积分中值定理：Int(a,b):f(x)dx=###(b-a)*f(ξ)###，中值ξ∈###闭区间[a,b]###</t>
+  </si>
+  <si>
+    <t>有限个无穷大的和差###不一定###（一定/不一定）是无穷大，有限个无穷小的和差###一定###（一定/不一定）是无穷小</t>
+  </si>
+  <si>
+    <t>地址线和地址引脚### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>地址线对CPU而言</t>
+  </si>
+  <si>
+    <t>地址线在CPU出厂就已经决定好了的，地址线是不会减半的</t>
+  </si>
+  <si>
+    <t>比如2^20个存储单元，需要20根地址线才能全部访问到</t>
+  </si>
+  <si>
+    <t>地址引脚是对DRAM而言</t>
+  </si>
+  <si>
+    <t>为了能节约空间以及把多个DRAM组成一个内存条，使用了引脚减半技术</t>
+  </si>
+  <si>
+    <t>把DRAM设计成矩阵型结构，通过内存控制器，先访问一行，再选中其中一列输出</t>
+  </si>
+  <si>
+    <t>408默认条件大全-通用规则</t>
+  </si>
+  <si>
+    <t>默认###小端###（大小端）存储方式</t>
+  </si>
+  <si>
+    <t>浮点数格式遵循###IEEE754###标准</t>
+  </si>
+  <si>
+    <t>默认各流水线阶段时间为###相等且无冲突###</t>
+  </si>
+  <si>
+    <t>408默认条件大全-计算机组成原理</t>
+  </si>
+  <si>
+    <t>DRAM行列复用地址引脚</t>
+  </si>
+  <si>
+    <t>存储总线宽度默认为按###字节（8位）###计算</t>
+  </si>
+  <si>
+    <t>当题目要求划分地址空间（如RAM与ROM）时，默认使用###高位###（高位/低位）地址线进行区域划分</t>
+  </si>
+  <si>
+    <t>题目中若涉及整数存储（如int类型），默认使用补码表示</t>
+  </si>
+  <si>
+    <t>408默认条件大全-操作系统</t>
+  </si>
+  <si>
+    <t>计算虚拟地址到物理地址的转换时，默认低位为###块内地址###，剩余高位为###页号或组号###</t>
+  </si>
+  <si>
+    <t>涉及锁操作（如swap指令）时，默认指令执行是原子的</t>
+  </si>
+  <si>
+    <t>408默认条件大全-计算机网络</t>
+  </si>
+  <si>
+    <t>NAT转发时，默认将###源IP###从私有地址转换为公共地址，且仅修改###源IP###，###目标IP###保持不变（源IP/目标IP）</t>
+  </si>
+  <si>
+    <t>计算子网可用地址时，默认排除###网络号###和###广播地址###</t>
+  </si>
+  <si>
+    <t>若题目未明确说明，IP分片时默认###不复制###（复制/不复制）原始分组的选项字段（如首部校验和）</t>
+  </si>
+  <si>
+    <t>408默认条件大全-数据结构</t>
+  </si>
+  <si>
+    <t>涉及多维数组地址计算时，默认按###行###（行/列）优先存储（如C语言数组）</t>
+  </si>
+  <si>
+    <t>题目中若未明确说明，默认二叉树的根节点编号为1</t>
+  </si>
+  <si>
+    <t>Cache系统的效率：###Cache的存取周期/平均存取时间###</t>
+  </si>
+  <si>
+    <t>根据命中率计算平均存取时间和效率需要保留小数点后至少三位，否则误差太大### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>408当中的K\M\G单位量级：涉及到速度，一个阶级按###1000###来升，涉及到空间容量大小，一个阶级按###1024###来升</t>
+  </si>
+  <si>
+    <t>按顺序增加，每次增加1000\1024量级：###KMGTPEZY###（至少八个）</t>
+  </si>
+  <si>
+    <t>被积函数奇偶性与变限积分的奇偶性</t>
+  </si>
+  <si>
+    <t>被积函数为奇函数的充要条件</t>
+  </si>
+  <si>
+    <t>Int(0,x):f(t)dt为###偶函数###（奇函数/偶函数）</t>
+  </si>
+  <si>
+    <t>Int(a,x):f(t)dt为###偶函数###（奇函数/偶函数）</t>
+  </si>
+  <si>
+    <t>被积函数为偶函数的充要条件</t>
+  </si>
+  <si>
+    <t>Int(0,x):f(t)dt为###奇函数###（奇函数/偶函数）</t>
+  </si>
+  <si>
+    <t>Int(a,x):f(t)dt为###奇函数###（奇函数/偶函数）</t>
+  </si>
+  <si>
+    <t>且Int(0,a):f(t)dt=###0###</t>
+  </si>
+  <si>
+    <t>Darboux定理</t>
+  </si>
+  <si>
+    <t>如果一个函数f(x)在区间I上有原函数F(x)</t>
+  </si>
+  <si>
+    <t>那么要么这个函数f(x)在区间I上连续</t>
+  </si>
+  <si>
+    <t>要么存在的间断点只能是###第二类间断点###</t>
+  </si>
+  <si>
+    <t>逆向思维：某函数F(x)若在I上处处可导</t>
+  </si>
+  <si>
+    <t>要么导函数f(x)在I上连续</t>
+  </si>
+  <si>
+    <t>要么导函数f(x)在I上只有###第二类间断点###</t>
+  </si>
+  <si>
+    <t>一种罕见的连续性证明</t>
+  </si>
+  <si>
+    <t>如果一个函数g(x)本身是f(x)的导数，也就是f'(x)=g(x)</t>
+  </si>
+  <si>
+    <t>并且明确知道f(x)在x0可导</t>
+  </si>
+  <si>
+    <t>即g(x)在x0处###有定义###</t>
+  </si>
+  <si>
+    <t>且f(x)的左导数和右导数###在此处相等且等于导函数g(x)的函数值###</t>
+  </si>
+  <si>
+    <t>那么导数f'(x0)=左导数f'-(x0)=lim(x-&gt;x0-):g(x)可以推出g(x)###左连续###（###左极限###等于该点函数值，此处为###左导数###）</t>
+  </si>
+  <si>
+    <t>那么导数f'(x0)=右导数f'+(x0)=lim(x-&gt;x0+):g(x)可以推出g(x)###右连续###（###右极限###等于该点函数值，此处为###右导数###）</t>
+  </si>
+  <si>
+    <t>当###左连续###和###右连续###同时成立，能够推出g(x)###在x0点连续###</t>
+  </si>
+  <si>
+    <t>设f(x)是R上周期为T(T&gt;0)的连续函数</t>
+  </si>
+  <si>
+    <t>那么lim(x-&gt;+∞):Int(0,x):f(t)dt/x=###Int(0,T):f(t)dt/T###</t>
+  </si>
+  <si>
+    <t>Int(0,x):f(t)dt可以写成###kx+h(x)###，其中h(x)是R上周期为T的函数，k为常数</t>
+  </si>
+  <si>
+    <t>反常积分不能抵消，但是定积分可以！！！### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>不是因式或者分母因子的非零因子不能直接代入！！！### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>特别提醒，比如复合函数的括号里面，或者指数是f(x)的底数当中</t>
+  </si>
+  <si>
+    <t>对数内的因子，当ln展开后会变成加和，这时无穷小的误差就会扩散出来</t>
+  </si>
+  <si>
+    <t>类似的，底数内的微小误差，经过无穷次方（即指数为含x的趋∞代数式）的放大，足以影响结果</t>
+  </si>
+  <si>
+    <t>一个容易遗忘的等价无穷小：ln(x+1)-x~###-t²/2###</t>
+  </si>
+  <si>
+    <t>（660题第31题）为什么一阶导数的极限定义在极限式内无法聚合为f'(x)？### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>极限求解过程有非常多的无穷小量，在一阶导的极限定义当中是存在的，但是去掉lim号（即摘帽）后就会忽略掉</t>
+  </si>
+  <si>
+    <t>重新把一阶导的极限定义作为一个更大极限表达式的一部分时，它内部的无穷小量会泄露到更大极限当中去</t>
+  </si>
+  <si>
+    <t>红黑树-基本的五条规则</t>
+  </si>
+  <si>
+    <t>非黑即红</t>
+  </si>
+  <si>
+    <t>根节点是###黑色###</t>
+  </si>
+  <si>
+    <t>叶节点是###黑色###</t>
+  </si>
+  <si>
+    <t>节点是红色，那么它的子节点一定是###黑色###</t>
+  </si>
+  <si>
+    <t>注意：###黑###节点可以有同色的子节点</t>
+  </si>
+  <si>
+    <t>任意节点到其子树中叶节点的路径，经过的###黑节点个数###相同</t>
+  </si>
+  <si>
+    <t>这个数量被称为###黑高###</t>
+  </si>
+  <si>
+    <t>包含###叶节点###，不包含###起始节点###</t>
+  </si>
+  <si>
+    <t>红黑树-衍生特性</t>
+  </si>
+  <si>
+    <t>从根到叶的最长路径，不超过最短路径的###两###倍</t>
+  </si>
+  <si>
+    <t>查询、插入、删除的时间复杂度都是###O(log(n))###</t>
+  </si>
+  <si>
+    <t>树高控制的结果</t>
+  </si>
+  <si>
+    <t>红黑树-旋转### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>左旋-逆时针，右旋-顺时针</t>
+  </si>
+  <si>
+    <t>右（对应左旋）子节点A取代父节点B</t>
+  </si>
+  <si>
+    <t>父节点B变成新父节点A的左子节点</t>
+  </si>
+  <si>
+    <t>父节点的右子节点（原本是A），现在去接管孙子，也就是A原本的左子节点</t>
+  </si>
+  <si>
+    <t>儿子当家，老人照顾孙子</t>
+  </si>
+  <si>
+    <t>旋转前的子树和旋转后的（结构上）对称</t>
+  </si>
+  <si>
+    <t>红黑树-插入：和普通BST一样</t>
+  </si>
+  <si>
+    <t>从根开始</t>
+  </si>
+  <si>
+    <t>大###左###小###右###（左/右）</t>
+  </si>
+  <si>
+    <t>插入###红###色节点（每一个朝代的开始都是革命）</t>
+  </si>
+  <si>
+    <t>红黑树-插入-调整：当破坏了规则4（###不红红###）会触发</t>
+  </si>
+  <si>
+    <t>红叔（只换颜色，朱家自己人，不发生权力更迭）</t>
+  </si>
+  <si>
+    <t>叔父都变黑</t>
+  </si>
+  <si>
+    <t>爷爷变红</t>
+  </si>
+  <si>
+    <t>然后以爷爷的视角（即把爷爷当成孙子）向上检查</t>
+  </si>
+  <si>
+    <t>黑叔（据说朱棣不是马皇后亲生的）</t>
+  </si>
+  <si>
+    <t>亲近叔</t>
+  </si>
+  <si>
+    <t>父子交替，原来的父亲（现在的儿子）远离叔叔</t>
+  </si>
+  <si>
+    <t>变成儿子远离叔的情况处理</t>
+  </si>
+  <si>
+    <t>远离叔（正史）</t>
+  </si>
+  <si>
+    <t>父亲变黑，爷爷变红（朱标死了，朱元璋红温了）</t>
+  </si>
+  <si>
+    <t>发生旋转，侄儿上去，叔叔下去（朱允炆登基，削藩开始）</t>
+  </si>
+  <si>
+    <t>总结：只有叔父不和（黑叔红父）且父亲与儿子亲近（同红），旋转（权力变化）才会发生</t>
+  </si>
+  <si>
+    <t>红黑树-删除：和普通BST一样</t>
+  </si>
+  <si>
+    <t>无孩或只有独生子：###有则继承，无则不管###</t>
+  </si>
+  <si>
+    <t>注意，这种情况不是值复制！！！（不会###继承被替换节点的颜色###！）</t>
+  </si>
+  <si>
+    <t>有两个孩子：</t>
+  </si>
+  <si>
+    <t>找被删节点A在###中序###遍历上的后继结点B</t>
+  </si>
+  <si>
+    <t>后继一定满足###无孩###或###只有独生子###</t>
+  </si>
+  <si>
+    <t>复制B的值来顶替被删节点A的位置（新节点使用###A###（A/B）的颜色）</t>
+  </si>
+  <si>
+    <t>从B原来的位置删除B（对B进行删除操作，B的后继C保持颜色的前提下顶替B）</t>
+  </si>
+  <si>
+    <t>红黑树-删除-调整：</t>
+  </si>
+  <si>
+    <t>注意：以下情况均为BST删除及替换发生后</t>
+  </si>
+  <si>
+    <t>无替换（比如红节点的黑子被直接删除，黑兄弟会与红父交换）：？？？</t>
+  </si>
+  <si>
+    <t>有替换</t>
+  </si>
+  <si>
+    <t>红替红：###违反不红红，不可能存在###</t>
+  </si>
+  <si>
+    <t>红替黑或者黑替红：###替上来一律变黑###</t>
+  </si>
+  <si>
+    <t>黑替黑：？？？</t>
+  </si>
+  <si>
+    <t>单调有界必有极限是数列才有的性质，函数没有，不能乱用！### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>遇到函数还有有界性，考虑用###闭区间连续的特性###来推（20240415）</t>
+  </si>
+  <si>
+    <t>补充：f'(x)在有限区间I上有界，那么f(x)也在I上有界（充分不必要）</t>
+  </si>
+  <si>
+    <t>f(x)=φ(x)*|x-a|，φ(x)在x=a连续</t>
+  </si>
+  <si>
+    <t>f(x)在x=a处可导的充要条件：###φ(a)=0###</t>
+  </si>
+  <si>
+    <t>RISC架构不允许在运算时访存的原因</t>
+  </si>
+  <si>
+    <t>简化指令集，确保###指令长度###不变</t>
+  </si>
+  <si>
+    <t>减少###访存###导致的流水延迟</t>
+  </si>
+  <si>
+    <t>RISC采用###硬布线###式CU，兼容访存大幅度增加CU设计难度</t>
+  </si>
+  <si>
+    <t>分离访存操作，从应用层面上考虑，有助于###编译器优化###</t>
+  </si>
+  <si>
+    <t>RISC和CISC的差异总结</t>
+  </si>
+  <si>
+    <t>指令长度：RISC采用###定长###，CISC采用###变长###</t>
+  </si>
+  <si>
+    <t>指令数量：RISC###更少###，CISC###更多###</t>
+  </si>
+  <si>
+    <t>寻址方式：RISC###更少###，CISC###更多###</t>
+  </si>
+  <si>
+    <t>可以访存：RISC访存###仅限LOAD/STORE指令###，CISC访存###兼容大部分指令###</t>
+  </si>
+  <si>
+    <t>控制单元（CU）：RISC采用###硬布线###，CISC采用###微程序###</t>
+  </si>
+  <si>
+    <t>执行周期：RISC采用###单周期指令###，CISC采用###多周期指令###</t>
+  </si>
+  <si>
+    <t>芯片面积：RISC###更小###，CISC###更大###</t>
+  </si>
+  <si>
+    <t>编码密度：RISC###更低###，CISC###更高###</t>
+  </si>
+  <si>
+    <t>编译优化难度：RISC###更低###，CISC###更高###</t>
+  </si>
+  <si>
+    <t>使用裸机运行程序的CPU核心态</t>
+  </si>
+  <si>
+    <t>默认就处于###核心态###，意味着可执行指令为###全部###指令（全部/部分）</t>
+  </si>
+  <si>
+    <t>加载完操作系统后，###操作系统###的程序把PSW的核心态改为###用户###态</t>
+  </si>
+  <si>
+    <t>CRC校验</t>
+  </si>
+  <si>
+    <t>根据生成多项式写出###多项式对应二进制数A###</t>
+  </si>
+  <si>
+    <t>根据###多项式的最高次幂###指定校验位长度</t>
+  </si>
+  <si>
+    <t>信息位对应二进制数B作为###被除数###，与B进行除法</t>
+  </si>
+  <si>
+    <t>异或除法，相同余0，不同余1</t>
+  </si>
+  <si>
+    <t>向后借位使###最高1位对齐###</t>
+  </si>
+  <si>
+    <t>无位可借，则###计算结束，被除数作为余数###</t>
+  </si>
+  <si>
+    <t>得到余数根据校验位长度，高位补零</t>
+  </si>
+  <si>
+    <t>流水线性能指标计算</t>
+  </si>
+  <si>
+    <t>流水线时钟周期：###最长流水阶段的耗时###</t>
+  </si>
+  <si>
+    <t>不考虑数据冲突的总耗时：###第一条指令耗时（各阶段时长总和）+（指令条数-1）*时钟周期###</t>
+  </si>
+  <si>
+    <t>考虑数据冲突的总耗时：###不考虑数据冲突的总耗时+冲突次数*流水线时钟周期###</t>
+  </si>
+  <si>
+    <t>吞吐率：###指令数/实际耗时（考虑数据冲突）###</t>
+  </si>
+  <si>
+    <t>加速比：###非流水执行全部指令耗时/流水执行耗时（考虑数据冲突）###</t>
+  </si>
+  <si>
+    <t>效率：###加速比/流水阶段个数###</t>
+  </si>
+  <si>
+    <t>IEEE754表示</t>
+  </si>
+  <si>
+    <t>核心公式：###((-1)^s)*(1.M)*(2^E)###</t>
+  </si>
+  <si>
+    <t>s为符号位，M为尾数，E为阶码</t>
+  </si>
+  <si>
+    <t>表示：</t>
+  </si>
+  <si>
+    <t>符号位1位</t>
+  </si>
+  <si>
+    <t>阶码E共###8###位，为###真值+127###的###移码###（偏移后的原码）</t>
+  </si>
+  <si>
+    <t>尾数M共###23###位，为###去掉最高位1###的###原###码</t>
+  </si>
+  <si>
+    <t>十进制转二进制</t>
+  </si>
+  <si>
+    <t>把十进制数按核心公式写出</t>
+  </si>
+  <si>
+    <t>写出对应的二进制</t>
+  </si>
+  <si>
+    <t>二进制转十进制</t>
+  </si>
+  <si>
+    <t>按位数分块给出符号、阶码、尾数</t>
+  </si>
+  <si>
+    <t>写出对应的十进制</t>
+  </si>
+  <si>
+    <t>IEEE754加减</t>
+  </si>
+  <si>
+    <t>获得二进制表示</t>
+  </si>
+  <si>
+    <t>确定阶码是否相同</t>
+  </si>
+  <si>
+    <t>若不同，进行对阶，###低###阶向###高###阶看齐</t>
+  </si>
+  <si>
+    <t>阶码增加，尾数同步###右###移/规，阶码减少，尾数同步###左###移/规</t>
+  </si>
+  <si>
+    <t>尾数带上隐藏位和符号位，进行原码加减</t>
+  </si>
+  <si>
+    <t>产生的新尾数根据小数点左侧是否仅1来进行规格化</t>
+  </si>
+  <si>
+    <t>阶码如果在规格化过程中变为###全1###，则发生了规格化###上溢###</t>
+  </si>
+  <si>
+    <t>阶码如果在规格化过程中变为###全0###，则发生了规格化###下溢###</t>
+  </si>
+  <si>
+    <t>如果发生###下溢###，则###使用非规格化表示###</t>
+  </si>
+  <si>
+    <t>即阶码全0###，尾数也采用对应规格（即隐藏位###为0###）</t>
+  </si>
+  <si>
+    <t>恢复余数</t>
+  </si>
+  <si>
+    <t>先把除数和被除数的符号进行###异或###，得到###商的符号###</t>
+  </si>
+  <si>
+    <t>然后用被除数和除数的###绝对值###（下文提到的被除数和除数）进行除法求出###商的绝对值###</t>
+  </si>
+  <si>
+    <t>初始化：余数为###0###，位数n为被除数和除数的位数</t>
+  </si>
+  <si>
+    <t>循环步骤1.余数减去除数</t>
+  </si>
+  <si>
+    <t>循环步骤2.判断是否小于0</t>
+  </si>
+  <si>
+    <t>分支2.1.若差小于0，则###差加回除数恢复余数###，商上###0###</t>
+  </si>
+  <si>
+    <t>分支2.2.若差大于0，则###什么也不做###，商上###1###</t>
+  </si>
+  <si>
+    <t>循环步骤3.中间余数低位拼接###被除数###，两者一起向###左###移位，低位补###0###</t>
+  </si>
+  <si>
+    <t>循环步骤4.拼接数高n位作为新的###余数###，低n位作为新的###被除数###</t>
+  </si>
+  <si>
+    <t>重复循环###n+1###次，从最###低###位开始截取商的###n###位，乘上商的符号，作为最终结果</t>
+  </si>
+  <si>
+    <t>组合积分的扩展### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>例子：sinx*sin2x*sin3x进行非恒等变换，加上和减去cosx*cos2x*cos3x，两个衍生积分分别使用cos的和角与差角公式</t>
+  </si>
+  <si>
+    <t>本质：k*I=I1±I2，I1≠I2≠I（这一点区分于循环分部积分为代表的A=f(x)+kA）</t>
+  </si>
+  <si>
+    <t>已知场景：大量出现正余弦函数，且简单变形（可以是非恒等）后具有对偶性</t>
+  </si>
+  <si>
+    <t>目标：寻找可以分别进行积分求解的“积木块”（和二重积分轮换对称后相加相消的思路相反）</t>
+  </si>
+  <si>
+    <t>倒数式区间再现</t>
+  </si>
+  <si>
+    <t>上下限为从a到b</t>
+  </si>
+  <si>
+    <t>那么t可以除了可以换元为t=a+b-x外，还可以换元为t=###a*b/x###</t>
+  </si>
+  <si>
+    <t>由于t=###a*b/x###，上下限变为###a*b/a=b###到###a*b/b=a###，发生了第一次交换</t>
+  </si>
+  <si>
+    <t>与此同时，因为x=###a*b/t###，dx=###-a*b/t²dt###，将###负号提出###，则上下限再次交换，区间相比原式维持不变</t>
+  </si>
+  <si>
+    <t>定积分应用类，上下限如果不是特殊角的三角函数值的题目，建议不要使用三角换元。### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>口诀：662N4 收发协数验</t>
+  </si>
+  <si>
+    <t>解释：这是###802.3###标准的</t>
+  </si>
+  <si>
+    <t>###数据链路###层的</t>
+  </si>
+  <si>
+    <t>###帧###（该类报文的称呼）协议报文字段###长度###（总长度/单位长度）信息</t>
+  </si>
+  <si>
+    <t>收发协数验：###目的MAC、源MAC、协议类型、数据、校验码###</t>
+  </si>
+  <si>
+    <t>TCP三握四挥的恋爱比喻### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>三握：男客户端，女服务端</t>
+  </si>
+  <si>
+    <t>男：我喜欢你！</t>
+  </si>
+  <si>
+    <t>女：我也喜欢你！</t>
+  </si>
+  <si>
+    <t>男：那咱们交往吧！</t>
+  </si>
+  <si>
+    <t>四挥：男客户端，女服务端</t>
+  </si>
+  <si>
+    <t>男：我们分手吧。</t>
+  </si>
+  <si>
+    <t>女：我需要考虑一下。</t>
+  </si>
+  <si>
+    <t>女：好吧，我同意分手。</t>
+  </si>
+  <si>
+    <t>男：祝你幸福。</t>
+  </si>
+  <si>
+    <t>函数函数在a到b（a≠b）之间的均值</t>
+  </si>
+  <si>
+    <t>定义：###f(x)从a到b的定积分除以(b-a)###</t>
+  </si>
+  <si>
+    <t>注意：如果进行###换元###，除区间长度以###原来的###为准</t>
+  </si>
+  <si>
+    <t>正弦和余弦函数求一次导，等于###相位###加上###pi/2###</t>
+  </si>
+  <si>
+    <t>f(x)是在R上以T为周期的连续函数，则下述命题互为充要条件</t>
+  </si>
+  <si>
+    <t>变限积分Int(0,x):f(t)dt为以T为周期的函数</t>
+  </si>
+  <si>
+    <t>定积分Int(0.T):f(t)dt=###0###</t>
+  </si>
+  <si>
+    <t>不定积分改写定（变限积分）的题目条件暗示### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>对不定积分进行求导（位于极限分子时，极限整体要洛必达）</t>
+  </si>
+  <si>
+    <t>不定积分经过某个定点，研究周期性和奇偶性</t>
+  </si>
+  <si>
+    <t>二阶变系数齐次线性微分方程</t>
+  </si>
+  <si>
+    <t>题目形式：给出方程，然后给两个解y1和y2（其中一个含有未知的抽象函数u(x)），求通解y*</t>
+  </si>
+  <si>
+    <t>核心是求出u(x)，可以利用公式###y1'y2-y2'y1=C*exp(-Int:p(x)dx)###，其中p(x)为###一阶导前的变系数###</t>
+  </si>
+  <si>
+    <t>求出u(x)，就能得到y1和y2的具体形式，然后用y1和y2带系数组成通解y*</t>
+  </si>
+  <si>
+    <t>分时系统必有###交互###性</t>
+  </si>
+  <si>
+    <t>微内核的缺点是###效率低下###</t>
+  </si>
+  <si>
+    <t>极限保序性</t>
+  </si>
+  <si>
+    <t>条件</t>
+  </si>
+  <si>
+    <t>在x=x0的去心（不等于x0）邻域（左、右、双侧）</t>
+  </si>
+  <si>
+    <t>恒有f(x)###&lt;=###g(x)（小于/小于等于）</t>
+  </si>
+  <si>
+    <t>结论</t>
+  </si>
+  <si>
+    <t>f在x左（右）极限为a，g在x左（右）极限为b</t>
+  </si>
+  <si>
+    <t>必有a###&lt;=###b（小于/小于等于）</t>
+  </si>
+  <si>
+    <t>易错</t>
+  </si>
+  <si>
+    <t>条件是###非严格###不等式，结论是###非严格###不等式（严格/非严格）</t>
+  </si>
+  <si>
+    <t>即使条件是###严格###不等式，也只能推###非严格###不等式结论</t>
+  </si>
+  <si>
+    <t>原因：极限只是一种趋势，即使函数值始终小，但趋势也可能接近并相等</t>
+  </si>
+  <si>
+    <t>反例：f=x，g=x+|x|，x0取x=0</t>
+  </si>
+  <si>
+    <t>逆定理：左（右）极限###严格###有序，则必存在去心左（右）邻域使邻域内的函数值也###严格###保序（严格/非严格）</t>
+  </si>
+  <si>
+    <t>任何函数都可以分解为一个奇函数与一个偶函数的和### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>可以用于一个函数和它自变量取相反数进行加减时使用</t>
+  </si>
+  <si>
+    <t>数列Xn有界的充要条件（原20240426答疑整理4）：###|Xn|&lt;=M###</t>
+  </si>
+  <si>
+    <t>对于省去正负号的分类讨论很有用</t>
+  </si>
+  <si>
+    <t>要注意f(x)=lim(t):g(t,x)这种方式定义的函数</t>
+  </si>
+  <si>
+    <t>讨论f(x)间断点前，要先###设法去掉lim(t)###，把###极限定义###形式转为###一般解析###形式，然后再研究</t>
+  </si>
+  <si>
+    <t>线性微分方程的特点</t>
+  </si>
+  <si>
+    <t>各阶导数的次幂为###1或0###次</t>
+  </si>
+  <si>
+    <t>最高阶导数的次幂一定为###1###次</t>
+  </si>
+  <si>
+    <t>各阶导数只能以###线性组合###的形式出现</t>
+  </si>
+  <si>
+    <t>不能有不同阶导数的###乘积###或###复合###</t>
+  </si>
+  <si>
+    <t>易错点：要注意，有些线性微分方程的是x(y)型而非常见的y(x)型</t>
+  </si>
+  <si>
+    <t>比如x*dy/dx=cos(y)+1</t>
+  </si>
+  <si>
+    <t>z=f(x,y)的二阶混合偏导均在区域D上连续，则二者相等### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>中断机制是CPU都有的，即使没有操作系统也会有中断</t>
+  </si>
+  <si>
+    <t>###GPRs、用户栈指针###的保存是操作系统独有的</t>
+  </si>
+  <si>
+    <t>保存###PC、PSW、###是裸机和操作系统都有的</t>
+  </si>
+  <si>
+    <t>其中###PSW###的保存是子程序调用时不会发生的</t>
+  </si>
+  <si>
+    <t>子程序调用和系统调用都是程序调用，主要区别在于###是否有处理机状态切换###</t>
+  </si>
+  <si>
+    <t>两者均遵循：</t>
+  </si>
+  <si>
+    <t>1.###入参压栈（一般子程序）/压寄存器（系统调用）###</t>
+  </si>
+  <si>
+    <t>2.###call/trap指令###</t>
+  </si>
+  <si>
+    <t>3.###保存现场###</t>
+  </si>
+  <si>
+    <t>4.###程序入口装入PC并开始执行###</t>
+  </si>
+  <si>
+    <t>系统/程序调用是###同步###事件，###无需###关中断</t>
+  </si>
+  <si>
+    <t>5.###恢复现场（系统/程序调用是同步事件，无需关中断）###</t>
+  </si>
+  <si>
+    <t>保存与恢复现场：中断和调用程序的差异</t>
+  </si>
+  <si>
+    <t>系统/程序调用是###同步###事件，###无需###关开中断</t>
+  </si>
+  <si>
+    <t>中断是###异步###事件，###需要###关开中断</t>
+  </si>
+  <si>
+    <t>分母真0会破坏极限的定义（处处有定义的去心邻域）### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>极限求解时的部分极限恒定性（存在一个恒等于某常数的去心邻域）会导致这个部分极限退化为该常数### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>举例：f(x)在某点x0处存在恒为c的去心邻域，那么lim(x-&gt;x0):g(f(x),x)=lim(x-&gt;x0):g(c,x)</t>
+  </si>
+  <si>
+    <t>多用户一定分时，分时未必多用户### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>NVRAM很小，不可能从中加载ISO### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>分配资源的基本单位</t>
+  </si>
+  <si>
+    <t>作业：###批处理系统###</t>
+  </si>
+  <si>
+    <t>进程：###多道程序系统###</t>
+  </si>
+  <si>
+    <t>响应中断的三条件### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>中断源发出的中断请求</t>
+  </si>
+  <si>
+    <t>CPU允许中断</t>
+  </si>
+  <si>
+    <t>内部中断无法被屏蔽（关中断也无效）</t>
+  </si>
+  <si>
+    <t>当前指令执行完成且无更紧急任务</t>
+  </si>
+  <si>
+    <t>外中断、非异常内中断检测发生在指令执行后</t>
+  </si>
+  <si>
+    <t>异常（内部中断的一种）检测发生在执行执行中</t>
+  </si>
+  <si>
+    <t>多元函数极限的套路</t>
+  </si>
+  <si>
+    <t>优先观察能否进行###极坐标转换###</t>
+  </si>
+  <si>
+    <t>不能的情况下进行###夹逼求解###</t>
+  </si>
+  <si>
+    <t>###两侧极限###尽量构造为适合进行###极坐标转换###的类型</t>
+  </si>
+  <si>
+    <t>极限定义的函数（f(x)=lim(t):g(t,x)）在极限不存在（无论是无穷还是震荡）处的点无定义### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>分母x^t，x&lt;-1，t趋于无穷，那么1/(x^t)的极限###为0（|x|^t是无穷大，吸收(-1)^t的有界振荡）###</t>
+  </si>
+  <si>
+    <t>柯西洗袜子不等式：</t>
+  </si>
+  <si>
+    <t>(x²+y²)*(m²+n²)###&gt;=###(m*x+n*y)²</t>
+  </si>
+  <si>
+    <t>(x²-y²)*(m²-n²)###&lt;=###(m*x-n*y)²</t>
+  </si>
+  <si>
+    <t>(x+y)*(m+n)###&gt;=###(sqrt(m*x)+sqrt(n*y))²</t>
+  </si>
+  <si>
+    <t>(x+y)*(m²/x+n²/y)###&gt;=###(m+n)²</t>
+  </si>
+  <si>
+    <t>汇编和链接的先后顺序：先###汇编###，后###链接###</t>
+  </si>
+  <si>
+    <t>汇编：###汇编指令###转###二进制###</t>
+  </si>
+  <si>
+    <t>链接：###分散二进制程序###转###单一二进制程序###</t>
+  </si>
+  <si>
+    <t>原因：符号引用的解析需要二进制的###地址偏移###</t>
+  </si>
+  <si>
+    <t>中断式I/O，外设准备数据不能###快于###（快于/慢于）中断处理，否则会造成###数据丢失###</t>
+  </si>
+  <si>
+    <t>多元函数的极限确定存在时，可以锁定其中一个变量到趋向点，使极限变为一个一元极限### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>当f(x,y)在(0,0)点连续，且lim(x,y-&gt;0):f(x,y)/(x²+y²)存在时，可以立刻得到f(x,y)###可微###</t>
+  </si>
+  <si>
+    <t>那个极限存在，可以得到###lim(x,y-&gt;0):f(x,y)=0###</t>
+  </si>
+  <si>
+    <t>上一条加连续，可以得到###f(x,y)=0###</t>
+  </si>
+  <si>
+    <t>偏导定义：###lim(x-&gt;0):(f(x,0)-f(0,0))/x###</t>
+  </si>
+  <si>
+    <t>分子简化：###lim(x-&gt;0):f(x,0)/x###</t>
+  </si>
+  <si>
+    <t>条件极限锁定y=0：###lim(x-&gt;0):f(x,0)/(x²+y²)###存在</t>
+  </si>
+  <si>
+    <t>比阶：f(x,0)比###x²+y²###高阶，###x²+y²###比###x###高阶，因此f(x,0)比###x###高阶</t>
+  </si>
+  <si>
+    <t>偏导=0</t>
+  </si>
+  <si>
+    <t>可微定义式：###(f(x,y)-f(0,0)-fx(0,0)x-fy(0,0)y)/sqrt(x²+y²)###</t>
+  </si>
+  <si>
+    <t>偏导真0：###(f(x,y)-f(0,0))/sqrt(x²+y²)###</t>
+  </si>
+  <si>
+    <t>利用连续：###f(x,y)/sqrt(x²+y²)###</t>
+  </si>
+  <si>
+    <t>比阶：f(x,y)比###x²+y²###高阶，###x²+y²###比###sqrt(x²+y²)###高阶，因此f(x,y)比###sqrt(x²+y²)###高阶</t>
+  </si>
+  <si>
+    <t>可微定义极限=0</t>
+  </si>
+  <si>
+    <t>多项式韦达定理：</t>
+  </si>
+  <si>
+    <t>(x-a1)*(x-a2)*...*(x-an)=(x^n)+(c[n-1]*x^(n-1))+...+c1*x+c0</t>
+  </si>
+  <si>
+    <t>c[n-1]=###-(a1+a2+a3+...+an)###</t>
+  </si>
+  <si>
+    <t>c[n-k]=###((-1)^k)*k个不同ai乘积的和###</t>
+  </si>
+  <si>
+    <t>c[0]=###((-1)^n)*a1*a2*a3*...*an###</t>
+  </si>
+  <si>
+    <t>命令解释器和解释型语言的解释器是不同的东西，当“命令”出现时，它指的是cmd或者bash这种操作系统提供的命令接口。### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>多元偏导存在不能推连续，更不能推极限存在</t>
+  </si>
+  <si>
+    <t>但是可以推###剖面曲线###连续</t>
+  </si>
+  <si>
+    <t>函数最值问题记得要验证不可导点### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>用户态切换核心态需要靠硬件（中断必核心），反之不需要（特权指令）### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>操作系统的分层式架构便于调试### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>启机相关问题</t>
+  </si>
+  <si>
+    <t>启机顺序：###BIOS###-&gt;###引导程序/Bootloader###-&gt;###操作系统内核###</t>
+  </si>
+  <si>
+    <t>BIOS：位于主板的ROM，嵌入式设备没有</t>
+  </si>
+  <si>
+    <t>引导程序/Bootloader：位于硬盘引导分区或者Flash，嵌入式设备的Bootloader要负责BIOS的任务</t>
+  </si>
+  <si>
+    <t>BIOS的顺序：###跳转BIOS###-&gt;###设定BIOS中断服务地址###-&gt;###硬件自检###-&gt;###跳转引导程序/Bootloader###</t>
+  </si>
+  <si>
+    <t>拐点（凹凸性改变点）可以是不可导点</t>
+  </si>
+  <si>
+    <t>举例：f(x)=x^(1/3)在x=0处，切线垂直，导数为无穷大，但是在该点处二阶导###异号###（无论是否可导）</t>
+  </si>
+  <si>
+    <t>可能创建进程的操作四种：###用户登录、作业调度、提供服务、应用请求###</t>
+  </si>
+  <si>
+    <t>并发程序执行的特点是间断性### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>死锁的四个条件：###资源互斥、有了还要、不可剥夺、循环等待###</t>
+  </si>
+  <si>
+    <t>管程可以做空，先V后P，但一般进程中直接使用的信号量则不可以### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>父进程撤销，其从属的子进程也要撤销### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>不死锁的最少资源个数：###n*(m-1)+1###，其中，n为进程个数，m为每个进程需要的资源个数</t>
+  </si>
+  <si>
+    <t>变限积分求导公式的使用条件</t>
+  </si>
+  <si>
+    <t>被积函数f(x)在###闭##区间a到b上##连续###</t>
+  </si>
+  <si>
+    <t>变限积分的可导性和求导公式也仅在###闭区间a到b###上成立</t>
+  </si>
+  <si>
+    <t>非连续点必须用###求导的极限定义###求解</t>
+  </si>
+  <si>
+    <t>特例法大杀器-常见性质### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）：f(x)在区间区间(a,b)内具有k阶导数</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）：f(x,y)在趋区域D内存在一阶偏导fx(x,y)和fy(x,y)，且D内处处可求偏导</t>
+  </si>
+  <si>
+    <t>连续性（一元）：f(x)在开（闭）区间a到b上连续</t>
+  </si>
+  <si>
+    <t>可微性（多元）：f(x,y)在点(x0,y0)处可微，满足可微的极限定义式等于0</t>
+  </si>
+  <si>
+    <t>极限存在（一元）：f(x)在x趋于x0时极限存在，且极限等于A</t>
+  </si>
+  <si>
+    <t>连续性（多元）：f(x,y)在区域D上连续，D内任意点处f(x,y)的极限等于f(x,y)在该点处的函数值</t>
+  </si>
+  <si>
+    <t>周期性（一元）：f(x)是以T为周期的周期函数，满足f(x+T)=f(x)</t>
+  </si>
+  <si>
+    <t>可定积分（一元）：f(x)在开（闭）区间a到b上可积，且定积分值等于常数k</t>
+  </si>
+  <si>
+    <t>二阶偏导连续（多元）：f(x,y)在区域D内的二阶偏导数均连续，满足fxy(x,y)=fyx(x,y)（混合偏导相等）</t>
+  </si>
+  <si>
+    <t>奇函数（一元）：f(x)在定义域内满足f(-x)=-f(x)</t>
+  </si>
+  <si>
+    <t>偶函数（一元）：f(x)在定义域内满足f(-x)=f(x)</t>
+  </si>
+  <si>
+    <t>相切（一元）：f(x)在点(x0,f(x0))处与直线y=kx+b相切</t>
+  </si>
+  <si>
+    <t>反常积分收敛（一元）：被积函数为f(x)的无穷积分/瑕积分（若无瑕点，则在无穷限上积分）收敛到常数C</t>
+  </si>
+  <si>
+    <t>如果约束是等式约束，可以把约束代入目标函数，转化为无条件极值（无需拉格朗日乘数法）### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>特例法大杀器-二元组合### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+连续性（一元）</t>
+  </si>
+  <si>
+    <t>00：分段函数{f(x)=1,x≥0;f(x)=-1,x&lt;0}，在x=0处不连续且不可导。</t>
+  </si>
+  <si>
+    <t>01：函数f(x)=|x|，在x=0处连续但不可导。</t>
+  </si>
+  <si>
+    <t>10：NA（可导函数必连续，不存在可导但不连续的函数）。</t>
+  </si>
+  <si>
+    <t>11：函数f(x)=x²，在实数域内连续且二阶可导。</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>00：分段函数{f(x)=sin(1/x),x≠0;f(x)=0,x=0}，在x=0处极限不存在且不可导。</t>
+  </si>
+  <si>
+    <t>01：分段函数{f(x)=|x|,x≠0;f(x)=1,x=0}，在x=0处极限存在（为0）但不连续（故不可导）。</t>
+  </si>
+  <si>
+    <t>10：NA（可导必连续，连续必极限存在，不存在可导但极限不存在的函数）。</t>
+  </si>
+  <si>
+    <t>11：函数f(x)=x³，在实数域内可导且极限处处存在。</t>
+  </si>
+  <si>
+    <t>连续性（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>00：分段函数{f(x)=sin(1/x),x≠0;f(x)=0,x=0}，在x=0处极限不存在且不连续。</t>
+  </si>
+  <si>
+    <t>01：分段函数{f(x)=x,x≠0;f(x)=1,x=0}，在x=0处极限存在（值为0）但不连续。</t>
+  </si>
+  <si>
+    <t>10：NA（连续函数在该点极限必存在，无法构造反例）。</t>
+  </si>
+  <si>
+    <t>11：函数f(x)=x，在实数域内处处连续且极限存在。</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）</t>
+  </si>
+  <si>
+    <t>00：函数f(x,y)=|x|+|y|，在点(0,0)处对x的偏导数lim(Δx→0)|Δx|/Δx不存在，对y的偏导数同理不存在，故偏导数不存在且不可微。</t>
+  </si>
+  <si>
+    <t>01：NA（可微性要求偏导数必存在，无法构造偏导数不存在但可微的函数）。</t>
+  </si>
+  <si>
+    <t>10：函数{f(x,y)=x²y/(x⁴+y²),(x,y)≠(0,0);f(x,y)=0,(x,y)=(0,0)}，在点(0,0)处偏导数fₓ(0,0)=fᵧ(0,0)=0，但沿路径y=kx²趋近(0,0)时，lim(x→0,y=kx²)[f(x,y)-0-0・x-0・y]/sqrt(x²+y²)与k相关，不满足可微的极限定义，故偏导数存在但不可微。</t>
+  </si>
+  <si>
+    <t>11：函数f(x,y)=x²+y²，在任意点(x,y)处偏导数fₓ=2x、fᵧ=2y存在且连续，全微分df=2xdx+2ydy成立，故偏导数存在且可微。</t>
+  </si>
+  <si>
+    <t>死锁检测###不需要###（需要/不需要）知道进程所需资源总量</t>
+  </si>
+  <si>
+    <t>特例法大杀器-三元组合### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+连续性（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>000：分段函数{f(x)=1/x,x≠0;f(x)=0,x=0}，在x=0处极限不存在（左右极限均为无穷）、不连续且不可导。</t>
+  </si>
+  <si>
+    <t>001：分段函数{f(x)=x,x≠0;f(x)=1,x=0}，在x=0处极限存在（值为0），但不连续（函数值为1）且不可导。</t>
+  </si>
+  <si>
+    <t>010：NA（连续性必蕴含极限存在，无法构造连续但极限不存在的函数）。</t>
+  </si>
+  <si>
+    <t>011：函数f(x)=|x|，在x=0处连续且极限存在（值为0），但一阶导数不存在（左右导数分别为-1和1，矛盾）。</t>
+  </si>
+  <si>
+    <t>100：NA（可导必连续，连续必极限存在，无法构造可导但不连续且极限不存在的函数）。</t>
+  </si>
+  <si>
+    <t>101：NA（可导必连续，无法构造可导但不连续的函数）。</t>
+  </si>
+  <si>
+    <t>110：NA（连续必极限存在，无法构造连续但极限不存在的函数）。</t>
+  </si>
+  <si>
+    <t>111：函数f(x)=x²，在实数域内二阶可导、连续且极限处处存在（任意点极限等于函数值）。</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）+连续性（多元）</t>
+  </si>
+  <si>
+    <t>000：分段函数{f(x,y)=1,xy≠0;f(x,y)=0,xy=0}，在点(0,0)处偏导数不存在（如对x的偏导数在y=0时左右极限矛盾）、不可微且不连续（极限沿x=0和y=0路径分别为0和1，不唯一）。</t>
+  </si>
+  <si>
+    <t>001：函数f(x,y)=|x|+|y|，在点(0,0)处偏导数不存在（对x的偏导数左右极限为-1和1）、不可微，但连续（|x|+|y|→0当(x,y)→(0,0)）。</t>
+  </si>
+  <si>
+    <t>010：NA（可微性要求偏导数必存在，无法构造偏导数不存在但可微的函数）。</t>
+  </si>
+  <si>
+    <t>011：NA（可微性要求偏导数必存在，且可微必连续，无法构造偏导数不存在但可微且连续的函数）。</t>
+  </si>
+  <si>
+    <t>100：函数{f(x,y)=x²y/(x⁴+y²),(x,y)≠(0,0);f(x,y)=0,(x,y)=(0,0)}，在点(0,0)处偏导数fₓ(0,0)=0、fᵧ(0,0)=0（通过定义计算），但沿路径y=kx²趋近时极限为k/(1+k²)≠0，故不连续且不可微（全微分误差项极限不为0）。</t>
+  </si>
+  <si>
+    <t>101：函数f(x,y)=√(|xy|)，在点(0,0)处偏导数fₓ(0,0)=0、fᵧ(0,0)=0（定义计算），连续（|√(|xy|)|≤√(x²+y²)/√2→0），但不可微（全微分误差项Δf-0-0=√(|ΔxΔy|)，与ρ=√(Δx²+Δy²)的比值在Δx=Δy时为1/√2≠0）。</t>
+  </si>
+  <si>
+    <t>110：NA（可微性必蕴含连续性，无法构造可微但不连续的函数）。</t>
+  </si>
+  <si>
+    <t>111：函数f(x,y)=x²+y²，在任意点处偏导数fₓ=2x、fᵧ=2y存在且连续，全微分df=2xΔx+2yΔy，余项(Δx)²+(Δy)²=o(ρ)，故可微且连续（多项式函数处处连续）。</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>000：函数f(x,y)=|x|+|y|，在点(0,0)处对x的偏导数lim(Δx→0)|Δx|/Δx不存在（左右极限为-1和1），故偏导数不存在、不可微，且二阶偏导无定义（自然不连续）。</t>
+  </si>
+  <si>
+    <t>001：NA（偏导数不存在时，无法存在二阶偏导数，更无法连续）。</t>
+  </si>
+  <si>
+    <t>010：NA（可微性要求偏导数必存在，偏导数不存在时不可微）。</t>
+  </si>
+  <si>
+    <t>011：NA（偏导数不存在时，无法满足可微性和二阶偏导连续）。</t>
+  </si>
+  <si>
+    <t>100：函数{f(x,y)=x²y/(x⁴+y²),(x,y)≠(0,0);f(x,y)=0,(x,y)=(0,0)}，在点(0,0)处偏导数fₓ(0,0)=0、fᵧ(0,0)=0（定义计算），但沿路径y=kx²趋近时极限不唯一，故不可微；且一阶偏导在(0,0)附近不连续（如fₓ(x,kx²)随k变化），导致二阶偏导不连续。</t>
+  </si>
+  <si>
+    <t>101：NA（若二阶偏导连续，则一阶偏导必连续，而一阶偏导连续是可微的充分条件，与“不可微”矛盾）。</t>
+  </si>
+  <si>
+    <t>110：函数f(x,y)=x²y²sin(1/(x²+y²))（(x,y)≠(0,0)时），f(0,0)=0。在(0,0)处偏导数存在且可微（全微分误差项满足o(ρ)），但二阶偏导在原点附近因sin(1/(x²+y²))的振荡性不连续。</t>
+  </si>
+  <si>
+    <t>111：函数f(x,y)=x³+y³，在任意点处偏导数fₓ=3x²、fᵧ=3y²存在且连续，可微；二阶偏导数fₓₓ=6x、fᵧᵧ=6y、fₓᵧ=fᵧₓ=0均连续，满足所有条件。</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+连续性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>000：函数f(x,y)=|x|+|y|，在点(0,0)处对x的偏导数lim(Δx→0)|Δx|/Δx不存在（左右极限为-1和1），故偏导数不存在；沿x=0和y=0路径趋近原点时函数值分别为|y|和|x|，极限为0，但沿y=x路径时f(x,x)=2|x|→0，整体连续？不，此处错误：|x|+|y|在原点是连续的，但偏导数不存在。修正：分段函数{f(x,y)=1,x²+y²≥1;f(x,y)=0,x²+y²&lt;1}，在原点处不连续（边界突变），偏导数不存在（不连续导致），二阶偏导无定义（不连续且偏导数不存在）。</t>
+  </si>
+  <si>
+    <t>001：NA（偏导数不存在时，二阶偏导数无定义，无法满足“二阶偏导连续”）。</t>
+  </si>
+  <si>
+    <t>010：函数f(x,y)=|x|+|y|，在点(0,0)处连续（|x|+|y|→0当(x,y)→(0,0)），但对x的偏导数lim(Δx→0)(|Δx|)/Δx不存在（左右极限矛盾），故偏导数不存在；二阶偏导数无定义，自然不连续。</t>
+  </si>
+  <si>
+    <t>011：NA（偏导数不存在时，无法满足“可微性”或“二阶偏导连续”）。</t>
+  </si>
+  <si>
+    <t>100：函数{f(x,y)=x²y/(x⁴+y²),(x,y)≠(0,0);f(x,y)=0,(x,y)=(0,0)}，在点(0,0)处偏导数fₓ(0,0)=0、fᵧ(0,0)=0（定义计算），但沿路径y=kx²趋近时极限为k/(1+k²)≠0，故不连续；一阶偏导在(0,0)附近不连续（如fₓ(x,kx²)=2k/(1+k²)随k变化），导致二阶偏导不连续。</t>
+  </si>
+  <si>
+    <t>101：NA（若二阶偏导连续，则一阶偏导必连续，而一阶偏导连续→函数可微→函数必连续，与“不连续”矛盾）。</t>
+  </si>
+  <si>
+    <t>110：函数f(x,y)=x²y²sin(1/(x²+y²))（(x,y)≠(0,0)时），f(0,0)=0。在(0,0)处偏导数存在（fₓ(0,0)=0，fᵧ(0,0)=0），且连续（|x²y²sin(1/(x²+y²))|≤x²y²→0），但二阶偏导数在原点附近因sin(1/(x²+y²))的振荡性不连续（如fₓₓ在(ε,0)处为2sin(1/ε²)，极限不存在）。</t>
+  </si>
+  <si>
+    <t>111：函数f(x,y)=x³+y³，在任意点处偏导数fₓ=3x²、fᵧ=3y²存在且连续，故连续；二阶偏导数fₓₓ=6x、fᵧᵧ=6y、fₓᵧ=fᵧₓ=0均连续，满足所有条件。</t>
+  </si>
+  <si>
+    <t>可微性（多元）+连续性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>000：分段函数{f(x,y)=1,x²+y²≥1;f(x,y)=0,x²+y²&lt;1}，在原点处不连续（边界突变），故不可微，二阶偏导无定义（不连续且偏导数不存在）。</t>
+  </si>
+  <si>
+    <t>001：NA（连续性不成立时，函数在该点无定义或极限不存在，无法满足二阶偏导连续）。</t>
+  </si>
+  <si>
+    <t>010：函数f(x,y)=|x|+|y|，在原点处连续（|x|+|y|→0），但不可微（偏导数不存在），二阶偏导无定义（偏导数不存在），故二阶偏导不连续。</t>
+  </si>
+  <si>
+    <t>011：NA（可微性不成立时，若二阶偏导连续则一阶偏导必连续，而一阶偏导连续→可微，矛盾）。</t>
+  </si>
+  <si>
+    <t>100：NA（可微性必蕴含连续性，无法构造可微但不连续的函数）。</t>
+  </si>
+  <si>
+    <t>101：NA（可微性必蕴含连续性，与“连续性不成立”矛盾）。</t>
+  </si>
+  <si>
+    <t>110：函数f(x,y)=x²y²sin(1/(x²+y²))（(x,y)≠(0,0)时f=0），在原点处可微（全微分误差项满足o(ρ)）且连续，但二阶偏导数因sin(1/(x²+y²))振荡而不连续（如fₓₓ在(ε,0)处极限不存在）。</t>
+  </si>
+  <si>
+    <t>111：函数f(x,y)=x³+y³，在任意点处可微（偏导数连续）、连续，且二阶偏导数fₓₓ=6x、fᵧᵧ=6y、fₓᵧ=0均连续，满足所有条件。</t>
+  </si>
+  <si>
+    <t>特例法大杀器-一元运算### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>性质排序参考20250616</t>
+  </si>
+  <si>
+    <t>相反数（-f(x)=g(x)或-f(x,y)=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（不可导）,g(x)=-|x|（不可导）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（偏导数不存在）,g(x,y)=-|x|-|y|（偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段函数{1,x≥0;-1,x&lt;0}（不连续）,g(x)=分段函数{-1,x≥0;1,x&lt;0}（不连续）###-###&gt;&gt;&gt;f(x,y)=√(|xy|)（在(0,0)处不可微）,g(x,y)=-√(|xy|)（在(0,0)处不可微）###-###&gt;&gt;&gt;f(x)=分段函数{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段函数{-sin(1/x),x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段函数{1,xy≠0;0,xy=0}（在(0,0)处不连续）,g(x,y)=分段函数{-1,xy≠0;0,xy=0}（在(0,0)处不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=-x-1（非周期函数）###-###&gt;&gt;&gt;f(x)=分段函数{1,x为有理数；0,x为无理数}（不可积）,g(x)=分段函数{-1,x为有理数；0,x为无理数}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)处二阶偏导不连续）,g(x,y)=-x²y/(x⁴+y²)（在(0,0)处二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²+1（非奇函数）,g(x)=-x²-1（非奇函数）###-###性质K情形1：f(x)不满足性质K，g(x)满足性质K###-###性质L情形1：f(x)不满足性质L，g(x)满足性质L###-###性质M情形1：f(x)不满足性质M，g(x)满足性质M###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（f不可导时g=-f必不可导）###-###&gt;&gt;&gt;NA（f偏导数不存在时g=-f必不存在）###-###&gt;&gt;&gt;NA（因f不连续时g=-f必不连续，故无法构造此情形。）###-###&gt;&gt;&gt;NA（f不可微时g=-f必不可微）###-###&gt;&gt;&gt;f(x)=分段函数{1,x≥0;0,x&lt;0}（x→0极限不存在）,g(x)=分段函数{-1,x≥0;0,x&lt;0}（x→0极限不存在）###-###&gt;&gt;&gt;NA（f不连续时g=-f必不连续）###-###&gt;&gt;&gt;f(x)=x（非周期）,g(x)=-x（非周期）###-###&gt;&gt;&gt;NA（若f(x)不可积，则其相反数g(x)=-f(x)的不连续点分布与f完全一致，仍不满足黎曼可积的“几乎处处连续”条件，故无法构造g可积的例子）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（二阶偏导不连续）,g(x,y)=-x²y/(x⁴+y²)（二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²（非奇函数）,g(x)=-x²（非奇函数）###-###性质K情形2：f(x)满足性质K，g(x)不满足性质K###-###性质L情形2：f(x)满足性质L，g(x)不满足性质L###-###性质M情形2：f(x)满足性质M，g(x)不满足性质M###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;NA（f可导时g=-f必可导）###-###&gt;&gt;&gt;NA（f偏导数存在时g=-f必存在）###-###&gt;&gt;&gt;NA（f连续时g=-f必连续）###-###&gt;&gt;&gt;NA（f可微时g=-f必可微）###-###&gt;&gt;&gt;NA（f极限存在时g=-f必极限存在）###-###&gt;&gt;&gt;NA（f连续时g=-f必连续）###-###&gt;&gt;&gt;NA（f周期函数时g=-f必周期函数）###-###&gt;&gt;&gt;NA（f可积时g=-f必可积）###-###&gt;&gt;&gt;NA（f二阶偏导连续时g=-f必连续）###-###&gt;&gt;&gt;NA（因奇函数的相反数必为奇函数，故不存在f为奇函数而g非奇函数的情形）性质J情形3：f(x)满足性质J，g(x)满足性质J###-###性质K情形3：f(x)满足性质K，g(x)满足性质K###-###性质L情形3：f(x)满足性质L，g(x)满足性质L###-###性质M情形3：f(x)满足性质M，g(x)满足性质M###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;f(x)=x²（二阶可导）,g(x)=-x²（二阶可导）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x,y)=-x²-y²（偏导数存在）###-###&gt;&gt;&gt;f(x)=x（连续）,g(x)=-x（连续）###-###&gt;&gt;&gt;f(x,y)=x²+y²（可微）,g(x,y)=-x²-y²（可微）###-###&gt;&gt;&gt;f(x)=x（x→0极限存在）,g(x)=-x（x→0极限存在）###-###&gt;&gt;&gt;f(x,y)=x+y（连续）,g(x,y)=-x-y（连续）###-###&gt;&gt;&gt;f(x)=sinx（周期2π）,g(x)=-sinx（周期2π）###-###&gt;&gt;&gt;f(x)=1（在[0,1]可积，积分值1）,g(x)=-1（在[0,1]可积，积分值-1）###-###&gt;&gt;&gt;f(x,y)=x³+y³（二阶偏导连续）,g(x,y)=-x³-y³（二阶偏导连续）###-###===性质K讨论===###-###===性质L讨论===###-###===性质M讨论===###-######-</t>
+  </si>
+  <si>
+    <t>绝对值（|f(x)|=g(x)或|f(x,y)|=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=||x||=|x|（在x=0不可导）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=||x|+|y||=|x|+|y|（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;NA（若f(x)在x=0不连续，g(x)=|f(x)|连续，如f(x)=分段{1,x≥0;-1,x&lt;0}，g(x)=1连续）###-###&gt;&gt;&gt;f(x,y)=√(|xy|)（在(0,0)不可微）,g(x,y)=|√(|xy|)|=√(|xy|)（在(0,0)不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{|sin(1/x)|,x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;NA（若f(x,y)在(0,0)不连续，g(x,y)=|f(x,y)|连续，如f(x,y)=分段{1,xy≠0;0,xy=0}，g(x,y)=1连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期）,g(x)=|x+1|（非周期）###-###&gt;&gt;&gt;NA（若f(x)不可积，g(x)=|f(x)|可积，如f(x)=狄利克雷函数，g(x)=1可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=|x²y/(x⁴+y²)|（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=|x|（偶函数，非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=|x+1|（非偶函数）###-###&gt;&gt;&gt;f(x)=分段{x,x≥0;2x,x&lt;0}（在x=0无切线）,g(x)=分段{|x|,x≥0;|2x|,x&lt;0}（在x=0无切线）###-###&gt;&gt;&gt;f(x)=1/x（x&gt;0时无穷积分发散）,g(x)=|1/x|=1/x（无穷积分发散）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)不可导，g(x)=|f(x)|在同点仍不可导，如f(x)=|x|，g(x)=|x|不可导）###-###&gt;&gt;&gt;NA（若f(x,y)偏导数不存在，g(x,y)=|f(x,y)|偏导数仍不存在，如f(x,y)=|x|，g(x,y)=|x|）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;-1,x&lt;0}（在x=0不连续）,g(x)=1（在x=0连续）###-###&gt;&gt;&gt;NA（若f(x,y)不可微，g(x,y)=|f(x,y)|仍不可微，如f(x,y)=|x|，g(x,y)=|x|）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（x→0极限不存在）,g(x)=1（x→0极限存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=1（在(0,0)连续）###-###&gt;&gt;&gt;NA（非周期函数取绝对值仍为非周期函数，无法使g为周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=1（可积）###-###&gt;&gt;&gt;f(x,y)=分段{x²y/(x⁴+y²),x≠0;0,x=0}（在(0,0)二阶偏导不连续）,g(x,y)=0（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=|x|（偶函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=1（偶函数）###-###&gt;&gt;&gt;NA（若f(x)在x=0无切线，g(x)=|f(x)|仍无切线，如f(x)=|x|，g(x)=|x|）###-###&gt;&gt;&gt;f(x)=分段{e^x,x≥0;-e^x,x&lt;0}（无穷积分发散）,g(x)=e^x（无穷积分收敛）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x=0可导）,g(x)=|x|（在x=0不可导）###-###&gt;&gt;&gt;f(x,y)=x（在x=0偏导数存在）,g(x,y)=|x|（在x=0偏导数不存在）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=|f(x)|必连续，因|f(x)|-|f(x0)|≤|f(x)-f(x0)|→0）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=|x|（在x=0不可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g(x)=|f(x)|极限必存在，因||f(x)|-|A||≤|f(x)-A|→0）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x,y)=|f(x,y)|必连续，同上理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g(x)=|f(x)|周期≤T，如f(x)=sinx周期2π，g(x)=|sinx|周期π，不满足原周期性质）###-###&gt;&gt;&gt;NA（黎曼可积函数的绝对值必可积，因振幅ω(|f|)≤ω(f)）###-###&gt;&gt;&gt;f(x,y)=x³（二阶偏导连续）,g(x,y)=|x³|（在x=0二阶偏导不连续，因f''(x)=6|x|在x=0左导-6，右导6，不连续）###-###&gt;&gt;&gt;f(x)=0（既是奇函数又是偶函数）,g(x)=0（偶函数，非严格奇函数，因奇函数要求f(-x)=-f(x)，0满足但通常视为特殊情况，此处g(x)=0是偶函数，故f具奇函数性质而g不具）###-###&gt;&gt;&gt;NA（若f(x)是偶函数，则g(x)=|f(x)|必为偶函数，因|f(-x)|=|f(x)|）###-###&gt;&gt;&gt;f(x)=x（在x=0切线为y=x）,g(x)=|x|（在x=0无切线，左右导数不等）###-###&gt;&gt;&gt;f(x)=sinx/x（无穷积分收敛）,g(x)=|sinx/x|（无穷积分发散，因∫|sinx/x|dx≥∫sin²x/xdx，后者发散）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;f(x)=x²（二阶可导）,g(x)=x²（二阶可导）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x,y)=x²+y²（偏导数存在）###-###&gt;&gt;&gt;f(x)=x（连续）,g(x)=|x|（连续）###-###&gt;&gt;&gt;f(x,y)=x²+y²（可微）,g(x,y)=x²+y²（可微）###-###&gt;&gt;&gt;f(x)=x（x→0极限存在）,g(x)=|x|（x→0极限存在）###-###&gt;&gt;&gt;f(x,y)=x+y（连续）,g(x,y)=|x+y|（连续）###-###&gt;&gt;&gt;NA（若f(x)周期T，g(x)=|f(x)|周期改变，如f(x)=cosx周期2π，g(x)=|cosx|周期π，不满足原周期定义）###-###&gt;&gt;&gt;f(x)=1（在[0,1]可积）,g(x)=1（在[0,1]可积）###-###&gt;&gt;&gt;f(x,y)=x⁴+y⁴（二阶偏导连续）,g(x,y)=x⁴+y⁴（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=0（奇函数）,g(x)=0（奇函数，因0=-0）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=x²（偶函数）###-###&gt;&gt;&gt;f(x)=x²（在x=0切线为y=0）,g(x)=x²（在x=0切线为y=0）###-###&gt;&gt;&gt;f(x)=e^(-x²)（无穷积分收敛）,g(x)=e^(-x²)（无穷积分收敛）###-</t>
+  </si>
+  <si>
+    <t>取倒数（1/f(x)=g(x)或1/f(x,y)=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=1/|x|（在x=0不可导，导数为无穷大）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=1/(|x|+|y|)（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{1,x≥0;无定义，x&lt;0}（在x=0不连续且无定义）###-###&gt;&gt;&gt;f(x,y)=分段{x²+y²,(x,y)≠(0,0);0,(x,y)=(0,0)}（在(0,0)不可微）,g(x,y)=分段{1/(x²+y²),(x,y)≠(0,0);无定义，(x,y)=(0,0)}（在(0,0)不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{1/sin(1/x),x≠0;无定义，x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;无定义，xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=1/(x+1)（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;无定义，x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=(x⁴+y²)/(x²y)（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²+1（非奇函数）,g(x)=1/(x²+1)（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=1/(x+1)（非偶函数）###-###&gt;&gt;&gt;f(x)=|x|（在x=0无切线）,g(x)=1/|x|（在x=0无定义，无切线）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=x（无穷积分∫xdx从1到∞发散）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)在x0不可导且f(x0)≠0，则g(x)=1/f(x)在x0必不可导，因导数公式含f²分母）###-###&gt;&gt;&gt;NA（若f(x,y)在某点偏导数不存在且f≠0，则g=1/f偏导数必不存在，偏导公式依赖f的导数）###-###&gt;&gt;&gt;NA（若f(x)在x0不连续且f(x0)≠0，则g=1/f在x0必不连续，因极限不存在）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不可微且f≠0，则g=1/f不可微，因可微性要求偏导存在）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限不存在且f≠0，则g=1/f极限必不存在，极限运算不保持）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不连续且f≠0，则g=1/f必不连续，连续性依赖f的连续性）###-###&gt;&gt;&gt;NA（非周期函数取倒数仍为非周期函数，无法构造g为周期函数）###-###&gt;&gt;&gt;NA（若f(x)不可积且f≠0，则g=1/f可能仍不可积，如狄利克雷函数）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导不连续且f≠0，则g=1/f的二阶偏导必不连续，依赖f的导数连续性）###-###&gt;&gt;&gt;NA（若f(x)非奇函数且f≠0，g=1/f必非奇函数，因1/f(-x)≠-1/f(x)）###-###&gt;&gt;&gt;NA（若f(x)非偶函数且f≠0，g=1/f必非偶函数，因1/f(-x)≠1/f(x)）###-###&gt;&gt;&gt;NA（若f(x)在x0无切线且f(x0)≠0，则g=1/f在x0无定义或导数不存在，无切线）###-###&gt;&gt;&gt;f(x)=e^(-x²)（无穷积分∫e^(-x²)dx收敛）,g(x)=e^(x²)（无穷积分∫e^(x²)dx发散，因被积函数指数增长）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x0=0可导）,g(x)=1/x（在x0=0不可导，分母为0）###-###&gt;&gt;&gt;f(x,y)=x（偏导数存在）,g(x,y)=1/x（在x=0偏导数不存在，分母为0）###-###&gt;&gt;&gt;NA（若f(x)在区间连续且f≠0，则g=1/f必连续，连续函数倒数在非零点连续）###-###&gt;&gt;&gt;f(x,y)=x²+y²+1（可微）,g(x,y)=1/(x²+y²+1)（可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在且f≠0，则g=1/f极限必存在，为1/limf(x)）###-###&gt;&gt;&gt;NA（若f(x,y)连续且f≠0，则g=1/f必连续，连续性定理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g=1/f必周期T，因f(x+T)=f(x)⇒g(x+T)=g(x)）###-###&gt;&gt;&gt;NA（若f(x)可积且f≠0，则g=1/f可能不可积，如f(x)=x在[-1,1]可积，g=1/x不可积）###-###&gt;&gt;&gt;f(x,y)=x²+y²+1（二阶偏导连续）,g(x,y)=1/(x²+y²+1)（二阶偏导连续）###-###&gt;&gt;&gt;NA（若f(x)是奇函数且f≠0，则g=1/f必为奇函数，因1/f(-x)=-1/f(x)）###-###&gt;&gt;&gt;NA（若f(x)是偶函数且f≠0，则g=1/f必为偶函数，因1/f(-x)=1/f(x)）###-###&gt;&gt;&gt;f(x)=x+1（在x=0切线存在）,g(x)=1/(x+1)（在x=0切线存在，导数为-1）###-###&gt;&gt;&gt;f(x)=1/x²（无穷积分∫1/x²dx收敛）,g(x)=x²（无穷积分∫x²dx发散，因被积函数趋于无穷）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;NA（若f(x)可导且f≠0，则g=1/f必可导，导数为-f’/f²，故无法构造f可导但g不可导的11情况）###-###&gt;&gt;&gt;NA（若f(x,y)偏导数存在且f≠0，则g=1/f偏导数必存在，偏导公式保证）###-###&gt;&gt;&gt;NA（若f(x)连续且f≠0，则g=1/f必连续，连续函数倒数性质）###-###&gt;&gt;&gt;NA（若f(x,y)可微且f≠0，则g=1/f必可微，复合函数可微性）###-###&gt;&gt;&gt;NA（若f(x)极限存在且f≠0，则g=1/f极限必存在，极限运算性质）###-###&gt;&gt;&gt;NA（若f(x,y)连续且f≠0，则g=1/f必连续，同连续性逻辑）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g=1/f必周期T，周期函数性质）###-###&gt;&gt;&gt;NA（若f(x)可积且f≠0，则g=1/f可能不可积，如f(x)=x在[-1,1]可积，g=1/x不可积）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导连续且f≠0，则g=1/f二阶偏导必连续，导数连续性传递）###-###&gt;&gt;&gt;NA（若f(x)是奇函数且f≠0，则g=1/f必为奇函数，奇偶性保持）###-###&gt;&gt;&gt;NA（若f(x)是偶函数且f≠0，则g=1/f必为偶函数，奇偶性保持）###-###&gt;&gt;&gt;NA（若f(x)在x0切线存在且f≠0，则g=1/f在x0切线存在，导数公式保证）###-###&gt;&gt;&gt;NA（若f(x)反常积分收敛且f≠0，则g=1/f反常积分必发散，因f→0时1/f→∞或f→c≠0时1/f不趋于0）###-</t>
+  </si>
+  <si>
+    <t>平方（f(x)²=g(x)或f(x,y)²=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=分段{x,x≠0;1,x=0}（在x=0不可导）,g(x)=分段{x²,x≠0;1,x=0}（在x=0不可导）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=(|x|+|y|)²（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）###-###&gt;&gt;&gt;f(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）,g(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{sin²(1/x),x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=(x+1)²（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=[x²y/(x⁴+y²)]²（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x+1（非奇函数）,g(x)=(x+1)²（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=(x+1)²（非偶函数）###-###&gt;&gt;&gt;f(x)=分段{x,x≥0;2x,x&lt;0}（在x=0无切线）,g(x)=分段{x²,x≥0;4x²,x&lt;0}（在x=0无切线）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)在x0处不可导且不连续，则g(x)=f(x)²在x0处因函数值跳跃而不连续，必然不可导，故无法构造此情形）###-###&gt;&gt;&gt;f(x,y)=|x|（在(0,0)处对x的偏导数不存在）,g(x,y)=|x|²=x²（在(0,0)处对x的偏导数存在，为0）###-###&gt;&gt;&gt;NA（若f(x)在x0处不连续，则g(x)=f(x)²在x0处的左右极限必为f(x)左右极限的平方，若f(x)左右极限不等或与函数值不等，g(x)必不连续，故无法构造f不连续但g连续的情形）###-###&gt;&gt;&gt;f(x,y)=|x|（在(0,0)处不可微，因对x的偏导数不存在）,g(x,y)=|x|²=x²（在(0,0)处可微，因偏导数存在且满足全微分条件）###-###&gt;&gt;&gt;f(x)=分段{1,x&gt;0;-1,x&lt;0;0,x=0}（x→0时左极限为-1，右极限为1，极限不存在，不满足性质E）,g(x)=f(x)²=分段{1,x≠0;0,x=0}（x→0时左右极限均为1，极限存在，满足性质E）###-###&gt;&gt;&gt;f(x,y)=分段{2,xy≠0;0,xy=0}（在(0,0)处不连续，不满足性质F），g(x,y)=4（在(0,0)处连续，满足性质F）###-###&gt;&gt;&gt;f(x)=|sin(x)|,g(x)=sin(x)²###-###&gt;&gt;&gt;f(x)=分段{1,x∈Q;-1,x∉Q}（不可积）,g(x)=分段{1,x∈Q;1,x∉Q}（可积，因g几乎处处为1，满足黎曼可积的“几乎处处连续”条件）###-###&gt;&gt;&gt;NA（f(x,y)在(0,0)处二阶偏导不连续，其平方后g(x,y)=[x²y/(x⁴+y²)]²在该点附近沿不同路径（如y=kx²）极限值随k变化而不同，导致g(x,y)在(0,0)处不连续，进而二阶偏导必不连续，无法满足性质I）###-###&gt;&gt;&gt;NA（若f(x)非奇函数，g(x)=f²(x)可能为偶函数，如f(x)=x+1非奇函数，g(x)=(x+1)²非奇函数，无法使g为奇函数）###-###&gt;&gt;&gt;f(x)=x（非偶函数，不满足性质K），g(x)=x²（偶函数，满足性质K）###-###&gt;&gt;&gt;f(x)=|x|（在x=0处无切线，不满足性质L），g(x)=x²（在x=0处切线为y=0，满足性质L）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x=0可导）,g(x)=x²（在x=0可导）###-###&gt;&gt;&gt;f(x,y)=x（偏导数存在）,g(x,y)=x²（偏导数存在）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=f²(x)必连续）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=x²（可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g(x)=f²(x)极限必存在）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x,y)=f²(x,y)必连续）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g(x)=f²(x)周期≤T，如f(x)=sinx周期2π，g(x)=sin²x也有周期2π）###-###&gt;&gt;&gt;NA（若f(x)可积，则g(x)=f²(x)必可积）###-###&gt;&gt;&gt;f(x,y)=x³（二阶偏导连续）,g(x,y)=x⁶（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=x²（偶函数）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=x⁴（偶函数）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=x²（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）,g(x)=1/x⁴（无穷积分∫1/x⁴dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;f(x)=x²（二阶可导）,g(x)=x⁴（二阶可导）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x,y)=(x²+y²)²（偏导数存在）###-###&gt;&gt;&gt;f(x)=x（连续）,g(x)=x²（连续）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=x²（可微）###-###&gt;&gt;&gt;f(x)=x（极限存在）,g(x)=x²（极限存在）###-###&gt;&gt;&gt;f(x,y)=x+y（连续）,g(x,y)=(x+y)²（连续）###-###&gt;&gt;&gt;f(x)=sinx周期2π，g(x)=sin²x也有周期2π###-###&gt;&gt;&gt;f(x)=1（可积）,g(x)=1（可积）###-###&gt;&gt;&gt;f(x,y)=x⁴+y⁴（二阶偏导连续）,g(x,y)=(x⁴+y⁴)²（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=x²（偶函数）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=x⁴（偶函数）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=x²（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=e^(-x)（无穷积分∫e^(-x)dx从0到∞收敛）,g(x)=e^(-2x)（无穷积分∫e^(-2x)dx从0到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>立方（f(x)³=g(x)或f(x,y)³=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=|x|³（在x=0不可导，因左右导数均为0但f'''(0)不存在）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=(|x|+|y|)³（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）###-###&gt;&gt;&gt;f(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）,g(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{sin³(1/x),x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=(x+1)³（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=[x²y/(x⁴+y²)]³（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x+1（非奇函数）,g(x)=(x+1)³（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=(x+1)³（非偶函数）###-###&gt;&gt;&gt;f(x)=分段{x,x≥0;2x,x&lt;0}（在x=0无切线）,g(x)=分段{x³,x≥0;8x³,x&lt;0}（在x=0无切线）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=1/x³（无穷积分∫1/x³dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)在x0不可导，则g(x)=f³(x)在x0仍不可导，如f(x)=|x|，g(x)=|x|³不可导）###-###&gt;&gt;&gt;NA（若f(x,y)在某点偏导数不存在，则g(x)=f³(x,y)偏导数仍不存在，如f(x,y)=|x|+|y|）###-###&gt;&gt;&gt;NA（若f(x)在x0不连续，则g(x)=f³(x)在x0必不连续，因连续性要求极限等于函数值）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不可微，则g(x)=f³(x,y)不可微，因可微性要求偏导存在且满足全微分条件）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限不存在，则g(x)=f³(x)极限必不存在，因极限运算性质）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不连续，则g(x)=f³(x,y)必不连续，同连续性逻辑）###-###&gt;&gt;&gt;NA（非周期函数立方仍为非周期函数，无法使g为周期函数）###-###&gt;&gt;&gt;NA（若f(x)不可积，则g(x)=f³(x)仍不可积，如狄利克雷函数）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导不连续，则g(x)=f³(x,y)的二阶偏导依赖f的导数连续性，必不连续）###-###&gt;&gt;&gt;NA（若f(x)非奇函数，则g(x)=f³(x)仍非奇函数，如f(x)=x+1）###-###&gt;&gt;&gt;NA（若f(x)非偶函数，则g(x)=f³(x)仍非偶函数，如f(x)=x+1）###-###&gt;&gt;&gt;NA（若f(x)在x0无切线，则g(x)=f³(x)在x0无定义或导数不存在，无切线）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=1/x³（无穷积分∫1/x³dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x=0可导）,g(x)=x³（在x=0可导）###-###&gt;&gt;&gt;f(x,y)=x（偏导数存在）,g(x,y)=x³（偏导数存在）###-###&gt;&gt;&gt;NA（若f(x)在区间连续，则g(x)=f³(x)必连续，因连续函数的立方仍连续）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=x³（可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g(x)=f³(x)极限必存在，为[limf(x)]³）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x)=f³(x,y)必连续，同连续性定理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g(x)=f³(x)必周期T，因f(x+T)=f(x)⇒g(x+T)=g(x)）###-###&gt;&gt;&gt;NA（若f(x)可积，则g(x)=f³(x)必可积，因可积函数的立方仍可积）###-###&gt;&gt;&gt;f(x,y)=x³（二阶偏导连续）,g(x,y)=x⁹（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=x³（奇函数）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=x⁶（偶函数）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=x³（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）,g(x)=1/x⁶（无穷积分∫1/x⁶dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;f(x)=x²（二阶可导）,g(x)=x⁶（二阶可导）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x,y)=(x²+y²)³（偏导数存在）###-###&gt;&gt;&gt;f(x)=x（连续）,g(x)=x³（连续）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=x³（可微）###-###&gt;&gt;&gt;f(x)=x（极限存在）,g(x)=x³（极限存在）###-###&gt;&gt;&gt;f(x,y)=x+y（连续）,g(x,y)=(x+y)³（连续）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g(x)=f³(x)周期T，但g(x)=sin³x周期2π与f(x)=sinx周期2π相同，符合原周期定义）###-###&gt;&gt;&gt;f(x)=1（可积）,g(x)=1（可积）###-###&gt;&gt;&gt;f(x,y)=x⁴+y⁴（二阶偏导连续）,g(x,y)=(x⁴+y⁴)³（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=x³（奇函数）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=x⁶（偶函数）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=x³（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=e^(-x)（无穷积分∫e^(-x)dx从0到∞收敛）,g(x)=e^(-3x)（无穷积分∫e^(-3x)dx从0到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>平方根（sqrt(f(x))=g(x)或sqrt(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=sqrt(|x|)（在x=0不可导，导数为无穷大）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=sqrt(|x|+|y|)（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）###-###&gt;&gt;&gt;f(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）,g(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）###-###&gt;&gt;&gt;f(x)=分段{sin²(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{|sin(1/x)|,x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x²+1（非周期函数）,g(x)=sqrt(x²+1)（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y²/(x⁴+y⁴)（在(0,0)二阶偏导不连续）,g(x,y)=|xy|/sqrt(x⁴+y⁴)（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=|x|（偶函数）###-###&gt;&gt;&gt;f(x)=x²+1（非奇函数）,g(x)=sqrt(x²+1)（非奇函数）###-###&gt;&gt;&gt;f(x)=分段{x²,x≥0;2x²,x&lt;0}（在x=0无切线）,g(x)=分段{|x|,x≥0;|x|sqrt(2),x&lt;0}（在x=0无切线）###-###&gt;&gt;&gt;f(x)=1/x⁴（无穷积分∫1/x⁴dx从1到∞收敛）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)在x0不可导且f(x0)&gt;0，则g(x)=sqrt(f(x))在x0可能仍不可导，如f(x)=|x|，g(x)=sqrt(|x|)不可导）###-###&gt;&gt;&gt;NA（若f(x,y)在某点偏导数不存在且f&gt;0，则g=sqrt(f)偏导数仍不存在，如f(x,y)=|x|+|y|）###-###&gt;&gt;&gt;NA（若f(x)在x0不连续且f(x0)≥0，则g=sqrt(f)在x0必不连续，因连续性要求极限等于函数值）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不可微且f&gt;0，则g=sqrt(f)不可微，因可微性要求偏导存在且满足全微分条件）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限不存在且f(x)≥0，则g=sqrt(f)极限必不存在，因极限运算性质）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不连续且f≥0，则g=sqrt(f)必不连续，同连续性逻辑）###-###&gt;&gt;&gt;NA（非周期函数的平方根仍为非周期函数，无法使g为周期函数）###-###&gt;&gt;&gt;NA（若f(x)不可积且f(x)≥0，则g=sqrt(f)可能仍不可积，如狄利克雷函数）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导不连续且f&gt;0，则g=sqrt(f)的二阶偏导依赖f的导数连续性，必不连续）###-###&gt;&gt;&gt;NA（若f(x)非偶函数且f(x)≥0，则g=sqrt(f)可能仍非偶函数，如f(x)=x²+1）###-###&gt;&gt;&gt;NA（若f(x)非奇函数且f(x)≥0，则g=sqrt(f)可能仍非奇函数，如f(x)=x²+1）###-###&gt;&gt;&gt;NA（若f(x)在x0无切线且f(x0)&gt;0，则g=sqrt(f)在x0无定义或导数不存在，无切线）###-###&gt;&gt;&gt;f(x)=1/x⁴（无穷积分∫1/x⁴dx从1到∞收敛）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x²（在x=0可导）,g(x)=|x|（在x=0不可导）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x)=sqrt(x²+y²)（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;NA（若f(x)在区间连续且f(x)≥0，则g=sqrt(f)必连续，因连续函数的平方根仍连续）###-###&gt;&gt;&gt;f(x,y)=x²+y²（可微）,g(x)=sqrt(x²+y²)（在(0,0)不可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在且f(x)≥0，则g=sqrt(f)极限必存在，为sqrt(limf(x))）###-###&gt;&gt;&gt;NA（若f(x,y)连续且f(x,y)≥0，则g=sqrt(f)必连续，同连续性定理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g=sqrt(f)周期≤T，如f(x)=sin²x周期π，g(x)=|sinx|周期π）###-###&gt;&gt;&gt;NA（若f(x)可积且f(x)≥0，则g=sqrt(f)必可积，因可积函数的平方根仍可积）###-###&gt;&gt;&gt;f(x,y)=x⁴+y⁴（二阶偏导连续）,g(x)=sqrt(x⁴+y⁴)（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=|x|（偶函数）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=|x|（偶函数）###-###&gt;&gt;&gt;f(x)=x²（在x=0切线存在）,g(x)=|x|（在x=0无切线）###-###&gt;&gt;&gt;f(x)=1/x⁴（无穷积分∫1/x⁴dx从1到∞收敛）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;NA（若f(x)在x0二阶可导且f(x0)&gt;0，则g=sqrt(f)在x0的二阶导数可能不存在，如f(x)=x²，g=|x|二阶导数不存在）###-###&gt;&gt;&gt;NA（若f(x,y)在某点偏导数存在且f&gt;0，则g=sqrt(f)偏导数可能不存在，如f(x,y)=x²+y²）###-###&gt;&gt;&gt;NA（若f(x)在区间连续且f(x)≥0，则g=sqrt(f)必连续，因连续函数的平方根仍连续）###-###&gt;&gt;&gt;NA（若f(x,y)在某点可微且f&gt;0，则g=sqrt(f)可能不可微，如f(x,y)=x²+y²）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在且f(x)≥0，则g=sqrt(f)极限必存在，为sqrt(limf(x))）###-###&gt;&gt;&gt;NA（若f(x,y)连续且f(x,y)≥0，则g=sqrt(f)必连续，同连续性定理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g=sqrt(f)周期≤T，如f(x)=sin²x周期π，g(x)=|sinx|周期π）###-###&gt;&gt;&gt;NA（若f(x)可积且f(x)≥0，则g=sqrt(f)必可积，因可积函数的平方根仍可积）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导连续且f&gt;0，则g=sqrt(f)的二阶偏导可能不连续，如f(x,y)=x⁴+y⁴）###-###&gt;&gt;&gt;NA（若f(x)是偶函数且f(x)≥0，则g=sqrt(f)必为偶函数，因sqrt(f(-x))=sqrt(f(x))）###-###&gt;&gt;&gt;NA（若f(x)是偶函数且f(x)≥0，则g=sqrt(f)必为偶函数，同上）###-###&gt;&gt;&gt;NA（若f(x)在x0切线存在且f(x0)&gt;0，则g=sqrt(f)在x0可能无切线，如f(x)=x²）###-###&gt;&gt;&gt;NA（若f(x)为反常积分收敛且f(x)≥0，则g=sqrt(f)的反常积分可能发散，如f(x)=1/x⁴收敛，g=1/x²发散）###-</t>
+  </si>
+  <si>
+    <t>立方根（curt(f(x))=g(x)或curt(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=curt(|x|)（在x=0导数为无穷大，不可导）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=curt(|x|+|y|)（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{curt(1),x≥0;curt(0),x&lt;0}={1,x≥0;0,x&lt;0}（在x=0不连续）###-###&gt;&gt;&gt;f(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）,g(x,y)=分段{1,x≥0;0,x&lt;0}（在x=0不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{curt(sin(1/x)),x≠0;0,x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=curt(x+1)（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=curt(x²y/(x⁴+y²))（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²+1（非奇函数）,g(x)=curt(x²+1)（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=curt(x+1)（非偶函数）###-###&gt;&gt;&gt;f(x)=|x|（在x=0无切线）,g(x)=curt(|x|)（在x=0无切线，导数无穷大）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=1/x^(1/3)（无穷积分∫1/x^(1/3)dx从1到∞发散）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;NA（若f(x)在x0不可导且f(x0)≠0，g(x)=curt(f(x))在x0可能仍不可导，如f(x)=|x|，g(x)不可导）###-###&gt;&gt;&gt;NA（若f(x,y)在某点偏导数不存在且f≠0，g=curt(f)偏导数仍不存在，如f(x,y)=|x|+|y|）###-###&gt;&gt;&gt;NA（若f(x)在x0不连续，则g=curt(f)在x0必不连续，因f极限不存在则g极限也不存在）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不可微且f≠0，则g=curt(f)不可微，因偏导不存在）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限不存在，则g=curt(f)极限必不存在，因立方根保持极限不存在性）###-###&gt;&gt;&gt;NA（若f(x,y)在某点不连续，则g=curt(f)必不连续，同极限逻辑）###-###&gt;&gt;&gt;NA（非周期函数的立方根仍为非周期函数，无法使g为周期函数）###-###&gt;&gt;&gt;NA（若f(x)不可积且f(x)为有界函数，则g=curt(f)可能仍不可积，如狄利克雷函数）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导不连续且f≠0，则g=curt(f)的二阶偏导依赖f的导数连续性，必不连续）###-###&gt;&gt;&gt;NA（若f(x)非奇函数且f(x)≠-f(-x)，则g=curt(f)可能仍非奇函数，如f(x)=x²+1）###-###&gt;&gt;&gt;NA（若f(x)非偶函数且f(x)≠f(-x)，则g=curt(f)可能仍非偶函数，如f(x)=x+1）###-###&gt;&gt;&gt;NA（若f(x)在x0无切线且f(x0)≠0，则g=curt(f)在x0无定义或导数不存在，无切线）###-###&gt;&gt;&gt;f(x)=1/x³（无穷积分∫1/x³dx从1到∞收敛）,g(x)=1/x（无穷积分∫1/xdx从1到∞发散）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x²（在x=0可导）,g(x)=curt(x²)=|x|^(2/3)（在x=0导数不存在）###-###&gt;&gt;&gt;f(x,y)=x²+y²（偏导数存在）,g(x,y)=curt(x²+y²)（在(0,0)偏导数存在但二阶偏导不连续）###-###&gt;&gt;&gt;NA（若f(x)连续，则g=curt(f)必连续，因立方根函数连续）###-###&gt;&gt;&gt;f(x,y)=x³（可微）,g(x,y)=x（可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g=curt(f)极限必存在，为curt(limf(x))）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g=curt(f)必连续，同连续性定理）###-###&gt;&gt;&gt;NA（若f(x)周期T，则g=curt(f)必周期T，因f(x+T)=f(x)⇒g(x+T)=g(x)）###-###&gt;&gt;&gt;NA（若f(x)可积，则g=curt(f)必可积，因可积函数的立方根仍可积（有界时））###-###&gt;&gt;&gt;f(x,y)=x⁶+y⁶（二阶偏导连续）,g(x,y)=x²+y²（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x³（奇函数）,g(x)=x（奇函数）###-###&gt;&gt;&gt;f(x)=x⁶（偶函数）,g(x)=x²（偶函数）###-###&gt;&gt;&gt;f(x)=x³（在x=0切线存在）,g(x)=x（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=1/x⁶（无穷积分∫1/x⁶dx从1到∞收敛）,g(x)=1/x²（无穷积分∫1/x²dx从1到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;f(x)=x³（二阶可导）,g(x)=x（二阶可导）###-###&gt;&gt;&gt;f(x,y)=x³+y³（偏导数存在）,g(x,y)=x+y（偏导数存在）###-###&gt;&gt;&gt;f(x)=x（连续）,g(x)=curt(x)（连续）###-###&gt;&gt;&gt;f(x,y)=x³+y³（可微）,g(x,y)=x+y（可微）###-###&gt;&gt;&gt;f(x)=x（极限存在）,g(x)=curt(x)（极限存在）###-###&gt;&gt;&gt;f(x,y)=x+y（连续）,g(x,y)=curt(x+y)（连续）###-###&gt;&gt;&gt;f(x)=sinx（周期2π）,g(x)=curt(sinx)（周期2π）###-###&gt;&gt;&gt;f(x)=1（可积）,g(x)=1（可积）###-###&gt;&gt;&gt;f(x,y)=x⁶+y⁶（二阶偏导连续）,g(x,y)=x²+y²（二阶偏导连续）###-###&gt;&gt;&gt;f(x)=x³（奇函数）,g(x)=x（奇函数）###-###&gt;&gt;&gt;f(x)=x⁶（偶函数）,g(x)=x²（偶函数）###-###&gt;&gt;&gt;f(x)=x³（在x=0切线存在）,g(x)=x（在x=0切线存在）###-###&gt;&gt;&gt;f(x)=e^(-3x)（无穷积分∫e^(-3x)dx从0到∞收敛）,g(x)=e^(-x)（无穷积分∫e^(-x)dx从0到∞收敛）###-</t>
+  </si>
+  <si>
+    <t>向上取整（ceil(f(x))=g(x)或ceil(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=ceil(|x|)（在x=0不可导，因ceil(0)=0，ceil(|x|)在x→0+时为1，跳跃间断）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=ceil(|x|+|y|)（在(0,0)偏导数不存在，因(x,y)→(0,0)时g→1，跳跃）###-###&gt;&gt;&gt;f(x)=分段{0.5,x≥0;-0.5,x&lt;0}（在x=0处不连续，不满足性质C），g(x)=ceil(f(x))=分段{1,x≥0;0,x&lt;0}（在x=0处不连续，不满足性质C）###-###&gt;&gt;&gt;f(x,y)=分段{0.5,xy&lt;0;1.5,xy≥0}（在(0,0)不可微）,g(x,y)=分段{1,xy&lt;0;2,xy≥0}（在(0,0)不可微，跳跃）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{ceil(sin(1/x)),x≠0;0,x=0}（x→0极限不存在，因sin(1/x)在-1到1间震荡，ceil后在0到1间震荡）###-###&gt;&gt;&gt;f(x,y)=分段{1-|xy|,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+sinx（非周期函数）,g(x)=ceil(x+sinx)（非周期函数，因x递增时g无重复周期）###-###&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}（不可积，不满足性质H），g(x)=ceil(f(x))=分段{2,x∈Q;1,x∉Q}（不可积，不满足性质H）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)+1（在(0,0)处二阶偏导不连续，不满足性质I），g(x,y)=ceil(x²y/(x⁴+y²)+1)（在(0,0)处因沿y=kx²路径时f(x,y)趋近于1+k/(1+k²)，其值在(1,2)内波动，导致g(x,y)在1和2之间跳跃，二阶偏导不连续，不满足性质I）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=ceil(x)（非奇函数，如ceil(1)=1，ceil(-1)=-1，但ceil(0.5)=1，ceil(-0.5)=0，不满足f(-x)=-f(x)）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=ceil(x²)（偶函数，因ceil(x²)=ceil((-x)²)）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=ceil(x)（在x=0无切线，因x=0处左右导数不存在，跳跃）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx发散）,g(x)=ceil(1/x)（x≥1时1/x∈(0,1]，ceil(1/x)=1，无穷积分∫1dx发散）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=ceil(|x|+0.5)（在x=0可导，因|x|+0.5∈(0.5,1.5)，ceil后为1，常数函数）###-###&gt;&gt;&gt;f(x,y)=|x|（在x=0偏导数不存在）,g(x,y)=ceil(|x|+0.5)（在x=0偏导数存在，因|x|+0.5∈(0.5,1.5)，ceil后为1，偏导为0）###-###&gt;&gt;&gt;f(x)=分段{2.2,x&lt;0;2.8,x≥0}（在x=0处不连续，不满足性质C），g(x)=ceil(f(x))=2（在x=0处连续，满足性质C）###-###&gt;&gt;&gt;f(x,y)=|x|（在x=0不可微）,g(x,y)=ceil(|x|+0.5)（在x=0可微，常数函数）###-###&gt;&gt;&gt;f(x)=分段{0.5,x&lt;0;1.5,x≥0}（x→0极限不存在）,g(x)=分段{1,x&lt;0;2,x≥0}（x→0极限不存在，NA）###-###&gt;&gt;&gt;f(x,y)=分段{0.5,xy&lt;0;1.5,xy≥0}（在(0,0)不连续）,g(x,y)=分段{1,xy&lt;0;2,xy≥0}（在(0,0)不连续，NA）###-###&gt;&gt;&gt;f(x)=|0.5*sin(x)|+0.5,g(x)=1###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=1（可积，因几乎处处为1）###-###&gt;&gt;&gt;f(x,y)=x²y²/(x⁴+y⁴)（在(0,0)处二阶偏导不连续，不满足性质I），g(x,y)=ceil(x²y²/(x⁴+y⁴))=0（在全平面二阶偏导连续，满足性质I，因x²y²/(x⁴+y⁴)≤0.5恒成立，向上取整后为0）###-###&gt;&gt;&gt;f(x)=x+1（非奇函数）,g(x)=ceil(x+1)（非奇函数，如ceil(1+1)=2，ceil(-1+1)=0）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=ceil(x+1)（非偶函数，如ceil(1+1)=2，ceil(-1+1)=0）###-###&gt;&gt;&gt;f(x)=|x|（在x=0无切线）,g(x)=ceil(|x|+0.5)（在x=0有切线，常数函数导数为0）###-###&gt;&gt;&gt;f(x)=1/x+1（x≥1时1/x+1∈(1,2]，无穷积分∫(1/x+1)dx发散）,g(x)=2（无穷积分∫2dx发散）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x=0可导）,g(x)=ceil(x)（在x=0不可导，因ceil(0)=0，ceil(x)在x→0+时为1，跳跃）###-###&gt;&gt;&gt;f(x,y)=x（偏导数存在）,g(x,y)=ceil(x)（在x=0偏导数不存在，跳跃）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=ceil(f(x))在f(x)为整数处可能不连续，如f(x)=x在x=1连续，g(1)=1，g(1-ε)=1，g(1+ε)=2，不连续）###-###&gt;&gt;&gt;f(x,y)=x（可微）,g(x,y)=ceil(x)（在x=0不可微，跳跃）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g(x)=ceil(f(x))在f(x0)为整数时可能极限不存在，如f(x)=x→1，g(x)→2（x→1+）和1（x→1-））###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x,y)=ceil(f(x,y))在f=整数处不连续，如f(x,y)=x+y在(0,1)连续，g(0,1)=1，g(0,1+ε)=2）###-###&gt;&gt;&gt;NA（若f(x)周期T，g(x)=ceil(f(x))周期必为T，因f(x+T)=f(x)⇒g(x+T)=g(x)，但g在整数点间断，仍为周期函数）###-###&gt;&gt;&gt;NA（若f(x)可积，g(x)=ceil(f(x))在f(x)值域不含整数时可积，如f(x)=x+0.5在[0,1]可积，g(x)=1可积，无法构造g不可积的例子）###-###&gt;&gt;&gt;f(x,y)=x³（二阶偏导连续）,g(x,y)=ceil(x³)（在x=0二阶偏导不存在，跳跃）###-###&gt;&gt;&gt;f(x)=x（奇函数）,g(x)=ceil(x)（非奇函数，如ceil(1)=1，ceil(-1)=-1，但ceil(0.5)=1，ceil(-0.5)=0≠-1）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=ceil(x²)（偶函数，因x²=(-x)²）###-###&gt;&gt;&gt;f(x)=x（在x=0切线存在）,g(x)=ceil(x)（在x=0无切线，跳跃）###-###&gt;&gt;&gt;f(x)=e^(-x)（无穷积分收敛）,g(x)=ceil(e^(-x))=1（无穷积分发散）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;NA（若f(x)可导，则g(x)=ceil(f(x))在f(x)为整数处不可导，因跳跃，故无法构造f可导且g可导的11情况）###-###&gt;&gt;&gt;NA（若f(x,y)偏导数存在，则g(x,y)=ceil(f(x,y))在f为整数处偏导数不存在，跳跃）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=ceil(f(x))在f(x)为整数处不连续，无法同时连续）###-###&gt;&gt;&gt;NA（若f(x,y)可微，则g(x,y)=ceil(f(x,y))在f为整数处不可微，跳跃）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在，则g(x)=ceil(f(x))在f(x0)为整数时左右极限不同，极限不存在）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x,y)=ceil(f(x,y))在f为整数处不连续，无法同时连续）###-###&gt;&gt;&gt;f(x)=sinx（周期2π，满足性质G），g(x)=ceil(sinx)（周期2π，满足性质G）###-###&gt;&gt;&gt;NA（若f(x)可积，则g(x)=ceil(f(x))可能可积（如f(x)值域不含整数），但需f和g都可积，如f(x)=x+0.5在[0,1]可积，g(x)=1可积）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导连续，则g(x,y)=ceil(f(x,y))在f为整数处二阶偏导不存在，跳跃）###-###&gt;&gt;&gt;NA（若f(x)是奇函数且g(x)=ceil(f(x))，则g(-x)=ceil(-f(x))≠-ceil(f(x))，如f(x)=x，g(-x)=ceil(-x)≠-ceil(x)）###-###&gt;&gt;&gt;NA（若f(x)是偶函数，则g(x)=ceil(f(x))是偶函数，因f(-x)=f(x)⇒g(-x)=g(x)，但需f和g都为偶函数，如f(x)=x²，g(x)=ceil(x²)）###-###&gt;&gt;&gt;NA（若f(x)在x0切线存在，则g(x)=ceil(f(x))在x0无切线，因跳跃）###-###&gt;&gt;&gt;NA（若f(x)反常积分收敛，则g(x)=ceil(f(x))因f(x)→0时ceil(f(x))在0附近为0或1，积分可能发散，如f(x)=e^(-x)收敛，g(x)=1（x≥0）发散）###-</t>
+  </si>
+  <si>
+    <t>向下取整（floor(f(x))=g(x)或floor(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=floor(|x|)（在x=0不可导，跳跃间断）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=floor(|x|+|y|)（在(0,0)偏导数不存在，跳跃）###-###&gt;&gt;&gt;f(x)=分段{0.5,x&lt;0;1.5,x≥0}（在x=0不连续）,g(x)=分段{0,x&lt;0;1,x≥0}（在x=0不连续）###-###&gt;&gt;&gt;f(x,y)=分段{0.5,xy&lt;0;1.5,xy≥0}（在(0,0)不可微）,g(x,y)=分段{0,xy&lt;0;1,xy≥0}（在(0,0)不可微，跳跃）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{floor(sin(1/x)),x≠0;0,x=0}（x→0极限不存在，震荡）###-###&gt;&gt;&gt;f(x,y)=分段{1-|xy|,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=0（在(0,0)连续，因floor将(0,1)内的f值统一映射为0，消除了跳跃间断）###-###&gt;&gt;&gt;f(x)=x+sinx（非周期函数）,g(x)=floor(x+sinx)（非周期函数）###-###&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}（类狄利克雷不可积），g(x)=1（可积，因floor将f(x)恒映射为1，满足可积条件）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=0（二阶偏导连续，因floor将f(x,y)在(0,0)附近的值强制映射为0，导数恒为0）###-###&gt;&gt;&gt;f(x)=x+1（非奇函数）,g(x)=floor(x+1)（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=floor(x+1)（非偶函数）###-###&gt;&gt;&gt;f(x)=|x|（在x=0无切线）,g(x)=floor(|x|)（在x=0无切线，分段常数）###-###&gt;&gt;&gt;NA（floor函数对f(x)=1/x（x≥1）取整后恒为0，导致g(x)在积分区间内几乎处处为0，其积分必然收敛，与f(x)的发散性无关，故无法通过f发散推断g必发散）###-</t>
+  </si>
+  <si>
+    <t>01：###&gt;&gt;&gt;f(x)=|x|+0.5（在x=0处因不可导无切线，不满足性质L）,g(x)=floor(|x|+0.5)=1（在x=0处为常数函数，切线存在且为y=1，满足性质L）###-###&gt;&gt;&gt;f(x,y)=|x|+0.5（在x=0处对x的偏导数不存在，不满足性质B）,g(x,y)=floor(|x|+0.5)=1（在全平面偏导数存在，满足性质B，因常数函数偏导恒为0）###-###&gt;&gt;&gt;f(x)=分段{2.2,x&lt;0;2.8,x≥0}（在x=0处左极限2.2，右极限2.8，不连续）,g(x)=floor(f(x))=2（在x=0处左右极限均为2，连续）###-###&gt;&gt;&gt;f(x,y)=|x|+0.5（在(0,0)处因偏导数不存在-&gt;不可微，不满足性质D）,g(x,y)=floor(|x|+0.5)=0（在全平面可微，满足性质D，因常数函数必可微）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限不存在，g(x)=floor(f(x))可能仍极限不存在，如分段函数，故无需NA）###-###&gt;&gt;&gt;f(x,y)=分段{0.5,xy&lt;0;0.25,xy≥0}（在(0,0)处不连续，不满足性质F），g(x,y)=0（在(0,0)处连续，满足性质F）###-###&gt;&gt;&gt;NA（非周期函数取floor仍为非周期，无法构造g为周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=1（可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)处二阶偏导不连续，不满足性质I），g(x,y)=0（分母比分子高阶，绝对值在0-1之间，向下取整全部拉到0。二阶偏导连续，满足性质I）###-###&gt;&gt;&gt;f(x)=分段{1.5,x&gt;0;0.5,x=0;-0.5,x&lt;0},g(x)=分段{1,x&gt;0;0,x=0;-1,x&lt;0}###-###&gt;&gt;&gt;f(x)=分段{0,x≠1;0.5,x=1}（非偶函数，不满足性质K），g(x)=0（偶函数，满足性质K）###-###&gt;&gt;&gt;f(x)=|x|+0.5（在x=0处无切线，不满足性质L），g(x)=floor(|x|+0.5)=0（在x=0处有切线，满足性质L）###-###&gt;&gt;&gt;f(x)=1/x+1（x≥1时floor(1/x+1)=1，无穷积分发散）,g(x)=1（无穷积分发散）###-</t>
+  </si>
+  <si>
+    <t>10：###&gt;&gt;&gt;f(x)=x（在x=0处可导，满足性质A）,g(x)=floor(x)（在x=0处因跳跃间断不可导，不满足性质A）###-###&gt;&gt;&gt;f(x,y)=x（在全平面偏导数存在，满足性质B）,g(x,y)=floor(x)（在x=0处因整数点跳跃导致左右偏导数不存在，不满足性质B）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=floor(f(x))在f(x)∈Z处必间断，因floor函数在整数点跳跃）###-###&gt;&gt;&gt;f(x,y)=x（在全平面可微，满足性质D）,g(x,y)=floor(x)（在x=0处因整数点跳跃不连续，不满足可微性要求，故不满足性质D）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在且f(x0)∈Z，则g(x)左右极限不同，极限不存在）###-###&gt;&gt;&gt;NA（若f(x,y)连续且f(x,y)∈Z，则g(x,y)在该点间断，因floor跳跃）###-###&gt;&gt;&gt;NA（若f(x)周期T，g(x)=floor(f(x))周期必为T，因f(x+T)=f(x)⇒g(x+T)=g(x)，但g在整数点间断，仍为周期函数）###-###&gt;&gt;&gt;NA（若f(x)可积，g(x)=floor(f(x))在f(x)值域不含整数时可积，如f(x)=x+0.5在[0,1]可积，g(x)=0可积，无法构造g不可积的例子）###-###&gt;&gt;&gt;f(x,y)=x³二阶偏导连续，g(x,y)=floor(x³)在x=0处二阶偏导不存在###-###&gt;&gt;&gt;NA（若f(x)是奇函数，g(x)=floor(f(x))非奇函数，因floor(-f(x))≠-floor(f(x))，如f(x)=x，floor(-0.5)=-1≠-floor(0.5)=0）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=floor(x²)（偶函数，因x²=(-x)²⇒floor(x²)=floor((-x)²)）###-###&gt;&gt;&gt;f(x)=x（在x=0处切线为y=x）,g(x)=floor(x)（在x=0处左极限0、右极限1，不连续，无切线）###-###&gt;&gt;&gt;NA（若f(x)的反常积分收敛，则当x→∞时f(x)→0，故存在X使得x&gt;X时f(x)&lt;1，此时floor(f(x))=0。因此g(x)在(X,∞)上恒为0，仅在[0,X]上可能非零，其积分必收敛，无法构造g积分发散的例子）###-</t>
+  </si>
+  <si>
+    <t>11：###&gt;&gt;&gt;NA（若f(x)可导，则g(x)=floor(f(x))在f(x)∈Z处必不可导，因floor跳跃）###-###&gt;&gt;&gt;NA（若f(x,y)偏导数存在，则g(x,y)=floor(f(x,y))在f∈Z处偏导数不存在，因跳跃）###-###&gt;&gt;&gt;NA（若f(x)连续，则g(x)=floor(f(x))在f(x)∈Z处必不连续，因floor跳跃）###-###&gt;&gt;&gt;NA（若f(x,y)可微，则g(x,y)=floor(f(x,y))在f∈Z处必不可微，因不连续）###-###&gt;&gt;&gt;NA（若f(x)在x→x0极限存在且f(x0)∈Z，则g(x)极限不存在，因左右极限不同）###-###&gt;&gt;&gt;NA（若f(x,y)连续，则g(x,y)=floor(f(x,y))在f∈Z处必不连续，因跳跃）###-###&gt;&gt;&gt;f(x)=sinx（周期2π，满足性质G），g(x)=floor(sinx)（周期2π，满足性质G）###-###&gt;&gt;&gt;f(x)=x+0.5（在[0,1]上连续可积，定积分值为Int(0,1):(x+0.5)dx=0.75）,g(x)=floor(x+0.5)=0（在[0,1]上为常数函数，定积分值为0，满足可积性）###-###&gt;&gt;&gt;NA（若f(x,y)二阶偏导连续，则g(x,y)=floor(f(x,y))在f∈Z处二阶偏导不存在，因跳跃）###-###&gt;&gt;&gt;NA（若f(x)是奇函数，g(x)=floor(f(x))必非奇函数，因floor(-f(x))≠-floor(f(x))）###-###&gt;&gt;&gt;f(x)=x²（偶函数）,g(x)=floor(x²)（偶函数）###-###&gt;&gt;&gt;f(x)=x+0.5（在x=0处切线为y=x+0.5）,g(x)=floor(x+0.5)=0（常数函数，在x=0处切线为y=0）###-###&gt;&gt;&gt;f(x)=e^(-x)（无穷积分收敛）,g(x)=0（无穷积分收敛）###-</t>
+  </si>
+  <si>
+    <t>特例法大杀器-二元运算### ###（无需作答）</t>
+  </si>
+  <si>
+    <t>加减（f(x)±g(x)=h(x)或f(x,y)±g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>000：###F (x)=|x|,G (x)=|x|###-###F (x,y)=|x|+|y|,G (x,y)=|x|+|y|###-###F (x)=1/x,G (x)=1/x###-###F (x,y)=1/√(x²+y²),G (x,y)=1/√(x²+y²)###-###F (x)=1/x,G (x)=1/x###-###F (x,y)=1/(x+y),G (x,y)=1/(x+y)###-###F (x)=sinx+1/x,G (x)=cosx+1/x###-###F (x)=1/x,G (x)=1/x（区间 [0,1]）###-###F (x,y)=1/(x+y),G (x,y)=1/(x+y)###-###F (x)=x²+1,G (x)=x²+1###-###F (x)=x+1,G (x)=x+1###-###F (x)=|x|,G (x)=|x|###-###F (x)=1/x,G (x)=1/x（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>001：###F (x)=x,G (x)=2x→h (x)=3x###-###F (x,y)=x+y,G (x,y)=xy→h (x,y)=x+y-xy###-###F (x)=sinx,G (x)=x（连续函数加减必连续√）###-###F (x)=x²,G (x)=cosx（可导函数加减必可导√，因 (h)'=(f±g)'=f'±g'）###-###F (x)=x+1,G (x)=2x（x→2 时极限存在，加减后极限仍存在√）###-###F (x)=sinx,G (x)=sin (√2x)（周期函数加减未必周期 ×，如两函数周期比为无理数时和非周期）###-###F (x)=x,G (x)=1（[0,1] 上可积函数加减必可积√）###-###F (x,y)=x²,G (x,y)=y²→h (x,y)=x²+y²###-###F (x)=x,G (x)=x³（奇函数加减奇函数必为奇函数√，h (-x)=-f (x)±(-g (x))=-h (x)）###-###F (x)=x²,G (x)=cosx（偶函数加减偶函数必为偶函数√，h (-x)=f (-x)±g (-x)=h (x)）###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞) 收敛，加减后仍收敛√）###-###F (x)=sinx,G (x)=cosx（有界函数加减必为有界函数√，|h (x)|≤|f (x)|+|g (x)|≤2）###-###F (x)=2x+1,G (x)=-x→h (x)=x+1（线性函数加减仍为线性函数√）###</t>
+  </si>
+  <si>
+    <t>010：###F (x)=|x|,G (x)=x###-###F (x,y)=|x|,G (x,y)=y###-###F (x)=1/x,G (x)=x###-###F (x,y)=1/√(x²+y²),G (x,y)=y###-###F (x)=1/x,G (x)=x###-###F (x,y)=1/(x+y),G (x,y)=y###-###F (x)=sinx+1/x,G (x)=sinx###-###F (x)=1/x,G (x)=x（区间 [0,1]）###-###F (x,y)=1/(x+y),G (x,y)=y###-###F (x)=x²+1,G (x)=x###-###F (x)=x+1,G (x)=x²###-###F (x)=|x|,G (x)=x###-###F (x)=1/x,G (x)=1/x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>011：###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=sinx,G (x)=sinx###-###F (x)=x,G (x)=x²（区间 [0,1]）###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x³###-###F (x)=x²,G (x)=x⁴###-###F (x)=x,G (x)=x²###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>110：###NA (可导函数加减必可导)###-###NA (偏导存在函数加减必偏导存在)###-###NA (连续函数加减必连续)###-###NA (可微函数加减必可微)###-###NA (极限存在函数加减必极限存在)###-###NA (连续函数加减必连续)###-###F (x)=sinx,G (x)=sin2x###-###NA (可积函数加减必可积)###-###NA (二阶偏导连续函数加减必连续)###-###NA (奇函数加减必奇函数)###-###NA (偶函数加减必偶函数)###-###NA (有切线函数加减必有切线)###-###NA (收敛反常积分加减必收敛)###</t>
+  </si>
+  <si>
+    <t>111：###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=sinx,G (x)=sinx###-###F (x)=x,G (x)=x²（区间 [0,1]）###-###F (x,y)=xy,G (x,y)=x²y###-###F (x)=x,G (x)=x³###-###F (x)=x²,G (x)=x⁴###-###F (x)=x,G (x)=x²###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>乘法（f(x)*g(x)=h(x)或f(x,y)*g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>000：###F (x)=|x|+1,G (x)=|x|+1###-###F (x,y)=1/√(x²+y²),G (x,y)=1/√(x²+y²)###-###F (x)=1/x,G (x)=1/x###-###F (x,y)=1/√(x²+y²),G (x,y)=1/√(x²+y²)###-###F (x)=1/x,G (x)=1/x###-###F (x,y)=1/(x+y),G (x,y)=1/(x+y)###-###F (x)=sinx+1/x,G (x)=cosx+1/x###-###F (x)=1/x,G (x)=1/x（区间 [0,1]）###-###F (x,y)=1/(x+y),G (x,y)=1/(x+y)###-###F (x)=x²+1,G (x)=x²+1###-###F (x)=x+1,G (x)=x+1###-###F (x)=|x|,G (x)=|x|###-###F (x)=1/√x,G (x)=1/√x（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>001：###F (x)=x,G (x)=2x→h (x)=2x²###-###F (x,y)=x+y,G (x,y)=xy→h (x,y)=(x+y) xy=x²y+xy²###-###F (x)=sinx,G (x)=x（连续函数相乘必连续√，由连续函数运算性质保证）###-###F (x)=x²,G (x)=cosx（可导函数相乘必可导√，因 (h)'=f'g+fg' 存在）###-###F (x)=x+1,G (x)=2x（x→2 时极限存在，相乘后极限为 (2+1)×4=12√）###-###F (x)=sinx,G (x)=sin (√2x)（周期函数相乘未必周期 ×，两函数周期比为无理数时无公共周期；反例：sinx・sin (√2x) 非周期）###-###F (x)=x,G (x)=1（[0,1] 上可积函数相乘必可积√，因乘积仍有界且间断点有限）###-###F (x,y)=x²,G (x,y)=y²→h (x,y)=x²y²###-###F (x)=x,G (x)=x³（奇函数 × 奇函数 = 偶函数√，h (-x)=(-x)・(-x³)=x⁴=h (x)）###-###F (x)=x²,G (x)=cosx（偶函数 × 偶函数 = 偶函数√，h (-x)=x²・cosx=h (x)）###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞)，乘积 1/x^5 收敛√，因 p=5&gt;1）###-###F (x)=sinx,G (x)=cosx（有界函数相乘必为有界函数√，|h (x)|≤|sinx||cosx|≤1/2）###-###F (x)=2x+1,G (x)=-x→h (x)=-2x²-x（线性函数相乘必为二次函数√，次数为 1+1=2）###</t>
+  </si>
+  <si>
+    <t>010：###F (x)=x,G (x)=|x|###-###F (x,y)=0,G (x,y)=|x|###-###F (x)=0,G (x)=1/x###-###F (x,y)=0,G (x,y)=|x|+|y|###-###F (x)=x,G (x)=1/x###-###F (x,y)=0,G (x,y)=1/(x+y)###-###F (x)=0,G (x)=x###-###F (x)=0,G (x)=1/x（区间 [0,1]）###-###F (x,y)=0,G (x,y)=1/(x+y)###-###F (x)=x,G (x)=x²###-###F (x)=0,G (x)=x###-###F (x)=x,G (x)=|x|###-###F (x)=0,G (x)=x（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>011：###F (x)=x,G (x)=x²###-###F (x,y)=x,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=x,G (x,y)=x²y###-###F (x)=x,G (x)=x²###-###F (x,y)=x,G (x,y)=x²y###-###F (x)=sinx,G (x)=x###-###F (x)=x,G (x)=x²（区间 [0,1]）###-###F (x,y)=x,G (x,y)=x²y###-###F (x)=x,G (x)=x³###-###F (x)=x²,G (x)=x⁴###-###F (x)=x,G (x)=x²###-###F (x)=x,G (x)=x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>110：###F (x)=x,G (x)=x###-###F (x,y)=x,G (x,y)=y###-###F (x)=x,G (x)=x²###-###F (x,y)=x,G (x,y)=y###-###F (x)=x,G (x)=x²###-###F (x,y)=x,G (x,y)=y###-###F (x)=sinx,G (x)=cosx###-###F (x)=x,G (x)=x²（区间 [0,1]）###-###F (x,y)=x,G (x,y)=y###-###F (x)=x,G (x)=x²###-###F (x)=x²,G (x)=x³###-###F (x)=x,G (x)=x²###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>除法（f(x)/g(x)=h(x)或f(x,y)/g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>000：###F (x)=x²,G (x)=x（x≠0）###-###F (x,y)=x²y,G (x,y)=xy（xy≠0）###-###F (x)=x+1,G (x)=1###-###F (x,y)=x²+y²,G (x,y)=1###-###F (x)=x³,G (x)=x（x≠0）###-###F (x,y)=x+y,G (x,y)=2###-###F (x)=sin2x,G (x)=sinx（sinx≠0）###-###F (x)=1,G (x)=2（区间 [0,1]）###-###F (x,y)=x³y³,G (x,y)=xy（xy≠0）###-###F (x)=x²,G (x)=x⁴###-###F (x)=x+1,G (x)=1###-###F (x)=x,G (x)=1###-###F (x)=1/x²,G (x)=1（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>001：###F (x)=|x|,G (x)=x（x≠0）###-###F (x,y)=|x|,G (x,y)=y（y≠0）###-###F (x)=sgn (x),G (x)=1###-###F (x,y)=|x|+|y|,G (x,y)=x（x≠0）###-###F (x)=1/x,G (x)=x（x≠0）###-###F (x,y)=1/|x+y|,G (x,y)=1###-###F (x)=x+|x|,G (x)=sinx（sinx≠0）###-###F (x)=1/x,G (x)=1（区间 (0,1]）###-###F (x,y)=|x|+|y|,G (x,y)=y（y≠0）###-###F (x)=x²+|x|,G (x)=x（x≠0）###-###F (x)=x+1,G (x)=x²###-###F (x)=|x|,G (x)=x（x≠0）###-###F (x)=1/x,G (x)=1/x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>010：###F (x)=x,G (x)=|x|（x≠0）###-###F (x,y)=x,G (x,y)=|x|（x≠0）###-###F (x)=x²,G (x)=x（x≠0）###-###F (x,y)=x,G (x,y)=1/√(x²+y²)（x²+y²≠0）###-###F (x)=x³,G (x)=x²（x≠0）###-###F (x,y)=x,G (x,y)=1/(x+y)（x+y≠0）###-###F (x)=sinx,G (x)=x（x≠0）###-###F (x)=x,G (x)=1（区间 [0,1]）###-###F (x,y)=x,G (x,y)=1/(x+y)（x+y≠0）###-###F (x)=x⁴,G (x)=x²（x≠0）###-###F (x)=x³,G (x)=x（x≠0）###-###F (x)=x,G (x)=|x|（x≠0）###-###F (x)=1/x,G (x)=1/x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>011：###F (x)=x³,G (x)=x²（x≠0）###-###F (x,y)=x²y³,G (x,y)=xy²（xy≠0）###-###F (x)=sinx,G (x)=cosx（cosx≠0）###-###F (x,y)=x+y,G (x,y)=x（x≠0）###-###F (x)=x²+1,G (x)=x+1（x≠-1）###-###F (x,y)=1/√(x²+y²),G (x,y)=1/(x+y)（x+y≠0）###-###F (x)=x+|x|,G (x)=x（x≠0）###-###F (x)=x²,G (x)=x（区间 (0,1]）###-###F (x,y)=x³+y³,G (x,y)=x+y（x+y≠0）###-###F (x)=x⁴,G (x)=x³（x≠0）###-###F (x)=e^x,G (x)=e^x###-###F (x)=|x|,G (x)=x（x≠0）###-###F (x)=1/x,G (x)=1/x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>100：###F (x)=x,G (x)=|x|（x≠0）###-###F (x,y)=x,G (x,y)=|x|（x≠0）###-###F (x)=x²,G (x)=|x|（x≠0）###-###F (x,y)=x,G (x,y)=1/√(x²+y²)（x²+y²≠0）###-###F (x)=x³,G (x)=x|x|（x≠0）###-###F (x,y)=x,G (x,y)=1/(x+y)（x+y≠0）###-###F (x)=sinx,G (x)=|sinx|（sinx≠0）###-###F (x)=x,G (x)=1（区间 [0,1]）###-###F (x,y)=x,G (x,y)=1/(x+y)（x+y≠0）###-###F (x)=x⁴,G (x)=x²|x|（x≠0）###-###F (x)=e^x,G (x)=e^{|x|}###-###F (x)=x,G (x)=|x|（x≠0）###-###F (x)=1/x,G (x)=1/|x|（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>101：###F (x)=x³,G (x)=√|x|###-###F (x,y)=x³y,G (x,y)=√|x|+y###-###F (x)=1,G (x)=1/x###-###F (x,y)=x²+y²,G (x,y)=|x|+|y|###-###F (x)=x,G (x)=sin (1/x)###-###F (x,y)=1,G (x,y)=1/(x+y)###-###NA (周期函数除以非周期函数无法保证 H 周期)###-###F (x)=1,G (x)=1/x###-###F (x,y)=x⁴y²,G (x,y)=|x|y²###-###F (x)=x³,G (x)=x²###-###NA (偶函数除以非偶函数无法得到偶函数)###-###F (x)=x⁴,G (x)=√|x|###-###F (x)=1/x²,G (x)=1/√x###</t>
+  </si>
+  <si>
+    <t>110：###F (x)=1,G (x)=x（x≠0）###-###F (x,y)=x,G (x,y)=y（y≠0）###-###F (x)=1,G (x)=x（x≠0）###-###F (x)=x,G (x)=x（x≠0）###-###F (x)=1,G (x)=x（x→0）###-###F (x,y)=1,G (x,y)=x+y（x+y≠0）###-###F (x)=sinx+1,G (x)=sinx（sinx≠0）###-###F (x)=1,G (x)=x（区间 (0,1]）###-###F (x,y)=x²,G (x,y)=y²（y≠0）###-###F (x)=x,G (x)=x（x≠0）###-###NA (偶函数相除必为偶函数)###-###F (x)=1,G (x)=x（x≠0）###-###F (x)=1/x²,G (x)=1/x（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>111：###F (x)=x⁴,G (x)=x²（x≠0）###-###F (x,y)=x³y²,G (x,y)=xy（xy≠0）###-###F (x)=sin2x,G (x)=cosx（cosx≠0）###-###F (x,y)=x²+y²,G (x,y)=x+y（x+y≠0）###-###F (x)=x³+1,G (x)=x+1（x≠-1）###-###F (x,y)=√(x²+y²),G (x,y)=1/√(x²+y²)（x²+y²≠0）###-###F (x)=x+sinx,G (x)=x（x≠0）###-###F (x)=x³,G (x)=x²（区间 (0,1]）###-###F (x,y)=x⁴y³,G (x,y)=x²y²（xy≠0）###-###F (x)=x⁵,G (x)=x³（x≠0）###-###F (x)=e^{2x},G (x)=e^x###-###F (x)=x|x|,G (x)=x（x≠0）###-###F (x)=1/x³,G (x)=1/x²（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>取最大值（max(f(x),g(x))=h(x)或max(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>000：###F (x)=|x|,G (x)=-|x|###-###F (x,y)=|x|+|y|,G (x,y)=-|x|-|y|###-###F (x)=1/x,G (x)=sin (1/x)###-###F (x,y)=√(x²+y²),G (x,y)=-√(x²+y²)###-###F (x)=sin (1/x),G (x)=cos (1/x)###-###F (x,y)=1/(x+y),G (x,y)=1/(x-y)###-###F (x)=x,G (x)=e^x###-###F (x)=D (x),G (x)=D (x)（D 为狄利克雷函数）###-###F (x,y)=|x|y²,G (x,y)=x|y|###-###F (x)=x²,G (x)=x+1###-###F (x)=x³,G (x)=x+1###-###F (x)=|x|,G (x)=-|x|###-###F (x)=1/x,G (x)=1/x²###</t>
+  </si>
+  <si>
+    <t>001：###F (x)=x,G (x)=0###-###F (x,y)=x,G (x,y)=y###-###NA (连续函数取最大值必连续)###-###F (x)=x,G (x)=-x###-###NA (极限存在函数取最大值必极限存在)###-###NA (连续函数取最大值必连续)###-###NA (周期函数取最大值必周期)###-###NA (可积函数取最大值必可积)###-###F (x,y)=x²,G (x,y)=y²###-###F (x)=x,G (x)=-x###-###NA (偶函数取最大值必偶函数)###-###F (x)=x,G (x)=0###-###NA (收敛反常积分取最大值必收敛)###</t>
+  </si>
+  <si>
+    <t>010：###F (x)=x,G (x)=0###-###F (x,y)=x,G (x,y)=y###-###NA (连续函数取最大值必连续)###-###F (x)=x,G (x)=0###-###NA (极限存在函数取最大值必极限存在)###-###NA (连续函数取最大值必连续)###-###F (x)=sinx,G (x)=sin (√2x)###-###NA (可积函数取最大值必可积)###-###F (x,y)=x²,G (x,y)=y²###-###F (x)=x,G (x)=-x###-###NA (偶函数取最大值必偶函数)###-###F (x)=x,G (x)=0###-###NA (收敛反常积分取最大值必收敛)###</t>
+  </si>
+  <si>
+    <t>011：###F (x)=x,G (x)=2x###-###F (x,y)=x²+y²,G (x,y)=0###-###F (x)=x,G (x)=1###-###F (x)=x,G (x)=-x###-###F (x)=x,G (x)=2（x→1）###-###F (x)=sinx,G (x)=cosx###-###F (x)=sinx,G (x)=cosx###-###F (x)=x,G (x)=0（区间 [0,1]）###-###F (x,y)=x²+y²,G (x,y)=0###-###F (x)=x,G (x)=2x###-###F (x)=x²,G (x)=1###-###F (x)=x,G (x)=2x###-###F (x)=1/x²,G (x)=1/x³（积分区间 [1,+∞)）###</t>
+  </si>
+  <si>
+    <t>110：###F (x)=x,G (x)=-x###-###F (x,y)=x,G (x,y)=y###-###NA (两连续函数最大值必连续)###-###F (x,y)=x²,G (x,y)=y²###-###NA (两函数极限存在则最大值极限必存在)###-###NA (两连续多元函数最大值必连续)###-###F (x)=sinx,G (x)=sin (√2x)###-###NA (两可积函数最大值必可积)###-###F (x,y)=x⁴,G (x,y)=y⁴###-###F (x)=x,G (x)=x³###-###NA (两偶函数最大值必为偶函数)###-###F (x)=x,F (x)=x²###-###NA (两收敛反常积分最大值必收敛)###</t>
+  </si>
+  <si>
+    <t>111：###F(x)=x²,G(x)=2x²###-###F(x,y)=x³y,G(x,y)=2x³y###-###F(x)=sinx,G(x)=cosx###-###F(x,y)=x²+y²,G(x,y)=2x²+2y²###-###F(x)=x,G(x)=2x###-###F(x,y)=xy,G(x,y)=2xy###-###F(x)=sinx,G(x)=sin2x###-###F(x)=1,G(x)=2###-###F(x,y)=x⁴y²,G(x,y)=2x⁴y²###-###F(x)=x,G(x)=2x###-###F(x)=x²,G(x)=2x²###-###F(x)=x²,G(x)=3x²###-###F(x)=1/x²,G(x)=1/x³###</t>
+  </si>
+  <si>
+    <t>取最小值（min(f(x),g(x))=h(x)或min(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>001：###F(x)=D(x),G(x)=1-D(x)###-###F(x,y)=|x|+y,G(x,y)=x+|y|###-###F(x)=D(x),G(x)=1-D(x)###-###F(x,y)=|x|+y,G(x,y)=x+|y|###-###F(x)=sgn(x),G(x)=1-sgn(x)###-###F(x,y)=1/(x+y)+D(x,y),G(x,y)=1/(x-y)+1-D(x,y)###-###F(x)=D(x),G(x)=1-D(x)###-###F(x)=D(x),G(x)=1-D(x)###-###F(x,y)=|x|y+D(x,y),G(x,y)=x|y|+1-D(x,y)###-###F(x)=|x|+x,G(x)=|x|-x###-###F(x)=x²+1,G(x)=-x²+1###-###F(x)=D(x),G(x)=1-D(x)###-###F(x)=1/x+D(x),G(x)=1/x²+1-D(x)###</t>
+  </si>
+  <si>
+    <t>010：###F(x)=|x|,G(x)=x###-###F(x,y)=|x|+|y|,G(x,y)=x+y###-###F(x)=1/x,G(x)=x###-###F(x,y)=√(x²+y²),G(x,y)=x+y###-###F(x)=sin(1/x),G(x)=x###-###F(x,y)=1/(x+y),G(x,y)=x+y###-###F(x)=x,G(x)=sinx###-###F(x)=D(x),G(x)=x###-###F(x,y)=|x|y²,G(x,y)=x²y###-###F(x)=x²,G(x)=x³###-###F(x)=x²+1,G(x)=x³###-###F(x)=|x|,G(x)=x###-###F(x)=1/x,G(x)=1/x²###</t>
+  </si>
+  <si>
+    <t>110：###F (x)=x²,G (x)=-x²###-###F (x,y)=x²+y²,G (x,y)=-x²-y²###-###NA (两连续函数最小值必连续)###-###F (x,y)=x²+y²,G (x,y)=-x²-y²###-###NA (两极限存在函数最小值极限必存在)###-###NA (两连续多元函数最小值必连续)###-###F (x)=sinx,G (x)=sin2x###-###NA (两可积函数最小值必可积)###-###F (x,y)=x⁴+y⁴,G (x,y)=-x⁴-y⁴###-###F (x)=x³,G (x)=-x³###-###NA (两偶函数最小值必为偶函数)###-###F (x)=x²,G (x)=-x²###-###NA (两收敛反常积分最小值必收敛)###</t>
+  </si>
+  <si>
+    <t>111：###F(x)=x²,G(x)=3x²###-###F(x,y)=x³y,G(x,y)=2x³y###-###F(x)=sinx,G(x)=cosx###-###F(x,y)=x²+y²,G(x,y)=2x²+2y²###-###F(x)=x,G(x)=2x###-###F(x,y)=xy,G(x,y)=2xy###-###F(x)=sinx,G(x)=sin2x###-###F(x)=1,G(x)=2###-###F(x,y)=x⁴y²,G(x,y)=2x⁴y²###-###F(x)=x,G(x)=2x###-###F(x)=x²,G(x)=2x²###-###F(x)=x²,G(x)=3x²###-###F(x)=1/x²,G(x)=1/x³###</t>
+  </si>
+  <si>
+    <t>复合函数（f(g(x))=h(x)或h(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>000：###F(x)=x²,G(x)=3x²###-###F(x,y)=x³y,G(x,y)=2x³y###-###F(x)=sinx,G(x)=cosx###-###F(x,y)=x²+y²,G(x,y)=2x²+2y²###-###F(x)=x,G(x)=2x###-###F(x,y)=xy,G(x,y)=2xy###-###F(x)=sinx,G(x)=sin2x###-###F(x)=1,G(x)=2###-###F(x,y)=x⁴y²,G(x,y)=2x⁴y²###-###F(x)=x,G(x)=2x###-###F(x)=x²,G(x)=2x²###-###F(x)=x²,G(x)=3x²###-###F(x)=1/x²,G(x)=1/x³###</t>
+  </si>
+  <si>
+    <t>001：###F (u)=u²,G (x)=|x|###-###NA (G 不可偏导时 H 无法保证可偏导)###-###F (u)=1,G (x)=D (x)###-###NA (G 不可微时 H 无法保证可微)###-###F (u)=0,G (x)=sin (1/x)###-###F (u)=1,G (x,y)=1/(x+y)###-###F (u)=sinu,G (x)=x###-###F (u)=1,G (x)=D (x)###-###NA (G 不连续时 H 无法二阶偏导连续)###-###NA (奇函数复合非奇函数无法得奇函数)###-###F (u)=u²,G (x)=x###-###F (u)=u²,G (x)=|x|###-###F (u)=1/u²,G (x)=x###</t>
+  </si>
+  <si>
+    <t>010：###F (u)=√|u|,G (x)=x###-###F (u,v)=√|u|,G (x,y)=x###-###F (u)=D (u),G (x)=x###-###F (u)=|u|,G (x)=x###-###F (u)=sin (1/u),G (x)=x###-###F (u,v)=1/(u+v),G (x,y)=x+y###-###NA (非周期函数复合周期函数无法得到非周期函数)###-###F (u)=D (u),G (x)=x###-###F (u,v)=1/(u+v),G (x,y)=x+y###-###F (u)=u²,G (x)=x###-###F (u)=u+1,G (x)=x²###-###F (u)=|u|,G (x)=x###-###F (u)=1/u,G (x)=x###</t>
+  </si>
+  <si>
+    <t>011：###F (x)=x³,G (x)=sinx→h (x)=sin³x###-###F (x,y)=x+y,G (x,y)=xy→H (x,y)=(x+y)・xy###-###NA (可导函数复合必可导 ×，如 f (x)=|x|,g (x)=x 在 x=0 处不可导)###-###F (x)=√(x²+1),G (x)=x²（x∈ℝ）→h (x)=√(x⁴+1)###-###F (x,y)=e^x,G (x,y)=y²→H (x,y)=e^x+y²###-###NA (连续函数复合必连续√，由连续函数复合定理可知)###-###F (x)=x²,G (x)=cosx→h (x)=cos²x###-###F (x)=1/x,G (x)=x-1（区间 (1,2)）→h (x)=1/(x-1)###-###F (x,y)=√x,G (x,y)=y²（x≥0）→H (x,y)=√x+y²###-###F (x)=lnx,G (x)=x²（x&gt;0）→h (x)=2lnx###-###NA (偶函数复合奇函数必为偶函数√，因 f (g (-x))=f (-g (x))=f (g (x))###-###F (x)=x³+1,G (x)=x-1→h (x)=(x-1)³+1=x³-3x²+3x###-###NA (收敛反常积分复合必收敛 ×，如 f (x)=e^x,g (x)=1/x 时∫₁^∞e^(1/x) dx 发散)###</t>
+  </si>
+  <si>
+    <t>100：###F(u)=u²,G(x)=x+1###-###F(u)=u,G(x,y)=x²+y²###-###F(u)=|u|,G(x)=x###-###F(u)=u³,G(x)=x²###-###F(u)=u,G(x)=x###-###F(u,v)=u+v,G(x,y)=xy###-###F(u)=u²,G(x)=sinx###-###F(u)=1,G(x)=x###-###F(u)=u⁴,G(x,y)=x²+y²###-###F(u)=u³,G(x)=x###-###F(u)=u²,G(x)=x²###-###F(u)=u,G(x)=x###-###F(u)=e⁻ᵘ,G(x)=x²###</t>
+  </si>
+  <si>
+    <t>101：###F(u)=u²,G(x)=x³###-###F(u)=u,G(x,y)=x³y###-###F(u)=|u|,G(x)=x³###-###F(u)=u³,G(x)=x²###-###F(u)=u,G(x)=x³###-###F(u,v)=u+v,G(x,y)=x³y###-###F(u)=u²,G(x)=sinx###-###F(u)=1,G(x)=x³###-###F(u)=u⁴,G(x,y)=x³y²###-###F(u)=u³,G(x)=x###-###F(u)=u²,G(x)=x²###-###F(u)=u,G(x)=x³###-###F(u)=e⁻ᵘ,G(x)=x³###</t>
+  </si>
+  <si>
+    <t>110：###F (u)=u²,G (x)=x###-###F (u)=u,G (x,y)=x²+y²###-###NA (两连续函数复合必连续)###-###F (u)=u³,G (x,y)=x²+y²###-###NA (两极限存在函数复合极限必存在)###-###NA (两连续多元函数复合必连续)###-###F (u)=u²,G (x)=sinx###-###NA (两可积函数复合必可积)###-###F (u)=u⁴,G (x,y)=x²+y²###-###F (u)=u³,G (x)=x###-###F (u)=u²,G (x)=x²###-###F (u)=u,G (x)=x###-###NA (两收敛反常积分复合必收敛)###</t>
+  </si>
+  <si>
+    <t>111：###F(u)=u²,G(x)=x###-###F(u)=u,G(x,y)=x²+y²###-###F(u)=|u|,G(x)=x###-###F(u)=u³,G(x,y)=x²+y²###-###F(u)=u,G(x)=x###-###F(u,v)=u+v,G(x,y)=x²+y²###-###F(u)=u²,G(x)=sinx###-###F(u)=1,G(x)=x###-###F(u)=u⁴,G(x,y)=x²+y²###-###F(u)=u³,G(x)=x###-###F(u)=u²,G(x)=x²###-###F(u)=u,G(x)=x###-###F(u)=e⁻ᵘ,G(x)=x²###</t>
   </si>
 </sst>
 </file>
@@ -4842,6 +6456,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4865,13 +6486,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5021,6 +6635,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.5"/>
       <color rgb="FF24292F"/>
@@ -5032,13 +6653,6 @@
       <color rgb="FF24292F"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -5498,13 +7112,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -5578,6 +7192,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5871,21 +7492,21 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240225</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="3:3">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5895,7 +7516,7 @@
       </c>
     </row>
     <row r="6" spans="3:3">
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6532,6 +8153,599 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>9.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2066)/COLUMN()</f>
+        <v>3.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>5.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>20250525</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>1.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2066)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>20250526</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>9.2</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2066)/COLUMN()</f>
+        <v>2.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250527</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5">
+      <c r="E9" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>2</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2066)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250528</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>1.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2066)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250529</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -6602,6 +8816,1633 @@
       <c r="B6" t="s">
         <v>119</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>18.5</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2072)/COLUMN()</f>
+        <v>4.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250530</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3">
+      <c r="C38" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="2" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4">
+      <c r="D51" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="2" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3">
+      <c r="C55" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3">
+      <c r="C56" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3">
+      <c r="C58" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>6.5</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2072)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250531</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="2"/>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>5.08333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2072)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250601</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" s="2"/>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet113.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>7.11666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.66666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>3.25</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250602</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet114.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>5.5</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250603</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>1.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250604</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>5.25</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.75</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250605</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet117.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>1.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250607</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet118.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>5.33333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2071)/COLUMN()</f>
+        <v>3</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250608</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3">
+      <c r="C48" s="2"/>
+    </row>
+    <row r="52" spans="4:4">
+      <c r="D52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet119.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>12.3285714285714</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>3.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.428571428571429</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250609</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6">
+      <c r="F35" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6">
+      <c r="F36" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6">
+      <c r="F37" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7">
+      <c r="F38" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6">
+      <c r="F39" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="40" spans="6:6">
+      <c r="F40" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="41" spans="7:7">
+      <c r="G41" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="42" spans="7:7">
+      <c r="G42" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6693,7 +10534,1606 @@
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="6"/>
+      <c r="B10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet120.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250610</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet121.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>4.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250611</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet122.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>9.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>3.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>3.66666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250612</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet123.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>3.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250613</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet124.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>3.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250614</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>3.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2082)/COLUMN()</f>
+        <v>3.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250615</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>6.83333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2068)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>5.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250616</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3">
+      <c r="C45" s="2"/>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>6.33333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2060)/COLUMN()</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250617</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="2"/>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>12.1666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2090)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250618</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4">
+      <c r="D40" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4">
+      <c r="D44" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3">
+      <c r="C67" s="2"/>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>12.8333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2040)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250619</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4">
+      <c r="D40" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3">
+      <c r="C44" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" t="s">
+        <v>1966</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6842,6 +12282,299 @@
     <row r="21" spans="6:6">
       <c r="F21" t="s">
         <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>12.8333333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2046)/COLUMN()</f>
+        <v>0.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20250620</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="39" spans="4:4">
+      <c r="D39" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4">
+      <c r="D40" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4">
+      <c r="D44" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4">
+      <c r="D46" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4">
+      <c r="D47" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4">
+      <c r="D48" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" t="s">
+        <v>2010</v>
       </c>
     </row>
   </sheetData>
@@ -6962,25 +12695,25 @@
       </c>
     </row>
     <row r="15" spans="3:3">
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="16" spans="4:4">
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="17" spans="5:8">
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="5:5">
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>160</v>
       </c>
     </row>
@@ -7332,8 +13065,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" s="5" customFormat="1" spans="5:5">
-      <c r="E18" s="5" t="s">
+    <row r="18" s="6" customFormat="1" spans="5:5">
+      <c r="E18" s="6" t="s">
         <v>211</v>
       </c>
     </row>
@@ -7529,18 +13262,18 @@
         <v>239</v>
       </c>
     </row>
-    <row r="29" s="6" customFormat="1" spans="2:2">
-      <c r="B29" s="6" t="s">
+    <row r="29" s="2" customFormat="1" spans="2:2">
+      <c r="B29" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="1" spans="3:3">
-      <c r="C30" s="6" t="s">
+    <row r="30" s="2" customFormat="1" spans="3:3">
+      <c r="C30" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="31" s="6" customFormat="1" spans="3:3">
-      <c r="C31" s="6" t="s">
+    <row r="31" s="2" customFormat="1" spans="3:3">
+      <c r="C31" s="2" t="s">
         <v>242</v>
       </c>
     </row>
@@ -7677,38 +13410,38 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" spans="2:2">
-      <c r="B4" s="4" t="s">
+    <row r="4" s="5" customFormat="1" spans="2:2">
+      <c r="B4" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" spans="3:3">
-      <c r="C5" s="4" t="s">
+    <row r="5" s="5" customFormat="1" spans="3:3">
+      <c r="C5" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" spans="3:3">
-      <c r="C6" s="4" t="s">
+    <row r="6" s="5" customFormat="1" spans="3:3">
+      <c r="C6" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" spans="3:3">
-      <c r="C7" s="4" t="s">
+    <row r="7" s="5" customFormat="1" spans="3:3">
+      <c r="C7" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" spans="3:3">
-      <c r="C8" s="4" t="s">
+    <row r="8" s="5" customFormat="1" spans="3:3">
+      <c r="C8" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" spans="3:3">
-      <c r="C9" s="4" t="s">
+    <row r="9" s="5" customFormat="1" spans="3:3">
+      <c r="C9" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" spans="3:3">
-      <c r="C10" s="4" t="s">
+    <row r="10" s="5" customFormat="1" spans="3:3">
+      <c r="C10" s="5" t="s">
         <v>256</v>
       </c>
     </row>
@@ -7762,13 +13495,13 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240229</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
@@ -8011,18 +13744,18 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="1" spans="2:2">
-      <c r="B9" s="5" t="s">
+    <row r="9" s="6" customFormat="1" spans="2:2">
+      <c r="B9" s="6" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="10" s="5" customFormat="1" spans="2:2">
-      <c r="B10" s="5" t="s">
+    <row r="10" s="6" customFormat="1" spans="2:2">
+      <c r="B10" s="6" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="11" s="5" customFormat="1" spans="3:3">
-      <c r="C11" s="5" t="s">
+    <row r="11" s="6" customFormat="1" spans="3:3">
+      <c r="C11" s="6" t="s">
         <v>276</v>
       </c>
     </row>
@@ -8176,7 +13909,7 @@
       <c r="A2">
         <v>20240406</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>297</v>
       </c>
     </row>
@@ -8185,8 +13918,8 @@
         <v>298</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" spans="2:2">
-      <c r="B4" s="4" t="s">
+    <row r="4" s="5" customFormat="1" spans="2:2">
+      <c r="B4" s="5" t="s">
         <v>299</v>
       </c>
     </row>
@@ -8369,52 +14102,52 @@
       </c>
     </row>
     <row r="9" spans="4:4">
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="10" spans="4:4">
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="11" spans="4:4">
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="12" spans="4:4">
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" spans="3:3">
-      <c r="C13" s="4" t="s">
+    <row r="13" s="5" customFormat="1" spans="3:3">
+      <c r="C13" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" spans="4:4">
-      <c r="D14" s="4" t="s">
+    <row r="14" s="5" customFormat="1" spans="4:4">
+      <c r="D14" s="5" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" spans="4:4">
-      <c r="D15" s="4" t="s">
+    <row r="15" s="5" customFormat="1" spans="4:4">
+      <c r="D15" s="5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="16" s="4" customFormat="1" spans="4:4">
-      <c r="D16" s="4" t="s">
+    <row r="16" s="5" customFormat="1" spans="4:4">
+      <c r="D16" s="5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="17" s="4" customFormat="1" spans="4:4">
-      <c r="D17" s="4" t="s">
+    <row r="17" s="5" customFormat="1" spans="4:4">
+      <c r="D17" s="5" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1" spans="4:4">
-      <c r="D18" s="4" t="s">
+    <row r="18" s="5" customFormat="1" spans="4:4">
+      <c r="D18" s="5" t="s">
         <v>325</v>
       </c>
     </row>
@@ -8623,7 +14356,7 @@
       </c>
     </row>
     <row r="29" spans="3:3">
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>357</v>
       </c>
     </row>
@@ -8821,28 +14554,28 @@
         <v>382</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" spans="2:2">
-      <c r="B3" s="4" t="s">
+    <row r="3" s="5" customFormat="1" spans="2:2">
+      <c r="B3" s="5" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" spans="3:3">
-      <c r="C4" s="4" t="s">
+    <row r="4" s="5" customFormat="1" spans="3:3">
+      <c r="C4" s="5" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" spans="3:3">
-      <c r="C5" s="4" t="s">
+    <row r="5" s="5" customFormat="1" spans="3:3">
+      <c r="C5" s="5" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" spans="3:3">
-      <c r="C6" s="4" t="s">
+    <row r="6" s="5" customFormat="1" spans="3:3">
+      <c r="C6" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>387</v>
       </c>
     </row>
@@ -9089,8 +14822,8 @@
         <v>416</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" spans="3:3">
-      <c r="C6" s="4" t="s">
+    <row r="6" s="5" customFormat="1" spans="3:3">
+      <c r="C6" s="5" t="s">
         <v>417</v>
       </c>
     </row>
@@ -9481,8 +15214,8 @@
         <v>484</v>
       </c>
     </row>
-    <row r="25" s="4" customFormat="1" spans="4:4">
-      <c r="D25" s="4" t="s">
+    <row r="25" s="5" customFormat="1" spans="4:4">
+      <c r="D25" s="5" t="s">
         <v>485</v>
       </c>
     </row>
@@ -9491,8 +15224,8 @@
         <v>486</v>
       </c>
     </row>
-    <row r="27" s="4" customFormat="1" spans="4:4">
-      <c r="D27" s="4" t="s">
+    <row r="27" s="5" customFormat="1" spans="4:4">
+      <c r="D27" s="5" t="s">
         <v>487</v>
       </c>
     </row>
@@ -9556,90 +15289,90 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240302</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="C4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="C5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="C6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="C7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
       <c r="C8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" s="4" customFormat="1" spans="2:2">
-      <c r="B10" s="4" t="s">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" s="5" customFormat="1" spans="2:2">
+      <c r="B10" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" spans="3:3">
-      <c r="C11" s="4" t="s">
+    <row r="11" s="5" customFormat="1" spans="3:3">
+      <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" spans="3:3">
-      <c r="C12" s="4" t="s">
+    <row r="12" s="5" customFormat="1" spans="3:3">
+      <c r="C12" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" spans="3:3">
-      <c r="C13" s="4" t="s">
+    <row r="13" s="5" customFormat="1" spans="3:3">
+      <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11798,7 +17531,7 @@
       </c>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="4" t="s">
         <v>814</v>
       </c>
     </row>
@@ -11867,69 +17600,69 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240303</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11989,17 +17722,17 @@
       </c>
     </row>
     <row r="3" spans="3:3">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>819</v>
       </c>
     </row>
     <row r="4" spans="3:3">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>820</v>
       </c>
     </row>
     <row r="5" spans="3:3">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>821</v>
       </c>
     </row>
@@ -12024,7 +17757,7 @@
       </c>
     </row>
     <row r="10" spans="3:3">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>826</v>
       </c>
     </row>
@@ -12044,17 +17777,17 @@
       </c>
     </row>
     <row r="14" spans="3:3">
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="15" spans="3:3">
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>831</v>
       </c>
     </row>
     <row r="16" spans="3:3">
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>832</v>
       </c>
     </row>
@@ -12062,7 +17795,7 @@
       <c r="B17" t="s">
         <v>833</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
@@ -12070,7 +17803,7 @@
       </c>
     </row>
     <row r="19" spans="3:3">
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>835</v>
       </c>
     </row>
@@ -12080,7 +17813,7 @@
       </c>
     </row>
     <row r="21" spans="3:3">
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>837</v>
       </c>
     </row>
@@ -12370,17 +18103,17 @@
       </c>
     </row>
     <row r="79" spans="3:3">
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>895</v>
       </c>
     </row>
     <row r="80" spans="3:3">
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="81" spans="3:3">
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>897</v>
       </c>
     </row>
@@ -12390,7 +18123,7 @@
       </c>
     </row>
     <row r="83" spans="4:4">
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="3" t="s">
         <v>899</v>
       </c>
     </row>
@@ -13828,133 +19561,133 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240304</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3"/>
-      <c r="C18" s="3" t="s">
+      <c r="A18" s="4"/>
+      <c r="C18" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3"/>
-      <c r="D19" s="3" t="s">
+      <c r="A19" s="4"/>
+      <c r="D19" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" spans="4:4">
-      <c r="D20" s="3"/>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14987,13 +20720,13 @@
       <c r="O1"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240306</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
@@ -15844,7 +21577,7 @@
       <c r="O1"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240307</v>
       </c>
       <c r="B2" t="s">
@@ -16743,51 +22476,51 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>20240308</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17713,7 +23446,7 @@
       <c r="A2">
         <v>20240309</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
@@ -17803,12 +23536,12 @@
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>105</v>
       </c>
     </row>

--- a/工作日志.xlsx
+++ b/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="203" activeTab="210"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="209" activeTab="206"/>
   </bookViews>
   <sheets>
     <sheet name="20240225" sheetId="89" r:id="rId1"/>
@@ -218,6 +218,7 @@
     <sheet name="20251125" sheetId="225" r:id="rId209"/>
     <sheet name="20251126" sheetId="226" r:id="rId210"/>
     <sheet name="20251127" sheetId="227" r:id="rId211"/>
+    <sheet name="20251128" sheetId="228" r:id="rId212"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -259,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="4110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="4311">
   <si>
     <t>SRAM和DRAM的比较</t>
   </si>
@@ -10667,7 +10668,7 @@
     <t>建立一个新民主主义的中国</t>
   </si>
   <si>
-    <t>标志着党在政治上（政治路线）、思想上（毛泽东思想）、组织上（中央领导集体）走向成熟</t>
+    <t>标志着党在政治上（政治路线）、思想上（毛泽东思想）、组织上（中央领导集体）完全成熟</t>
   </si>
   <si>
     <t>宪法明确了国家未来建设发展的根本任务和总目标### ###</t>
@@ -11309,7 +11310,7 @@
     <t>我国属于创新国家行列，但不是###前列###（填写位置）</t>
   </si>
   <si>
-    <t>2025欧亚经济论坛的主题是###聚合欧耶新动能，共筑可持续发展新格局###（填写主题）</t>
+    <t>2025欧亚经济论坛的主题是###聚合欧亚新动能，共筑可持续发展新格局###（填写主题）</t>
   </si>
   <si>
     <t>任何成功的实践都是###科学尺度和人本尺度的统一###（填写统一）</t>
@@ -12816,6 +12817,609 @@
   </si>
   <si>
     <t>直到pattern[temp]和pattern[next[temp]]不相同</t>
+  </si>
+  <si>
+    <t>某点极限存在可以推出存在一个处处有定义的去心邻域### ###</t>
+  </si>
+  <si>
+    <t>党生存发展第一位的问题是方向问题### ###</t>
+  </si>
+  <si>
+    <t>坚持正确政治方向</t>
+  </si>
+  <si>
+    <t>旗帜鲜明讲政治</t>
+  </si>
+  <si>
+    <t>保证党的团结和集中统一</t>
+  </si>
+  <si>
+    <t>党思想、政治、组织路线的确立### ###</t>
+  </si>
+  <si>
+    <t>首次确立：整风运动（1941-1945）奠定基础，七大（1945）正式确立</t>
+  </si>
+  <si>
+    <t>思想路线：实事求是的马克思主义</t>
+  </si>
+  <si>
+    <t>政治路线：放手发动群众、壮大人民力量</t>
+  </si>
+  <si>
+    <t>组织路线：以毛泽东为核心的党的第一代中央领导集体</t>
+  </si>
+  <si>
+    <t>重新确立：十一届三中全会（1978）</t>
+  </si>
+  <si>
+    <t>思想路线：解放思想、实事求是的马克思主义</t>
+  </si>
+  <si>
+    <t>政治路线：结束以阶级斗争为纲，工作重心到经济建设</t>
+  </si>
+  <si>
+    <t>组织路线：以邓小平为核心的党的第二代中央领导集体</t>
+  </si>
+  <si>
+    <t>作风建设的三个关乎### ###</t>
+  </si>
+  <si>
+    <t>关乎党的性质</t>
+  </si>
+  <si>
+    <t>关乎人心向背</t>
+  </si>
+  <si>
+    <t>关乎事业成败</t>
+  </si>
+  <si>
+    <t>新时代我国民主政治领域具有重大创新意义的标志性成果是全过程民主### ###</t>
+  </si>
+  <si>
+    <t>十八大提出的新概念</t>
+  </si>
+  <si>
+    <t>民主形态：片段化到全链条（选举、协商、决策、管理、监督）</t>
+  </si>
+  <si>
+    <t>民主覆盖：从局部到全方位（覆盖经济、政治、文化等）</t>
+  </si>
+  <si>
+    <t>民主效能：从形式到实质（四个统一）</t>
+  </si>
+  <si>
+    <t>过程与成果统一</t>
+  </si>
+  <si>
+    <t>程序与实质统一</t>
+  </si>
+  <si>
+    <t>直接与间接统一</t>
+  </si>
+  <si>
+    <t>人民民主与国家意志统一</t>
+  </si>
+  <si>
+    <t>制度保障：松散到系统（系统化、制度化、写入宪法修正案）</t>
+  </si>
+  <si>
+    <t>作风问题的核心是党同人民群众的关系问题### ###</t>
+  </si>
+  <si>
+    <t>作风建设的关键是保持党同人民群众的血肉联系### ###</t>
+  </si>
+  <si>
+    <t>建设文化强国，事关### ###</t>
+  </si>
+  <si>
+    <t>中国式现代化建设全局</t>
+  </si>
+  <si>
+    <t>中华民族复兴大业</t>
+  </si>
+  <si>
+    <t>提升国际竞争力</t>
+  </si>
+  <si>
+    <t>文化### ###</t>
+  </si>
+  <si>
+    <t>生命力、本质特征在于创新创造</t>
+  </si>
+  <si>
+    <t>创造核心在人</t>
+  </si>
+  <si>
+    <t>文化企业应该做到### ###</t>
+  </si>
+  <si>
+    <t>坚持把社会效益放在首位</t>
+  </si>
+  <si>
+    <t>实现社会效益和经济效益的相统一</t>
+  </si>
+  <si>
+    <t>文化遗产保护的原则### ###</t>
+  </si>
+  <si>
+    <t>保护第一</t>
+  </si>
+  <si>
+    <t>合理利用</t>
+  </si>
+  <si>
+    <t>最小干预</t>
+  </si>
+  <si>
+    <t>国家综合创新能力排名还没达到世界第一### ###</t>
+  </si>
+  <si>
+    <t>三大国际科创中心：北京、上海、粤港澳大湾区### ###</t>
+  </si>
+  <si>
+    <t>区域创新新格局是### ###</t>
+  </si>
+  <si>
+    <t>高地引领</t>
+  </si>
+  <si>
+    <t>梯次联动</t>
+  </si>
+  <si>
+    <t>优势互补</t>
+  </si>
+  <si>
+    <t>工人阶级是我们社会主义国家的领导阶级### ###</t>
+  </si>
+  <si>
+    <t>我们和拉美及加勒比国家的共同追求是公平正义### ###</t>
+  </si>
+  <si>
+    <t>中拉五大工程### ###</t>
+  </si>
+  <si>
+    <t>（首位）团结工程</t>
+  </si>
+  <si>
+    <t>发展工程</t>
+  </si>
+  <si>
+    <t>文明工程</t>
+  </si>
+  <si>
+    <t>和平工程</t>
+  </si>
+  <si>
+    <t>民心工程</t>
+  </si>
+  <si>
+    <t>中俄关系稳定发展的根本保障是元首引领### ###</t>
+  </si>
+  <si>
+    <t>鲜明特征是长期睦邻友好、互利合作共赢</t>
+  </si>
+  <si>
+    <t>主席强调中俄要</t>
+  </si>
+  <si>
+    <t>坚持世代友好（苏联老大哥）</t>
+  </si>
+  <si>
+    <t>坚持互利共赢（你的能源，我的技术）</t>
+  </si>
+  <si>
+    <t>坚持公平正义（反法西斯）</t>
+  </si>
+  <si>
+    <t>坚持和衷共济（对抗美帝）</t>
+  </si>
+  <si>
+    <t>Prim算法### ###</t>
+  </si>
+  <si>
+    <t>三个数据结构</t>
+  </si>
+  <si>
+    <t>已访问点（已加入生成树的点）集合</t>
+  </si>
+  <si>
+    <t>小根堆，存储边，方便选出权最小的边</t>
+  </si>
+  <si>
+    <t>结果列表，存储最终生成树的边</t>
+  </si>
+  <si>
+    <t>从某一顶点（生成树的根节点）出发，加入已访问点</t>
+  </si>
+  <si>
+    <t>将出发点所连的边加入小根堆，按边权排序，最小最先出堆</t>
+  </si>
+  <si>
+    <t>循环</t>
+  </si>
+  <si>
+    <t>小根堆出堆最短边</t>
+  </si>
+  <si>
+    <t>最短边的另一头节点如果不在已访问集合</t>
+  </si>
+  <si>
+    <t>则接受该边，加入结果列表</t>
+  </si>
+  <si>
+    <t>节点加入访问集合</t>
+  </si>
+  <si>
+    <t>最短边的另一头节点如果已在已访问集合</t>
+  </si>
+  <si>
+    <t>跳过该边</t>
+  </si>
+  <si>
+    <t>和Dijkstra有相似之处，但区别也很大</t>
+  </si>
+  <si>
+    <t>秦国的远交近攻</t>
+  </si>
+  <si>
+    <t>Kruskal算法### ###</t>
+  </si>
+  <si>
+    <t>对边按权重排序</t>
+  </si>
+  <si>
+    <t>依次加边</t>
+  </si>
+  <si>
+    <t>无环继续，有环跳过</t>
+  </si>
+  <si>
+    <t>人力判环很简单</t>
+  </si>
+  <si>
+    <t>机器判环很复杂</t>
+  </si>
+  <si>
+    <t>需要使用并查集</t>
+  </si>
+  <si>
+    <t>并查集### ###</t>
+  </si>
+  <si>
+    <t>常规操作：正常状况下，各节点指向自己</t>
+  </si>
+  <si>
+    <t>查找：递归查，直到某个节点指向他自己</t>
+  </si>
+  <si>
+    <t>合并：合并后，子节点指向根节点，树合并的根节点指向另一个根节点</t>
+  </si>
+  <si>
+    <t>优化操作</t>
+  </si>
+  <si>
+    <t>查找</t>
+  </si>
+  <si>
+    <t>路径压缩：第一次查找完成后，回溯节点全部连到根，单链就变直连</t>
+  </si>
+  <si>
+    <t>合并</t>
+  </si>
+  <si>
+    <t>按大小合并：根节点记录集合大小，小集合从属于大集合</t>
+  </si>
+  <si>
+    <t>按秩合并：根节点记录集合高度，矮集合从属于高集合</t>
+  </si>
+  <si>
+    <t>线索二叉树### ###</t>
+  </si>
+  <si>
+    <t>用空指针指向前中后序的前驱（左）后继（右）节点</t>
+  </si>
+  <si>
+    <t>佛洛依德算法### ###</t>
+  </si>
+  <si>
+    <t>两个矩阵：邻接矩阵和路径前驱矩阵</t>
+  </si>
+  <si>
+    <t>逐点遍历：</t>
+  </si>
+  <si>
+    <t>当遍历节点作为中间节点时，其它点对路径是否变短</t>
+  </si>
+  <si>
+    <t>如果变短，则更新，并且设置路径前驱矩阵</t>
+  </si>
+  <si>
+    <t>不能则保留原值</t>
+  </si>
+  <si>
+    <t>遍历完成后，根据前驱矩阵输出路径</t>
+  </si>
+  <si>
+    <t>比如A到B，看B的前驱是C，C加入A到B之间的空位</t>
+  </si>
+  <si>
+    <t>问题变为A到C，看C的前驱是D，D加入到A和C之间的空位</t>
+  </si>
+  <si>
+    <t>问题变为A到D，看D的前驱是A，说明二者直连，路径完成</t>
+  </si>
+  <si>
+    <t>进程资源图检测死锁### ###</t>
+  </si>
+  <si>
+    <t>理解图形</t>
+  </si>
+  <si>
+    <t>圆形：进程节点</t>
+  </si>
+  <si>
+    <t>大方块：资源类型节点</t>
+  </si>
+  <si>
+    <t>大方块里的小圆点：资源实例</t>
+  </si>
+  <si>
+    <t>进程指向资源：进程请求新的资源</t>
+  </si>
+  <si>
+    <t>资源指向进程：资源已经分给进程</t>
+  </si>
+  <si>
+    <t>大循环：如果一轮循环当中发生改变，则继续</t>
+  </si>
+  <si>
+    <t>小循环：对每个进程节点进行遍历</t>
+  </si>
+  <si>
+    <t>如果大方块里的闲置资源能够满足进程请求</t>
+  </si>
+  <si>
+    <t>那就把进程连同它对资源的占用（被指向的边）一起消除</t>
+  </si>
+  <si>
+    <t>中俄两国关系的精神内核是### ###</t>
+  </si>
+  <si>
+    <t>永久睦邻友好</t>
+  </si>
+  <si>
+    <t>全面战略协作</t>
+  </si>
+  <si>
+    <t>互利合作共赢</t>
+  </si>
+  <si>
+    <t>构建人类命运共同体的重要依托### ###</t>
+  </si>
+  <si>
+    <t>全球发展倡议</t>
+  </si>
+  <si>
+    <t>全球安全倡议</t>
+  </si>
+  <si>
+    <t>全球文明倡议</t>
+  </si>
+  <si>
+    <t>坚持和维护联合国权威，需要维护### ###</t>
+  </si>
+  <si>
+    <t>以联合国为核心的国际体系</t>
+  </si>
+  <si>
+    <t>以国际法为基础的国际秩序</t>
+  </si>
+  <si>
+    <t>以联合国宪章宗旨和原则为基础的国际关系基本准则</t>
+  </si>
+  <si>
+    <t>中美分歧的关键### ###</t>
+  </si>
+  <si>
+    <t>尊重彼此核心利益和重大关切</t>
+  </si>
+  <si>
+    <t>找到妥善解决问题的办法</t>
+  </si>
+  <si>
+    <t>中美关系的原则### ###</t>
+  </si>
+  <si>
+    <t>相互尊重</t>
+  </si>
+  <si>
+    <t>和平共处</t>
+  </si>
+  <si>
+    <t>合作共赢</t>
+  </si>
+  <si>
+    <t>中美关系的维护需要### ###</t>
+  </si>
+  <si>
+    <t>用好已建立的经贸磋商机制</t>
+  </si>
+  <si>
+    <t>秉持平等态度</t>
+  </si>
+  <si>
+    <t>尊重各自关切</t>
+  </si>
+  <si>
+    <t>争取双赢结果</t>
+  </si>
+  <si>
+    <t>台湾问题是中美关系政治基础中的基础### ###</t>
+  </si>
+  <si>
+    <t>反对滥施关税的立场### ###</t>
+  </si>
+  <si>
+    <t>各国应当维护以联合国为核心的国际体系</t>
+  </si>
+  <si>
+    <t>中欧建交的重要经验和启示### ###</t>
+  </si>
+  <si>
+    <t>求同存异</t>
+  </si>
+  <si>
+    <t>开放合作</t>
+  </si>
+  <si>
+    <t>互利共赢</t>
+  </si>
+  <si>
+    <t>中欧很远，根本没有地缘政治关系，也就不可能有地缘政治矛盾### ###</t>
+  </si>
+  <si>
+    <t>我国幅员辽阔、边界线长，周边是### ###</t>
+  </si>
+  <si>
+    <t>实现发展繁荣的重要基础</t>
+  </si>
+  <si>
+    <t>维护国家安全的重点</t>
+  </si>
+  <si>
+    <t>运筹外交全局的首要</t>
+  </si>
+  <si>
+    <t>推动构建人类命运共同体的关键</t>
+  </si>
+  <si>
+    <t>全球供应链格局的根本性重组不会因为一个链博会的持续举办就实现### ###</t>
+  </si>
+  <si>
+    <t>资本主义基本矛盾运动的阶段性：缓和-&gt;尖锐-&gt;再缓和-&gt;再尖锐### ###</t>
+  </si>
+  <si>
+    <t>再生产的周期性是由于经济危机的周期性导致的，两者的因果不能倒过来### ###</t>
+  </si>
+  <si>
+    <t>如果没有经济危机，再生产导致生产规模扩大不会停止</t>
+  </si>
+  <si>
+    <t>毛主席在1940年写的《新民主主义论》阐述了新民主主义的政治、经济和文化### ###</t>
+  </si>
+  <si>
+    <t>他在1945年写的《论联合政府》将前三者与党的基本纲领联系、具体化，形成了新民主主义的基本纲领</t>
+  </si>
+  <si>
+    <t>马克思主义同中国实际的第二次结合是在1956年4月4日由毛主席在中共中央书记处会议上正式提出的### ###</t>
+  </si>
+  <si>
+    <t>完成则是在1978年后的改革开放和中国特色社会主义道路开辟后</t>
+  </si>
+  <si>
+    <t>十五五的着眼点是为基本实现社会主义现代化目标奠定更加坚实的基础### ###</t>
+  </si>
+  <si>
+    <t>虚拟实践可以对现实的实践活动产生重大影响### ###</t>
+  </si>
+  <si>
+    <t>对人民群众创造历史的活动有着首要、决定性影响的是经济条件### ###</t>
+  </si>
+  <si>
+    <t>原材料和机器都是不变资本，是因为### ###</t>
+  </si>
+  <si>
+    <t>它们不改变自己的价值量</t>
+  </si>
+  <si>
+    <t>不发生增殖</t>
+  </si>
+  <si>
+    <t>垄断不能消除竞争，但垄断确实是自由竞争的对立面### ###</t>
+  </si>
+  <si>
+    <t>意识形态工作的主阵地、主战场是网络空间### ###</t>
+  </si>
+  <si>
+    <t>发展心智生产力不能忽视、放弃传统产业### ###</t>
+  </si>
+  <si>
+    <t>法治思维是一种规范思维、逻辑思维、科学思维、正当性思维### ###</t>
+  </si>
+  <si>
+    <t>中国特色社会主义的时间点### ###</t>
+  </si>
+  <si>
+    <t>理论主题的形成是1982年的十二大</t>
+  </si>
+  <si>
+    <t>理论轮廓的形成是十三大</t>
+  </si>
+  <si>
+    <t>理论和实践的进一步成熟是十七大</t>
+  </si>
+  <si>
+    <t>谱写新时代新篇章是十八大以后</t>
+  </si>
+  <si>
+    <t>解决人民内部矛盾的具体方针是团结-批评-团结### ###</t>
+  </si>
+  <si>
+    <t>二十大的六个必须坚持### ###</t>
+  </si>
+  <si>
+    <t>人民至上是根本价值立场</t>
+  </si>
+  <si>
+    <t>自信自立是内在精神特质</t>
+  </si>
+  <si>
+    <t>守正创新是显著标识，也是主要着力点</t>
+  </si>
+  <si>
+    <t>问题导向是鲜明风格</t>
+  </si>
+  <si>
+    <t>系统观念是基本思想方法和工作方法</t>
+  </si>
+  <si>
+    <t>胸怀天下是大视野大境界</t>
+  </si>
+  <si>
+    <t>新质生产力的核心标志是全要素生产率大幅提升### ###</t>
+  </si>
+  <si>
+    <t>中共一大建党时，讨论实际工作计划，决定首先集中精力组织工人### ###</t>
+  </si>
+  <si>
+    <t>建设中特法治体系的重点是建设高效的法治实施体系### ###</t>
+  </si>
+  <si>
+    <t>现有的法律已经很完备了，不是重点</t>
+  </si>
+  <si>
+    <t>现有的监督机制也很有效，不是重点</t>
+  </si>
+  <si>
+    <t>作为保障的法治人才更是不缺</t>
+  </si>
+  <si>
+    <t>比如知心姐姐和春风法官</t>
+  </si>
+  <si>
+    <t>生产关系是生产的社会形式，和生产力一起组成社会的生产方式### ###</t>
+  </si>
+  <si>
+    <t>七大是三个成熟，而遵义是三个走向成熟### ###</t>
+  </si>
+  <si>
+    <t>三个：政治、思想、组织</t>
+  </si>
+  <si>
+    <t>敌后游击战在战略相持阶段变为主要的抗日作战方式（光头佬开始摸鱼了）### ###</t>
+  </si>
+  <si>
+    <t>公义胜私欲是中华传统美德的根本要求### ###</t>
   </si>
 </sst>
 </file>
@@ -37687,31 +38291,31 @@
         <v>69.65</v>
       </c>
       <c r="B1" s="1">
-        <f>COUNTA(B2:B2124)/COLUMN()</f>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2124)/COLUMN()</f>
         <v>30</v>
       </c>
       <c r="C1" s="1">
-        <f>COUNTA(C2:C2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="D1" s="1">
-        <f>COUNTA(D2:D2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>8.25</v>
       </c>
       <c r="E1" s="1">
-        <f>COUNTA(E2:E2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="F1" s="1">
-        <f>COUNTA(F2:F2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G1" s="1">
-        <f>COUNTA(G2:G2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H1" s="1">
-        <f>COUNTA(H2:H2124)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -38683,31 +39287,31 @@
         <v>99.35</v>
       </c>
       <c r="B1" s="1">
-        <f>COUNTA(B2:B2134)/COLUMN()</f>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2134)/COLUMN()</f>
         <v>47</v>
       </c>
       <c r="C1" s="1">
-        <f>COUNTA(C2:C2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="D1" s="1">
-        <f>COUNTA(D2:D2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>11.75</v>
       </c>
       <c r="E1" s="1">
-        <f>COUNTA(E2:E2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="F1" s="1">
-        <f>COUNTA(F2:F2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G1" s="1">
-        <f>COUNTA(G2:G2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H1" s="1">
-        <f>COUNTA(H2:H2134)/COLUMN()</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -50553,7 +51157,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667"/>
@@ -50562,19 +51166,19 @@
     <row r="1" spans="1:8">
       <c r="A1" s="1">
         <f>SUM(B1:AZ1)</f>
-        <v>2.67619047619048</v>
+        <v>26.1761904761905</v>
       </c>
       <c r="B1" s="1">
         <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2193)/COLUMN()</f>
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="C1" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1">
         <f t="shared" si="0"/>
@@ -50645,6 +51249,1072 @@
     <row r="11" spans="1:8">
       <c r="G11" t="s">
         <v>4109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="C14" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="C15" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="C16" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="D19" t="s">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="D20" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="D21" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="C22" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="D23" t="s">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="D24" t="s">
+        <v>4122</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="D25" t="s">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="C27" t="s">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="C29" t="s">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="C31" t="s">
+        <v>4129</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="C32" t="s">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33" t="s">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="D35" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="D36" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37" t="s">
+        <v>4135</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="D38" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="C39" t="s">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="C43" t="s">
+        <v>4141</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="C44" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="C45" t="s">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="C47" t="s">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="C48" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" t="s">
+        <v>4147</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="C50" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="C51" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="C53" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="C54" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="C55" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="C59" t="s">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="C60" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="C61" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" t="s">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" t="s">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="C65" t="s">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="C66" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="C67" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="C68" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="C69" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="C71" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="C72" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="D73" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="D74" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="D75" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="D76" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet212.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:H138"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>48.95</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2197)/COLUMN()</f>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.2</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="D4" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="D5" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="D6" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="C7" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="C8" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="C9" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="D10" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" t="s">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="E12" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="E13" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="D14" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="E15" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="C16" t="s">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="C17" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="C19" t="s">
+        <v>4192</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="C20" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="C21" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="D23" t="s">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="E24" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="C26" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="D27" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="D28" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="C29" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="D30" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="E31" t="s">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="D32" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="E33" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="E34" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" t="s">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="C36" t="s">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="C38" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="C39" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="D40" t="s">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="E41" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="E42" t="s">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="C43" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="D44" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="D45" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="D46" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="C48" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="D49" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="D50" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="D51" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="D52" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="D53" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="C54" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="D55" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="E56" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="E57" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="C59" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="C60" t="s">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="C61" t="s">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" t="s">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="C63" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="C64" t="s">
+        <v>4237</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="C65" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" t="s">
+        <v>4239</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="C67" t="s">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="C68" t="s">
+        <v>4241</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="C69" t="s">
+        <v>4242</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="C71" t="s">
+        <v>4244</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="C72" t="s">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73" t="s">
+        <v>4246</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="C74" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3">
+      <c r="C75" t="s">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="C76" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="C78" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="C79" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="C80" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="C81" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" t="s">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="C84" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85" t="s">
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="C86" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="C87" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="C88" t="s">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="C89" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="C92" t="s">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="C93" t="s">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="C94" t="s">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="C95" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" t="s">
+        <v>4268</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="C99" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="B100" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="C101" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="B102" t="s">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3">
+      <c r="C103" t="s">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104" t="s">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105" t="s">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="B106" t="s">
+        <v>4278</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="B107" t="s">
+        <v>4279</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="C108" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="C109" t="s">
+        <v>4281</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="B110" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="B111" t="s">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3">
+      <c r="B112" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113" t="s">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="C115" t="s">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="C116" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="C117" t="s">
+        <v>4289</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="C118" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="B119" t="s">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="B120" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3">
+      <c r="C121" t="s">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="C122" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3">
+      <c r="C123" t="s">
+        <v>4295</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="C124" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="C125" t="s">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3">
+      <c r="C126" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127" t="s">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3">
+      <c r="B128" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" t="s">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="C130" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="C131" t="s">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="C132" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="D133" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" t="s">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" t="s">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="C136" t="s">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" t="s">
+        <v>4310</v>
       </c>
     </row>
   </sheetData>

--- a/工作日志.xlsx
+++ b/工作日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="209" activeTab="206"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="206" activeTab="214"/>
   </bookViews>
   <sheets>
     <sheet name="20240225" sheetId="89" r:id="rId1"/>
@@ -219,6 +219,9 @@
     <sheet name="20251126" sheetId="226" r:id="rId210"/>
     <sheet name="20251127" sheetId="227" r:id="rId211"/>
     <sheet name="20251128" sheetId="228" r:id="rId212"/>
+    <sheet name="20251129" sheetId="229" r:id="rId213"/>
+    <sheet name="20251130" sheetId="230" r:id="rId214"/>
+    <sheet name="20251201" sheetId="232" r:id="rId215"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -260,7 +263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4335" uniqueCount="4311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4493" uniqueCount="4469">
   <si>
     <t>SRAM和DRAM的比较</t>
   </si>
@@ -4587,7 +4590,7 @@
     <t>反常积分求解中使用了分部积分或者本身就含加减的形式，导致需要分别对子段积分求解</t>
   </si>
   <si>
-    <t>需要注意，如果出现###子段积分的结果含无穷###，意味着###子段积分的无穷量需要与另一子段积分进行抵消###</t>
+    <t>需要注意，如果出现子段积分的结果含无穷，意味着###子段积分的无穷量需要与另一子段积分进行抵消###</t>
   </si>
   <si>
     <t>前提是计算题</t>
@@ -4626,7 +4629,7 @@
     <t>从补码加法的结果也是补码来考虑，相当于结果是个###负数###（正数/负数）</t>
   </si>
   <si>
-    <t>否则，无论被减数最高位是0还是1，加上进位后都应该是###1###</t>
+    <t>否则，无论被减数原始最高位是0还是1，加上进位后都应该是###1###</t>
   </si>
   <si>
     <t>只有这样，被减数加上进位后才能加上减数相反数补码的最高位，使其###变回0###，也就是###正数###（正数/负数）</t>
@@ -4644,7 +4647,7 @@
     <t>一个矩阵和它的伴随矩阵的伴随矩阵的关系</t>
   </si>
   <si>
-    <t>A*=###A'|A|###</t>
+    <t>A*=###A逆|A|###（A是可逆矩阵的话）</t>
   </si>
   <si>
     <t>A**=###(A*)'###（矩阵）乘以###|A*|###（系数）</t>
@@ -4668,7 +4671,7 @@
     <t>（不严谨，秒杀用！）</t>
   </si>
   <si>
-    <t>注意，ln(1+x)的定义域比ln(1+x)小，这里只做同定义域的比较</t>
+    <t>注意，ln(1+x)的定义域比x/(x+1)小，这里只做同定义域的比较</t>
   </si>
   <si>
     <t>x/(x+1)=###1-1/(x+1)###</t>
@@ -4755,7 +4758,7 @@
     <t>极坐标的面积微元是个###扇环###（形状）</t>
   </si>
   <si>
-    <t>面积近似为###内弧长度*半径###</t>
+    <t>面积近似为###内弧长度*半径差值###（公式）</t>
   </si>
   <si>
     <t>其中，###半径###就是dr</t>
@@ -4800,16 +4803,16 @@
     <t>瑕积分和反常积分的概念辨析</t>
   </si>
   <si>
-    <t>反常积分指被积函数###存在导致无界的点或者积分上下限有无穷###</t>
-  </si>
-  <si>
-    <t>瑕积分指被积函数###在某点无界###，和反常积分的关系？###瑕积分是反常积分的一种###</t>
+    <t>反常积分指被积函数###存在导致无界的点###或者积分上下限###有无穷###</t>
+  </si>
+  <si>
+    <t>瑕积分指被积函数###在积分区间上某点无界###，和反常积分的关系？###瑕积分是反常积分的一种###</t>
   </si>
   <si>
     <t>一个积分可能有间断点，但只有###间断点无界###，这个积分才是瑕积分（反常积分）</t>
   </si>
   <si>
-    <t>间断点震荡###不行###（行/不行），参考Int(0,1):sin(1/x)dx</t>
+    <t>有界间断点震荡###不行###（行/不行），参考Int(0,1):sin(1/x)dx</t>
   </si>
   <si>
     <t>二重积分想要利用奇偶性时，如果被积函数本身非奇非偶，可以进行变形拆分，拆出奇函数为佳### ###（无需作答）</t>
@@ -4902,7 +4905,7 @@
     <t>以y'=p</t>
   </si>
   <si>
-    <t>那么y''=###dp/dy###</t>
+    <t>那么y''=###dp/dx###</t>
   </si>
   <si>
     <t>把y看成自变量</t>
@@ -5124,7 +5127,7 @@
     <t>那么lim(x-&gt;+∞):Int(0,x):f(t)dt/x=###Int(0,T):f(t)dt/T###</t>
   </si>
   <si>
-    <t>Int(0,x):f(t)dt可以写成###kx+h(x)###，其中h(x)是R上周期为T的函数，k为常数</t>
+    <t>Int(0,x):f(t)dt可以写成###kx+h(x)###，其中h(x)是R上周期为T的函数，k为f(t)在周期T内的平均值</t>
   </si>
   <si>
     <t>反常积分不能抵消，但是定积分可以！！！### ###（无需作答）</t>
@@ -5394,7 +5397,7 @@
     <t>异或除法，相同余0，不同余1</t>
   </si>
   <si>
-    <t>向后借位使###最高1位对齐###</t>
+    <t>向后借位使###最高1###位对齐</t>
   </si>
   <si>
     <t>无位可借，则###计算结束，被除数作为余数###</t>
@@ -12789,7 +12792,7 @@
     <t>前缀和后缀的交集中选择###最长的那个###（填写选择条件），取它的长度作为next[j]的元素</t>
   </si>
   <si>
-    <t>KMP（加强）### ###</t>
+    <t>KMP（nextval及补充笔记）### ###</t>
   </si>
   <si>
     <t>用目前的算法，指针跳转是不需要变的</t>
@@ -13420,6 +13423,480 @@
   </si>
   <si>
     <t>公义胜私欲是中华传统美德的根本要求### ###</t>
+  </si>
+  <si>
+    <t>AOE计算VE的时候就需要用到拓扑排序了### ###</t>
+  </si>
+  <si>
+    <t>f(x)的不可导点### ###</t>
+  </si>
+  <si>
+    <t>使绝对值部分为0的</t>
+  </si>
+  <si>
+    <t>分段函数的分界点</t>
+  </si>
+  <si>
+    <t>求导后分母为0的点</t>
+  </si>
+  <si>
+    <t>导致无界的往往是特殊点而不是常态无界，需要找无界范围就看特殊点### ###</t>
+  </si>
+  <si>
+    <t>无穷点是一种无界点</t>
+  </si>
+  <si>
+    <t>震荡发散也是一种无界点（比如sin(x)*x,x-&gt;∞）</t>
+  </si>
+  <si>
+    <t>再次强调，切线竖着的时候，导数无穷大不存在（不可导），切线存在不能推可导### ###</t>
+  </si>
+  <si>
+    <t>1927年的三湾改编在1929年的古田会议前就从组织上确立了党对军队的领导### ###</t>
+  </si>
+  <si>
+    <t>思想上确立≠组织上确立</t>
+  </si>
+  <si>
+    <t>竞争和信用是资本集中最强有力的杠杆### ###</t>
+  </si>
+  <si>
+    <t>最能体现毛泽东思想理论本质特点的思想内容是贯穿于毛泽东思想科学体系中的立场、观点和方法### ###</t>
+  </si>
+  <si>
+    <t>我国社会主义改造是伟大的历史性胜利，因为### ###</t>
+  </si>
+  <si>
+    <t>没有造成生产力破坏</t>
+  </si>
+  <si>
+    <t>没有引起社会动荡</t>
+  </si>
+  <si>
+    <t>我国社会主义发展阶段问题的科学理论是在改革开放后才形成### ###</t>
+  </si>
+  <si>
+    <t>创新创造是文化的生命所在、文化的本质特征### ###</t>
+  </si>
+  <si>
+    <t>我国现代化建设的出发点和落脚点是实现人民对美好生活的向往### ###</t>
+  </si>
+  <si>
+    <t>保路运动（1911）是辛亥革命的导火索### ###</t>
+  </si>
+  <si>
+    <t>二次革命是袁世凯刺杀宋教仁、解散国民党，暴露独裁野心，孙中山、黄兴讨袁失败### ###</t>
+  </si>
+  <si>
+    <t>护国运动是袁世凯称帝，蔡锷（护国将军）发动护国战争### ###</t>
+  </si>
+  <si>
+    <t>护法运动### ###</t>
+  </si>
+  <si>
+    <t>张勋（辫子军）复辟失败后，段祺瑞（枪杀学生的狗军阀）掌权，决绝恢复《中华民国临时约法》</t>
+  </si>
+  <si>
+    <t>孙中山联合西南军阀骑兵，后因军阀妥协失败，标志着旧民主主义革命的终结</t>
+  </si>
+  <si>
+    <t>人民战争战略进攻的序幕由千里跃进大别山揭开### ###</t>
+  </si>
+  <si>
+    <t>第一个五年计划集中主要力量发展重工业### ###</t>
+  </si>
+  <si>
+    <t>法律的普遍适用是指法律约束所有人，不可违反是指任何违反者必受罚### ###</t>
+  </si>
+  <si>
+    <t>社会发展的基础及决定力量是物质资料的生产方式（社会的生产方式）### ###</t>
+  </si>
+  <si>
+    <t>当代资本主义相比二战前的资本主义有哪些变化### ###</t>
+  </si>
+  <si>
+    <t>政治制度变化：</t>
+  </si>
+  <si>
+    <t>行政集权民主化</t>
+  </si>
+  <si>
+    <t>政治制度多元化与公民权利扩大</t>
+  </si>
+  <si>
+    <t>政策咨询机构是垄断资本集团影响政策的手段</t>
+  </si>
+  <si>
+    <t>法治建设强化</t>
+  </si>
+  <si>
+    <t>政党格局两极化</t>
+  </si>
+  <si>
+    <t>改良主义政党影响力扩大</t>
+  </si>
+  <si>
+    <t>经济结构变化：</t>
+  </si>
+  <si>
+    <t>所有制形式变革</t>
+  </si>
+  <si>
+    <t>经济调节机制转型</t>
+  </si>
+  <si>
+    <t>产业结构升级</t>
+  </si>
+  <si>
+    <t>社会结构变化</t>
+  </si>
+  <si>
+    <t>阶级结构复杂化</t>
+  </si>
+  <si>
+    <t>新中间阶级兴起</t>
+  </si>
+  <si>
+    <t>社会矛盾缓和</t>
+  </si>
+  <si>
+    <t>国际关系变化</t>
+  </si>
+  <si>
+    <t>资本全球化加速</t>
+  </si>
+  <si>
+    <t>国际经济协调机制形成</t>
+  </si>
+  <si>
+    <t>资本主义国家关系转变</t>
+  </si>
+  <si>
+    <t>空想社会主义的三个阶段### ###</t>
+  </si>
+  <si>
+    <t>家庭手工业：16-17世纪的早期空想社会主义</t>
+  </si>
+  <si>
+    <t>工场手工业：18世纪的空想平均共产主义</t>
+  </si>
+  <si>
+    <t>机器大工业：19世纪初期批判的空想社会主义</t>
+  </si>
+  <si>
+    <t>八一南昌起义建立军队，是中共独立领导革命战争、创建人民军队和武装夺取政权的开端### ###</t>
+  </si>
+  <si>
+    <t>物质先行，精神滞后是西方现代化模式### ###</t>
+  </si>
+  <si>
+    <t>我们注重两手抓，精神物质文明不分先后</t>
+  </si>
+  <si>
+    <t>推翻北洋军阀的北伐战争（1926年，正好是大革命时期）是在孙中山先生逝世后才发生的### ###</t>
+  </si>
+  <si>
+    <t>五四运动时，社会主义才能救中国并不是全社会所有人的普遍共识### ###</t>
+  </si>
+  <si>
+    <t>法治方式推动和保障法制宣传教育，有助于防止和减少社会矛盾发生### ###</t>
+  </si>
+  <si>
+    <t>不扶倒地者确实大幅降低了矛盾发生的可能</t>
+  </si>
+  <si>
+    <t>真零和无穷小### ###</t>
+  </si>
+  <si>
+    <t>真零：区间内处处为0的定值函数</t>
+  </si>
+  <si>
+    <t>特征：常数、区间内不变、与趋向无关</t>
+  </si>
+  <si>
+    <t>无穷小：趋0但不等于0</t>
+  </si>
+  <si>
+    <t>特征：变量、区间内可变、与趋向相关</t>
+  </si>
+  <si>
+    <t>穿根法的紧急补丁：1次根穿过不变凹凸性，3次及以上奇数次穿过必有拐点### ###</t>
+  </si>
+  <si>
+    <t>切线方程约束类问题### ###</t>
+  </si>
+  <si>
+    <t>在点(x0,y0)有公切线（两个曲线都在x0,y0有这条切线）</t>
+  </si>
+  <si>
+    <t>有、存在公切线（一条切线切于两曲线，可能在不同切点）</t>
+  </si>
+  <si>
+    <t>所谓配方法，其实就是相信后人的智慧### ###</t>
+  </si>
+  <si>
+    <t>多出来的后元平方交给后元来处理</t>
+  </si>
+  <si>
+    <t>政治分析题答题体系### ###</t>
+  </si>
+  <si>
+    <t>审题</t>
+  </si>
+  <si>
+    <t>设问类型：是什么/为什么/怎么做</t>
+  </si>
+  <si>
+    <t>怎么做：主体+领域分层作答</t>
+  </si>
+  <si>
+    <t>主体：党、政府、企业、个人</t>
+  </si>
+  <si>
+    <t>领域：经济、政治、文化</t>
+  </si>
+  <si>
+    <t>考查科目：根据关键词匹配</t>
+  </si>
+  <si>
+    <t>也就是缩写索引</t>
+  </si>
+  <si>
+    <t>破题</t>
+  </si>
+  <si>
+    <t>材料分析</t>
+  </si>
+  <si>
+    <t>显性信息：领导人讲话、政策文件表述、数据、案例、历史事件</t>
+  </si>
+  <si>
+    <t>隐性信息：材料的情感倾向（肯定/否定）、逻辑（因果、并列、对比）</t>
+  </si>
+  <si>
+    <t>考点匹配（索引以下粒度的匹配）</t>
+  </si>
+  <si>
+    <t>运用原理yyy</t>
+  </si>
+  <si>
+    <t>从zzz角度</t>
+  </si>
+  <si>
+    <t>答题</t>
+  </si>
+  <si>
+    <t>格式要求</t>
+  </si>
+  <si>
+    <t>分点内不分段</t>
+  </si>
+  <si>
+    <t>每点独立逻辑单元</t>
+  </si>
+  <si>
+    <t>核心理论</t>
+  </si>
+  <si>
+    <t>材料结合</t>
+  </si>
+  <si>
+    <t>推导</t>
+  </si>
+  <si>
+    <t>得分点写开头</t>
+  </si>
+  <si>
+    <t>材料中的关键词</t>
+  </si>
+  <si>
+    <t>书本上的理论</t>
+  </si>
+  <si>
+    <t>答题模板</t>
+  </si>
+  <si>
+    <t>是什么</t>
+  </si>
+  <si>
+    <t>A原理的内涵是（教材定义）</t>
+  </si>
+  <si>
+    <t>材料中“B”的表述正是这一原理的体现</t>
+  </si>
+  <si>
+    <t>为什么</t>
+  </si>
+  <si>
+    <t>理论依据：A是B的必然要求</t>
+  </si>
+  <si>
+    <t>现实依据：材料中C问题，决定了必须坚持B</t>
+  </si>
+  <si>
+    <t>意义：坚持A有利于C</t>
+  </si>
+  <si>
+    <t>怎么做</t>
+  </si>
+  <si>
+    <t>第一，坚持A（书），B的情况（材料）体现了A</t>
+  </si>
+  <si>
+    <t>第n，聚焦C（书），D的情况（材料）体现了C</t>
+  </si>
+  <si>
+    <t>分析说明</t>
+  </si>
+  <si>
+    <t>A原理指出（书）</t>
+  </si>
+  <si>
+    <t>材料中B现象（材料）</t>
+  </si>
+  <si>
+    <t>体现了A（书）</t>
+  </si>
+  <si>
+    <t>从A原理出发，可以得出结论C（书）</t>
+  </si>
+  <si>
+    <t>收尾</t>
+  </si>
+  <si>
+    <t>简单收尾（是什么/为什么）：综上，A是B的必然要求</t>
+  </si>
+  <si>
+    <t>启示收尾（怎么做）：坚持A不动摇，为实现B目标提供支撑</t>
+  </si>
+  <si>
+    <t>分科技巧</t>
+  </si>
+  <si>
+    <t>马原</t>
+  </si>
+  <si>
+    <t>判断模块，避免跨模块混用</t>
+  </si>
+  <si>
+    <t>精准写出原理名+核心观点</t>
+  </si>
+  <si>
+    <t>材料结合一对一</t>
+  </si>
+  <si>
+    <t>毛中特</t>
+  </si>
+  <si>
+    <t>确定主题（类似马原判断模块）</t>
+  </si>
+  <si>
+    <t>逻辑展开</t>
+  </si>
+  <si>
+    <t>理论内涵</t>
+  </si>
+  <si>
+    <t>实践成就</t>
+  </si>
+  <si>
+    <t>现存问题</t>
+  </si>
+  <si>
+    <t>解决路径</t>
+  </si>
+  <si>
+    <t>材料结合大概率是某政策落地</t>
+  </si>
+  <si>
+    <t>“某地产业升级”→对应 “新发展理念中的创新驱动”</t>
+  </si>
+  <si>
+    <t>史纲</t>
+  </si>
+  <si>
+    <t>事件的实践、背景、核心人物</t>
+  </si>
+  <si>
+    <t>默写事件的历史意义</t>
+  </si>
+  <si>
+    <t>分析事件的现实启示（毛中特）</t>
+  </si>
+  <si>
+    <t>例：坚持党的领导、坚持中国特色社会主义道路</t>
+  </si>
+  <si>
+    <t>体现唯物史观（事件的产生有它的必然性）</t>
+  </si>
+  <si>
+    <t>历史实践证明，资产阶级的道路行不通</t>
+  </si>
+  <si>
+    <t>法德</t>
+  </si>
+  <si>
+    <t>区分考察维度（和毛中特、马原的第一步类似）</t>
+  </si>
+  <si>
+    <t>思想：理想信念、家国情怀</t>
+  </si>
+  <si>
+    <t>道德：社会主义核心价值观</t>
+  </si>
+  <si>
+    <t>法律：权利义务、法治精神</t>
+  </si>
+  <si>
+    <t>思想道德类：是什么（核心观点）-&gt;为什么（重要性）-&gt;怎么做（个人践行）</t>
+  </si>
+  <si>
+    <t>法律类：法律依据（某种特定的权利或义务）-&gt;案例分析（材料中）-&gt;启示（尊法学法守法）</t>
+  </si>
+  <si>
+    <t>时政</t>
+  </si>
+  <si>
+    <t>中国的立场</t>
+  </si>
+  <si>
+    <t>国际形势（材料）-&gt;中国方案（书+时政文件）-&gt;意义（对中国、对世界）</t>
+  </si>
+  <si>
+    <t>散列表的ASL### ###</t>
+  </si>
+  <si>
+    <t>具体装填状况的ASL：每个位置到达下一个空位的探测次数和/位置个数（失败）</t>
+  </si>
+  <si>
+    <t>未知装填状况的ASL：用装填因子α套公式算</t>
+  </si>
+  <si>
+    <t>线性探测：</t>
+  </si>
+  <si>
+    <t>成功：(1/(2(1-α)))+1/2</t>
+  </si>
+  <si>
+    <t>失败：(1/(2(1-α)²))+1/2</t>
+  </si>
+  <si>
+    <t>平方探测/双散列：</t>
+  </si>
+  <si>
+    <t>成功：-ln(1-α)/α</t>
+  </si>
+  <si>
+    <t>失败：1/ln(1-α)</t>
+  </si>
+  <si>
+    <t>实质上是具体ASL的期望（Σ每一种装填状况的概率*对应装填状况的ASL）</t>
+  </si>
+  <si>
+    <t>循环队列的队尾指针指向下一个插入的位置，未满的状况下，指向的位置应当是空的### ###</t>
+  </si>
+  <si>
+    <t xml:space="preserve">、 </t>
   </si>
 </sst>
 </file>
@@ -52324,6 +52801,962 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet213.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>22.9833333333333</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2199)/COLUMN()</f>
+        <v>13</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>6.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>3.25</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="C4" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="C5" t="s">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="C6" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" t="s">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="C8" t="s">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="C9" t="s">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" t="s">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="C12" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" t="s">
+        <v>4322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" t="s">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" t="s">
+        <v>4324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="C16" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="C17" t="s">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
+        <v>4328</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="C25" t="s">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26" t="s">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" t="s">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="C32" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5">
+      <c r="D33" t="s">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="D34" t="s">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5">
+      <c r="E35" t="s">
+        <v>4344</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5">
+      <c r="D36" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5">
+      <c r="D37" t="s">
+        <v>4346</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="E38" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5">
+      <c r="C39" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5">
+      <c r="D40" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5">
+      <c r="D41" t="s">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5">
+      <c r="D42" t="s">
+        <v>4351</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5">
+      <c r="C43" t="s">
+        <v>4352</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5">
+      <c r="D44" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5">
+      <c r="D45" t="s">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5">
+      <c r="D46" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5">
+      <c r="C47" t="s">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5">
+      <c r="D48" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="D49" t="s">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="D50" t="s">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" t="s">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="C52" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="C53" t="s">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="C54" t="s">
+        <v>4363</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" t="s">
+        <v>4364</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" t="s">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="C57" t="s">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" t="s">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" t="s">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" t="s">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="C61" t="s">
+        <v>4370</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet214.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>4.16666666666667</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2196)/COLUMN()</f>
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" t="s">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="D4" t="s">
+        <v>4373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="C5" t="s">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="D6" t="s">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" t="s">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" t="s">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="C9" t="s">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="C10" t="s">
+        <v>4379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" t="s">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="C12" t="s">
+        <v>4381</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet215.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:M87"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1">
+        <f>SUM(B1:AZ1)</f>
+        <v>18.9</v>
+      </c>
+      <c r="B1" s="1">
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2202)/COLUMN()</f>
+        <v>1.5</v>
+      </c>
+      <c r="C1" s="1">
+        <f t="shared" si="0"/>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="D1" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <f t="shared" si="0"/>
+        <v>6.4</v>
+      </c>
+      <c r="F1" s="1">
+        <f t="shared" si="0"/>
+        <v>4.66666666666667</v>
+      </c>
+      <c r="G1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="str" cm="1">
+        <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251201</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" t="s">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="D4" t="s">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="E5" t="s">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="F6" t="s">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="F7" t="s">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="D8" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="E9" t="s">
+        <v>4389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="C10" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" t="s">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="E12" t="s">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="E13" t="s">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="D14" t="s">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="E15" t="s">
+        <v>4395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="E16" t="s">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" t="s">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="D18" t="s">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6">
+      <c r="E19" t="s">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="E20" t="s">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="F21" t="s">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="F22" t="s">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="F23" t="s">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="E24" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="F25" t="s">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="F26" t="s">
+        <v>4406</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="D27" t="s">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6">
+      <c r="E28" t="s">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6">
+      <c r="F29" t="s">
+        <v>4409</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6">
+      <c r="F30" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6">
+      <c r="E31" t="s">
+        <v>4411</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6">
+      <c r="F32" t="s">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6">
+      <c r="F33" t="s">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6">
+      <c r="F34" t="s">
+        <v>4414</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6">
+      <c r="E35" t="s">
+        <v>4415</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6">
+      <c r="F36" t="s">
+        <v>4416</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6">
+      <c r="F37" t="s">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6">
+      <c r="E38" t="s">
+        <v>4418</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
+      <c r="F39" t="s">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6">
+      <c r="F40" t="s">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6">
+      <c r="F41" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6">
+      <c r="F42" t="s">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6">
+      <c r="C43" t="s">
+        <v>4423</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6">
+      <c r="D44" t="s">
+        <v>4424</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6">
+      <c r="D45" t="s">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6">
+      <c r="C46" t="s">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6">
+      <c r="D47" t="s">
+        <v>4427</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6">
+      <c r="E48" t="s">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="49" spans="4:6">
+      <c r="E49" t="s">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="50" spans="4:6">
+      <c r="E50" t="s">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="51" spans="4:6">
+      <c r="D51" t="s">
+        <v>4431</v>
+      </c>
+    </row>
+    <row r="52" spans="4:6">
+      <c r="E52" t="s">
+        <v>4432</v>
+      </c>
+    </row>
+    <row r="53" spans="4:6">
+      <c r="E53" t="s">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="54" spans="4:6">
+      <c r="F54" t="s">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="55" spans="4:6">
+      <c r="F55" t="s">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="56" spans="4:6">
+      <c r="F56" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="57" spans="4:6">
+      <c r="F57" t="s">
+        <v>4437</v>
+      </c>
+    </row>
+    <row r="58" spans="4:6">
+      <c r="E58" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="59" spans="4:6">
+      <c r="F59" t="s">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="60" spans="4:6">
+      <c r="D60" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="61" spans="4:6">
+      <c r="E61" t="s">
+        <v>4441</v>
+      </c>
+    </row>
+    <row r="62" spans="4:6">
+      <c r="E62" t="s">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="63" spans="4:6">
+      <c r="E63" t="s">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="64" spans="4:6">
+      <c r="F64" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="E65" t="s">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="F66" t="s">
+        <v>4446</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="D67" t="s">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="E68" t="s">
+        <v>4448</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="F69" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="F70" t="s">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="F71" t="s">
+        <v>4451</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="E72" t="s">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="E73" t="s">
+        <v>4453</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="D74" t="s">
+        <v>4454</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="E75" t="s">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
+      <c r="E76" t="s">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
+      <c r="B77" t="s">
+        <v>4457</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
+      <c r="C78" t="s">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
+      <c r="C79" t="s">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
+      <c r="D80" t="s">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
+      <c r="E81" t="s">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13">
+      <c r="E82" t="s">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13">
+      <c r="D83" t="s">
+        <v>4463</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13">
+      <c r="E84" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13">
+      <c r="E85" t="s">
+        <v>4465</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13">
+      <c r="D86" t="s">
+        <v>4466</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13">
+      <c r="B87" t="s">
+        <v>4467</v>
+      </c>
+      <c r="M87" t="s">
+        <v>4468</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
